--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\Document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47090BE-DFE7-4CE4-9182-D31A5AA789FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4AEC23-592B-415F-B0A4-115DBD096B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17235" yWindow="0" windowWidth="11670" windowHeight="15585" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="9885" yWindow="1335" windowWidth="21600" windowHeight="11385" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="410">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -818,10 +818,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PC ADDR + 4 (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PC ADDR + 4 (EX)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1230,10 +1226,6 @@
   </si>
   <si>
     <t>w_ex_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regwrite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1648,6 +1640,78 @@
     <t>u_pc_mux
 u_if_id_bridge
 u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_control_unit
+u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_jump_mux
+u_alu_forward_a_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regdst_jal_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux
+u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd or $ra Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux
+u_memtoreg_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (WB)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2631,13 +2695,55 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2649,28 +2755,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2680,30 +2768,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3066,31 +3130,31 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="133" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135"/>
-      <c r="I2" s="119" t="s">
+      <c r="B2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="143"/>
+      <c r="I2" s="120" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="121"/>
-      <c r="K2" s="119" t="s">
+      <c r="K2" s="120" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="120"/>
+      <c r="L2" s="122"/>
       <c r="M2" s="121"/>
-      <c r="O2" s="119" t="s">
+      <c r="O2" s="120" t="s">
         <v>102</v>
       </c>
       <c r="P2" s="121"/>
-      <c r="Q2" s="119" t="s">
+      <c r="Q2" s="120" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="120"/>
+      <c r="R2" s="122"/>
       <c r="S2" s="121"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3112,24 +3176,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="128" t="s">
+      <c r="I3" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="130" t="s">
+      <c r="J3" s="131"/>
+      <c r="K3" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="131"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="128" t="s">
+      <c r="L3" s="133"/>
+      <c r="M3" s="134"/>
+      <c r="O3" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="130" t="s">
-        <v>233</v>
-      </c>
-      <c r="R3" s="131"/>
-      <c r="S3" s="132"/>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="132" t="s">
+        <v>232</v>
+      </c>
+      <c r="R3" s="133"/>
+      <c r="S3" s="134"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3150,24 +3214,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="128" t="s">
+      <c r="I4" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="129"/>
-      <c r="K4" s="128" t="s">
+      <c r="J4" s="131"/>
+      <c r="K4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="142"/>
-      <c r="M4" s="129"/>
-      <c r="O4" s="128" t="s">
+      <c r="L4" s="135"/>
+      <c r="M4" s="131"/>
+      <c r="O4" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="128" t="s">
+      <c r="P4" s="131"/>
+      <c r="Q4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="142"/>
-      <c r="S4" s="129"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="131"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3188,24 +3252,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="122" t="s">
+      <c r="I5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="123"/>
-      <c r="K5" s="124" t="s">
+      <c r="J5" s="137"/>
+      <c r="K5" s="138" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="125"/>
-      <c r="M5" s="126"/>
-      <c r="O5" s="122" t="s">
+      <c r="L5" s="119"/>
+      <c r="M5" s="139"/>
+      <c r="O5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="124" t="s">
+      <c r="P5" s="137"/>
+      <c r="Q5" s="138" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="125"/>
-      <c r="S5" s="126"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="139"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3229,22 +3293,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="127" t="s">
+      <c r="J6" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="128"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="127" t="s">
+      <c r="P6" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="127"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="128"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3271,22 +3335,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="136" t="s">
+      <c r="J7" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="143" t="s">
+      <c r="P7" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="143"/>
-      <c r="R7" s="143"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
@@ -3328,11 +3392,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="125" t="s">
+      <c r="P8" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
@@ -3506,15 +3570,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="137" t="s">
+      <c r="I12" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="138"/>
-      <c r="K12" s="139" t="s">
+      <c r="J12" s="124"/>
+      <c r="K12" s="125" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="140"/>
-      <c r="M12" s="141"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="127"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3637,15 +3701,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="137" t="s">
+      <c r="O16" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="139" t="s">
-        <v>236</v>
-      </c>
-      <c r="R16" s="140"/>
-      <c r="S16" s="141"/>
+      <c r="P16" s="124"/>
+      <c r="Q16" s="125" t="s">
+        <v>235</v>
+      </c>
+      <c r="R16" s="126"/>
+      <c r="S16" s="127"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3673,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -3687,23 +3751,23 @@
       <c r="G18" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="119" t="s">
+      <c r="I18" s="120" t="s">
         <v>102</v>
       </c>
       <c r="J18" s="121"/>
-      <c r="K18" s="119" t="s">
+      <c r="K18" s="120" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="120"/>
+      <c r="L18" s="122"/>
       <c r="M18" s="121"/>
-      <c r="O18" s="119" t="s">
+      <c r="O18" s="120" t="s">
         <v>102</v>
       </c>
       <c r="P18" s="121"/>
-      <c r="Q18" s="119" t="s">
+      <c r="Q18" s="120" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="120"/>
+      <c r="R18" s="122"/>
       <c r="S18" s="121"/>
     </row>
     <row r="19" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -3712,7 +3776,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
@@ -3726,24 +3790,24 @@
       <c r="G19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="128" t="s">
+      <c r="I19" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="129"/>
-      <c r="K19" s="130" t="s">
+      <c r="J19" s="131"/>
+      <c r="K19" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="131"/>
-      <c r="M19" s="132"/>
-      <c r="O19" s="128" t="s">
+      <c r="L19" s="133"/>
+      <c r="M19" s="134"/>
+      <c r="O19" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="129"/>
-      <c r="Q19" s="130" t="s">
-        <v>233</v>
-      </c>
-      <c r="R19" s="131"/>
-      <c r="S19" s="132"/>
+      <c r="P19" s="131"/>
+      <c r="Q19" s="132" t="s">
+        <v>232</v>
+      </c>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3751,38 +3815,38 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D20" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F20" s="103" t="s">
         <v>75</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="I20" s="128" t="s">
+        <v>353</v>
+      </c>
+      <c r="I20" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="129"/>
-      <c r="K20" s="130" t="s">
+      <c r="J20" s="131"/>
+      <c r="K20" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="131"/>
-      <c r="M20" s="132"/>
-      <c r="O20" s="128" t="s">
+      <c r="L20" s="133"/>
+      <c r="M20" s="134"/>
+      <c r="O20" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="128" t="s">
+      <c r="P20" s="131"/>
+      <c r="Q20" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="142"/>
-      <c r="S20" s="129"/>
+      <c r="R20" s="135"/>
+      <c r="S20" s="131"/>
     </row>
     <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
@@ -3790,38 +3854,38 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F21" s="103" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="I21" s="122" t="s">
+        <v>355</v>
+      </c>
+      <c r="I21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="123"/>
-      <c r="K21" s="124" t="s">
+      <c r="J21" s="137"/>
+      <c r="K21" s="138" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="125"/>
-      <c r="M21" s="126"/>
-      <c r="O21" s="122" t="s">
+      <c r="L21" s="119"/>
+      <c r="M21" s="139"/>
+      <c r="O21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="124" t="s">
+      <c r="P21" s="137"/>
+      <c r="Q21" s="138" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="125"/>
-      <c r="S21" s="126"/>
+      <c r="R21" s="119"/>
+      <c r="S21" s="139"/>
     </row>
     <row r="22" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
@@ -3829,7 +3893,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>20</v>
@@ -3838,30 +3902,30 @@
         <v>78</v>
       </c>
       <c r="F22" s="103" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="127" t="s">
+      <c r="J22" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="127" t="s">
+      <c r="P22" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q22" s="127"/>
-      <c r="R22" s="127"/>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="128"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
@@ -3872,7 +3936,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -3881,7 +3945,7 @@
         <v>78</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>84</v>
@@ -3889,22 +3953,22 @@
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="136" t="s">
+      <c r="J23" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="136"/>
-      <c r="L23" s="136"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="143" t="s">
+      <c r="P23" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="143"/>
-      <c r="R23" s="143"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="129"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
@@ -3915,19 +3979,19 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
@@ -3947,11 +4011,11 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="125" t="s">
+      <c r="P24" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="125"/>
-      <c r="R24" s="125"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="119"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
@@ -3962,7 +4026,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D25" s="90" t="s">
         <v>20</v>
@@ -4013,19 +4077,19 @@
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
@@ -4064,7 +4128,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D27" s="90" t="s">
         <v>20</v>
@@ -4076,7 +4140,7 @@
         <v>53</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
@@ -4115,7 +4179,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D28" s="90" t="s">
         <v>21</v>
@@ -4166,19 +4230,19 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
@@ -4217,16 +4281,16 @@
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" s="102" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F30" s="103" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>89</v>
@@ -4268,19 +4332,19 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F31" s="103" t="s">
+        <v>384</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F31" s="103" t="s">
-        <v>386</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
@@ -4319,29 +4383,29 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F32" s="103" t="s">
         <v>63</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="I32" s="137" t="s">
+        <v>310</v>
+      </c>
+      <c r="I32" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="138"/>
-      <c r="K32" s="139" t="s">
+      <c r="J32" s="124"/>
+      <c r="K32" s="125" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="140"/>
-      <c r="M32" s="141"/>
+      <c r="L32" s="126"/>
+      <c r="M32" s="127"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4364,19 +4428,19 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D33" s="1">
         <v>6</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
@@ -4400,19 +4464,19 @@
         <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D34" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F34" s="103" t="s">
         <v>63</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
@@ -4436,19 +4500,19 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F35" s="103" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
@@ -4472,29 +4536,29 @@
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F36" s="103" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="O36" s="137" t="s">
+        <v>303</v>
+      </c>
+      <c r="O36" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="138"/>
-      <c r="Q36" s="139" t="s">
-        <v>237</v>
-      </c>
-      <c r="R36" s="140"/>
-      <c r="S36" s="141"/>
+      <c r="P36" s="124"/>
+      <c r="Q36" s="125" t="s">
+        <v>236</v>
+      </c>
+      <c r="R36" s="126"/>
+      <c r="S36" s="127"/>
     </row>
     <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4502,19 +4566,19 @@
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
       </c>
       <c r="E37" s="102" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F37" s="103" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -4523,37 +4587,37 @@
         <v>21</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="102" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F38" s="103" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="I38" s="119" t="s">
+        <v>361</v>
+      </c>
+      <c r="I38" s="120" t="s">
         <v>102</v>
       </c>
       <c r="J38" s="121"/>
-      <c r="K38" s="119" t="s">
+      <c r="K38" s="120" t="s">
         <v>122</v>
       </c>
-      <c r="L38" s="120"/>
+      <c r="L38" s="122"/>
       <c r="M38" s="121"/>
-      <c r="O38" s="119" t="s">
+      <c r="O38" s="120" t="s">
         <v>102</v>
       </c>
       <c r="P38" s="121"/>
-      <c r="Q38" s="119" t="s">
+      <c r="Q38" s="120" t="s">
         <v>173</v>
       </c>
-      <c r="R38" s="120"/>
+      <c r="R38" s="122"/>
       <c r="S38" s="121"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
@@ -4562,7 +4626,7 @@
         <v>22</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D39" s="90" t="s">
         <v>20</v>
@@ -4576,24 +4640,24 @@
       <c r="G39" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I39" s="128" t="s">
+      <c r="I39" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J39" s="129"/>
-      <c r="K39" s="130" t="s">
+      <c r="J39" s="131"/>
+      <c r="K39" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="131"/>
-      <c r="M39" s="132"/>
-      <c r="O39" s="128" t="s">
+      <c r="L39" s="133"/>
+      <c r="M39" s="134"/>
+      <c r="O39" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P39" s="129"/>
-      <c r="Q39" s="130" t="s">
-        <v>233</v>
-      </c>
-      <c r="R39" s="131"/>
-      <c r="S39" s="132"/>
+      <c r="P39" s="131"/>
+      <c r="Q39" s="132" t="s">
+        <v>232</v>
+      </c>
+      <c r="R39" s="133"/>
+      <c r="S39" s="134"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
@@ -4601,38 +4665,38 @@
         <v>23</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D40" s="101" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="102" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="I40" s="128" t="s">
+        <v>230</v>
+      </c>
+      <c r="I40" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J40" s="129"/>
-      <c r="K40" s="130" t="s">
+      <c r="J40" s="131"/>
+      <c r="K40" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L40" s="131"/>
-      <c r="M40" s="132"/>
-      <c r="O40" s="128" t="s">
+      <c r="L40" s="133"/>
+      <c r="M40" s="134"/>
+      <c r="O40" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P40" s="129"/>
-      <c r="Q40" s="128" t="s">
+      <c r="P40" s="131"/>
+      <c r="Q40" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="142"/>
-      <c r="S40" s="129"/>
+      <c r="R40" s="135"/>
+      <c r="S40" s="131"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4640,7 +4704,7 @@
         <v>24</v>
       </c>
       <c r="C41" s="97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D41" s="90" t="s">
         <v>21</v>
@@ -4649,29 +4713,29 @@
         <v>36</v>
       </c>
       <c r="F41" s="98" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G41" s="99" t="s">
-        <v>275</v>
-      </c>
-      <c r="I41" s="122" t="s">
+        <v>274</v>
+      </c>
+      <c r="I41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="123"/>
-      <c r="K41" s="124" t="s">
+      <c r="J41" s="137"/>
+      <c r="K41" s="138" t="s">
         <v>125</v>
       </c>
-      <c r="L41" s="125"/>
-      <c r="M41" s="126"/>
-      <c r="O41" s="122" t="s">
+      <c r="L41" s="119"/>
+      <c r="M41" s="139"/>
+      <c r="O41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="123"/>
-      <c r="Q41" s="124" t="s">
+      <c r="P41" s="137"/>
+      <c r="Q41" s="138" t="s">
         <v>174</v>
       </c>
-      <c r="R41" s="125"/>
-      <c r="S41" s="126"/>
+      <c r="R41" s="119"/>
+      <c r="S41" s="139"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
@@ -4679,7 +4743,7 @@
         <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D42" s="90" t="s">
         <v>20</v>
@@ -4696,22 +4760,22 @@
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="127" t="s">
+      <c r="J42" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K42" s="127"/>
-      <c r="L42" s="127"/>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="127" t="s">
+      <c r="P42" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q42" s="127"/>
-      <c r="R42" s="127"/>
+      <c r="Q42" s="128"/>
+      <c r="R42" s="128"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4722,39 +4786,39 @@
         <v>26</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
       <c r="E43" s="114" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F43" s="98" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="136" t="s">
+      <c r="J43" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="136"/>
-      <c r="L43" s="136"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="140"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="143" t="s">
+      <c r="P43" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="143"/>
-      <c r="R43" s="143"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="129"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
@@ -4765,19 +4829,19 @@
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F44" s="103" t="s">
         <v>237</v>
       </c>
-      <c r="F44" s="103" t="s">
-        <v>238</v>
-      </c>
       <c r="G44" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
@@ -4797,11 +4861,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="125" t="s">
+      <c r="P44" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="125"/>
-      <c r="R44" s="125"/>
+      <c r="Q44" s="119"/>
+      <c r="R44" s="119"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
@@ -4812,19 +4876,19 @@
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
       </c>
       <c r="E45" s="114" t="s">
+        <v>236</v>
+      </c>
+      <c r="F45" s="114" t="s">
         <v>237</v>
       </c>
-      <c r="F45" s="114" t="s">
-        <v>238</v>
-      </c>
       <c r="G45" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
@@ -4863,19 +4927,19 @@
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D46" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F46" s="103" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G46" s="99" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
@@ -4908,25 +4972,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="33">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D47" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F47" s="103" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
@@ -4965,29 +5029,29 @@
         <v>31</v>
       </c>
       <c r="C48" s="112" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D48" s="113" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F48" s="115" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G48" s="112" t="s">
-        <v>221</v>
-      </c>
-      <c r="I48" s="137" t="s">
+        <v>220</v>
+      </c>
+      <c r="I48" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="138"/>
-      <c r="K48" s="139" t="s">
+      <c r="J48" s="124"/>
+      <c r="K48" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="140"/>
-      <c r="M48" s="141"/>
+      <c r="L48" s="126"/>
+      <c r="M48" s="127"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5010,7 +5074,7 @@
         <v>32</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D49" s="90" t="s">
         <v>56</v>
@@ -5019,10 +5083,10 @@
         <v>63</v>
       </c>
       <c r="F49" s="103" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
@@ -5046,19 +5110,19 @@
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F50" s="103" t="s">
         <v>237</v>
       </c>
-      <c r="F50" s="103" t="s">
-        <v>238</v>
-      </c>
       <c r="G50" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
@@ -5082,7 +5146,7 @@
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D51" s="90" t="s">
         <v>49</v>
@@ -5091,19 +5155,19 @@
         <v>47</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I51" s="119" t="s">
+      <c r="I51" s="120" t="s">
         <v>102</v>
       </c>
       <c r="J51" s="121"/>
-      <c r="K51" s="119" t="s">
+      <c r="K51" s="120" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="120"/>
+      <c r="L51" s="122"/>
       <c r="M51" s="121"/>
       <c r="O51" s="83">
         <v>6</v>
@@ -5127,13 +5191,13 @@
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D52" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>40</v>
@@ -5141,15 +5205,15 @@
       <c r="G52" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I52" s="128" t="s">
+      <c r="I52" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="129"/>
-      <c r="K52" s="130" t="s">
+      <c r="J52" s="131"/>
+      <c r="K52" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="131"/>
-      <c r="M52" s="132"/>
+      <c r="L52" s="133"/>
+      <c r="M52" s="134"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5172,29 +5236,29 @@
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D53" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F53" s="103" t="s">
         <v>48</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="I53" s="128" t="s">
+        <v>223</v>
+      </c>
+      <c r="I53" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="129"/>
-      <c r="K53" s="130" t="s">
+      <c r="J53" s="131"/>
+      <c r="K53" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="131"/>
-      <c r="M53" s="132"/>
+      <c r="L53" s="133"/>
+      <c r="M53" s="134"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5217,29 +5281,29 @@
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D54" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="I54" s="122" t="s">
+        <v>373</v>
+      </c>
+      <c r="I54" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="123"/>
-      <c r="K54" s="124" t="s">
+      <c r="J54" s="137"/>
+      <c r="K54" s="138" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="125"/>
-      <c r="M54" s="126"/>
+      <c r="L54" s="119"/>
+      <c r="M54" s="139"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5262,28 +5326,28 @@
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="127" t="s">
+      <c r="J55" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K55" s="127"/>
-      <c r="L55" s="127"/>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5309,40 +5373,40 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="143" t="s">
+      <c r="J56" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="143"/>
-      <c r="L56" s="143"/>
+      <c r="K56" s="129"/>
+      <c r="L56" s="129"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="137" t="s">
+      <c r="O56" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="138"/>
-      <c r="Q56" s="139" t="s">
-        <v>238</v>
-      </c>
-      <c r="R56" s="140"/>
-      <c r="S56" s="141"/>
+      <c r="P56" s="124"/>
+      <c r="Q56" s="125" t="s">
+        <v>237</v>
+      </c>
+      <c r="R56" s="126"/>
+      <c r="S56" s="127"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5350,28 +5414,28 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="G57" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="125" t="s">
+      <c r="J57" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="125"/>
-      <c r="L57" s="125"/>
+      <c r="K57" s="119"/>
+      <c r="L57" s="119"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
@@ -5382,19 +5446,19 @@
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="G58" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
@@ -5411,14 +5475,14 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="119" t="s">
+      <c r="O58" s="120" t="s">
         <v>102</v>
       </c>
       <c r="P58" s="121"/>
-      <c r="Q58" s="119" t="s">
+      <c r="Q58" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="120"/>
+      <c r="R58" s="122"/>
       <c r="S58" s="121"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
@@ -5427,19 +5491,19 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D59" s="33">
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
@@ -5456,15 +5520,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="128" t="s">
+      <c r="O59" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="129"/>
-      <c r="Q59" s="130" t="s">
-        <v>233</v>
-      </c>
-      <c r="R59" s="131"/>
-      <c r="S59" s="132"/>
+      <c r="P59" s="131"/>
+      <c r="Q59" s="132" t="s">
+        <v>232</v>
+      </c>
+      <c r="R59" s="133"/>
+      <c r="S59" s="134"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5478,7 +5542,7 @@
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>44</v>
@@ -5501,15 +5565,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="128" t="s">
+      <c r="O60" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="129"/>
-      <c r="Q60" s="128" t="s">
+      <c r="P60" s="131"/>
+      <c r="Q60" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="142"/>
-      <c r="S60" s="129"/>
+      <c r="R60" s="135"/>
+      <c r="S60" s="131"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5517,7 +5581,7 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -5526,10 +5590,10 @@
         <v>58</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
@@ -5546,15 +5610,15 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="122" t="s">
+      <c r="O61" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="123"/>
-      <c r="Q61" s="124" t="s">
+      <c r="P61" s="137"/>
+      <c r="Q61" s="138" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="125"/>
-      <c r="S61" s="126"/>
+      <c r="R61" s="119"/>
+      <c r="S61" s="139"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5562,7 +5626,7 @@
         <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D62" s="1">
         <v>2</v>
@@ -5571,10 +5635,10 @@
         <v>58</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
@@ -5594,11 +5658,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="127" t="s">
+      <c r="P62" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="127"/>
-      <c r="R62" s="127"/>
+      <c r="Q62" s="128"/>
+      <c r="R62" s="128"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5609,7 +5673,7 @@
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
@@ -5618,10 +5682,10 @@
         <v>58</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
@@ -5641,11 +5705,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="143" t="s">
+      <c r="P63" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="143"/>
-      <c r="R63" s="143"/>
+      <c r="Q63" s="129"/>
+      <c r="R63" s="129"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
@@ -5656,7 +5720,7 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D64" s="90" t="s">
         <v>57</v>
@@ -5688,22 +5752,22 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="125" t="s">
+      <c r="P64" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="125"/>
-      <c r="R64" s="125"/>
+      <c r="Q64" s="119"/>
+      <c r="R64" s="119"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="33">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D65" s="1">
         <v>6</v>
@@ -5711,11 +5775,11 @@
       <c r="E65" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>237</v>
+      <c r="F65" s="103" t="s">
+        <v>393</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
@@ -5754,7 +5818,7 @@
         <v>49</v>
       </c>
       <c r="C66" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D66" s="101" t="s">
         <v>45</v>
@@ -5805,7 +5869,7 @@
         <v>50</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D67" s="90" t="s">
         <v>55</v>
@@ -5856,7 +5920,7 @@
         <v>51</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D68" s="90" t="s">
         <v>56</v>
@@ -5865,10 +5929,10 @@
         <v>44</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
@@ -5907,7 +5971,7 @@
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D69" s="90" t="s">
         <v>56</v>
@@ -5916,10 +5980,10 @@
         <v>44</v>
       </c>
       <c r="F69" s="103" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
@@ -5958,7 +6022,7 @@
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D70" s="90" t="s">
         <v>56</v>
@@ -5967,10 +6031,10 @@
         <v>44</v>
       </c>
       <c r="F70" s="103" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
@@ -6009,7 +6073,7 @@
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D71" s="1">
         <v>5</v>
@@ -6060,38 +6124,38 @@
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I72" s="137" t="s">
+        <v>215</v>
+      </c>
+      <c r="I72" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="138"/>
-      <c r="K72" s="139" t="s">
+      <c r="J72" s="124"/>
+      <c r="K72" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="140"/>
-      <c r="M72" s="141"/>
-      <c r="O72" s="137" t="s">
+      <c r="L72" s="126"/>
+      <c r="M72" s="127"/>
+      <c r="O72" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="P72" s="138"/>
-      <c r="Q72" s="139" t="s">
-        <v>239</v>
-      </c>
-      <c r="R72" s="140"/>
-      <c r="S72" s="141"/>
+      <c r="P72" s="124"/>
+      <c r="Q72" s="125" t="s">
+        <v>238</v>
+      </c>
+      <c r="R72" s="126"/>
+      <c r="S72" s="127"/>
     </row>
     <row r="73" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
@@ -6099,19 +6163,19 @@
         <v>56</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D73" s="101" t="s">
         <v>20</v>
       </c>
       <c r="E73" s="102" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74" spans="2:19" x14ac:dyDescent="0.3">
@@ -6120,7 +6184,7 @@
         <v>57</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -6129,10 +6193,10 @@
         <v>58</v>
       </c>
       <c r="F74" s="114" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
@@ -6141,7 +6205,7 @@
         <v>58</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -6150,10 +6214,10 @@
         <v>58</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
@@ -6162,7 +6226,7 @@
         <v>59</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -6171,10 +6235,10 @@
         <v>58</v>
       </c>
       <c r="F76" s="114" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -6183,19 +6247,19 @@
         <v>60</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D77" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F77" s="103" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G77" s="99" t="s">
-        <v>194</v>
+        <v>407</v>
       </c>
     </row>
     <row r="78" spans="2:19" x14ac:dyDescent="0.3">
@@ -6204,7 +6268,7 @@
         <v>61</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D78" s="90" t="s">
         <v>20</v>
@@ -6213,10 +6277,10 @@
         <v>62</v>
       </c>
       <c r="F78" s="111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
@@ -6225,7 +6289,7 @@
         <v>62</v>
       </c>
       <c r="C79" s="112" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D79" s="113" t="s">
         <v>20</v>
@@ -6234,10 +6298,10 @@
         <v>62</v>
       </c>
       <c r="F79" s="111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G79" s="112" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6246,7 +6310,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -6255,10 +6319,10 @@
         <v>58</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
@@ -6267,7 +6331,7 @@
         <v>64</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D81" s="1">
         <v>1</v>
@@ -6276,10 +6340,10 @@
         <v>58</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -6288,7 +6352,7 @@
         <v>65</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D82" s="101" t="s">
         <v>46</v>
@@ -6297,7 +6361,7 @@
         <v>42</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>51</v>
@@ -6309,7 +6373,7 @@
         <v>66</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -6321,7 +6385,7 @@
         <v>43</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -6330,7 +6394,7 @@
         <v>67</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D84" s="90" t="s">
         <v>20</v>
@@ -6339,10 +6403,10 @@
         <v>43</v>
       </c>
       <c r="F84" s="103" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
@@ -6360,7 +6424,7 @@
         <v>39</v>
       </c>
       <c r="F85" s="98" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G85" s="99" t="s">
         <v>191</v>
@@ -6372,7 +6436,7 @@
         <v>69</v>
       </c>
       <c r="C86" s="93" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D86" s="92">
         <v>1</v>
@@ -6393,7 +6457,7 @@
         <v>70</v>
       </c>
       <c r="C87" s="93" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D87" s="94" t="s">
         <v>21</v>
@@ -6402,7 +6466,7 @@
         <v>35</v>
       </c>
       <c r="F87" s="95" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G87" s="96" t="s">
         <v>37</v>
@@ -6414,19 +6478,19 @@
         <v>71</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D88" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="89" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6435,19 +6499,19 @@
         <v>72</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D89" s="1">
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F89" s="103" t="s">
         <v>391</v>
       </c>
-      <c r="F89" s="103" t="s">
-        <v>393</v>
-      </c>
       <c r="G89" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="90" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -6456,19 +6520,19 @@
         <v>73</v>
       </c>
       <c r="C90" s="104" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D90" s="109" t="s">
         <v>20</v>
       </c>
       <c r="E90" s="105" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F90" s="110" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G90" s="107" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -6477,19 +6541,19 @@
         <v>74</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D91" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E91" s="103" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F91" s="103" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
@@ -6498,19 +6562,19 @@
         <v>75</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F92" s="103" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6519,19 +6583,19 @@
         <v>76</v>
       </c>
       <c r="C93" s="104" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D93" s="105">
         <v>1</v>
       </c>
       <c r="E93" s="105" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F93" s="106" t="s">
         <v>14</v>
       </c>
       <c r="G93" s="107" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
@@ -6540,19 +6604,19 @@
         <v>77</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
       </c>
       <c r="E94" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="G94" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6561,19 +6625,19 @@
         <v>78</v>
       </c>
       <c r="C95" s="104" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D95" s="105">
         <v>1</v>
       </c>
       <c r="E95" s="105" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F95" s="108" t="s">
         <v>73</v>
       </c>
       <c r="G95" s="107" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6582,19 +6646,19 @@
         <v>79</v>
       </c>
       <c r="C96" s="112" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D96" s="113" t="s">
         <v>20</v>
       </c>
       <c r="E96" s="111" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F96" s="118" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G96" s="112" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6603,19 +6667,19 @@
         <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D97" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F97" s="103" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6624,19 +6688,19 @@
         <v>81</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F98" s="103" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
@@ -6645,19 +6709,19 @@
         <v>82</v>
       </c>
       <c r="C99" s="104" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D99" s="109" t="s">
         <v>20</v>
       </c>
       <c r="E99" s="117" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F99" s="106" t="s">
         <v>17</v>
       </c>
       <c r="G99" s="107" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
@@ -6666,19 +6730,19 @@
         <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D100" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="101" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -6687,19 +6751,19 @@
         <v>84</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D101" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F101" s="103" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -6708,19 +6772,19 @@
         <v>85</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D102" s="1">
         <v>1</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>80</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
@@ -6729,7 +6793,7 @@
         <v>86</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D103" s="90" t="s">
         <v>20</v>
@@ -6741,7 +6805,7 @@
         <v>62</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="104" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6750,19 +6814,19 @@
         <v>87</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D104" s="90" t="s">
         <v>56</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F104" s="103" t="s">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6771,60 +6835,129 @@
         <v>88</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>300</v>
+        <v>405</v>
       </c>
       <c r="D105" s="1">
         <v>1</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F105" s="103" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B106" s="33" t="str">
+      <c r="B106" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F106" s="103"/>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B107" s="33" t="str">
+        <v>89</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D106" s="1">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B107" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F107" s="103"/>
+        <v>90</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D107" s="1">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F107" s="103" t="s">
+        <v>406</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B108" s="33" t="str">
+      <c r="B108" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" s="103"/>
+        <v>91</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D108" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F108" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B109" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F109" s="103"/>
+      <c r="B109" s="33">
+        <f>IF(C109="","",B108+1)</f>
+        <v>92</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D109" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B110" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F110" s="103"/>
+      <c r="B110" s="33">
+        <f>IF(C110="","",B109+1)</f>
+        <v>93</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D110" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F110" s="103" t="s">
+        <v>80</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(C111="","",B110+1)</f>
         <v/>
       </c>
     </row>
@@ -7009,15 +7142,75 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="O72:P72"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="P8:R8"/>
@@ -7042,75 +7235,15 @@
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7132,25 +7265,25 @@
   <sheetData>
     <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="102" t="s">
         <v>318</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="102" t="s">
         <v>319</v>
-      </c>
-      <c r="G2" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="H2" s="102" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4AEC23-592B-415F-B0A4-115DBD096B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54974AFD-0562-4AE2-B869-771DCA299A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9885" yWindow="1335" windowWidth="21600" windowHeight="11385" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
@@ -2695,16 +2695,58 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2722,52 +2764,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3130,31 +3130,31 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="143"/>
-      <c r="I2" s="120" t="s">
+      <c r="B2" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135"/>
+      <c r="I2" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="121"/>
-      <c r="K2" s="120" t="s">
+      <c r="K2" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="122"/>
+      <c r="L2" s="120"/>
       <c r="M2" s="121"/>
-      <c r="O2" s="120" t="s">
+      <c r="O2" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P2" s="121"/>
-      <c r="Q2" s="120" t="s">
+      <c r="Q2" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="122"/>
+      <c r="R2" s="120"/>
       <c r="S2" s="121"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3176,24 +3176,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="131"/>
-      <c r="K3" s="132" t="s">
+      <c r="J3" s="129"/>
+      <c r="K3" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="133"/>
-      <c r="M3" s="134"/>
-      <c r="O3" s="130" t="s">
+      <c r="L3" s="131"/>
+      <c r="M3" s="132"/>
+      <c r="O3" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="132" t="s">
+      <c r="P3" s="129"/>
+      <c r="Q3" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="R3" s="133"/>
-      <c r="S3" s="134"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="132"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3214,24 +3214,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="130" t="s">
+      <c r="J4" s="129"/>
+      <c r="K4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="135"/>
-      <c r="M4" s="131"/>
-      <c r="O4" s="130" t="s">
+      <c r="L4" s="142"/>
+      <c r="M4" s="129"/>
+      <c r="O4" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="130" t="s">
+      <c r="P4" s="129"/>
+      <c r="Q4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="135"/>
-      <c r="S4" s="131"/>
+      <c r="R4" s="142"/>
+      <c r="S4" s="129"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3252,24 +3252,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="136" t="s">
+      <c r="I5" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="137"/>
-      <c r="K5" s="138" t="s">
+      <c r="J5" s="123"/>
+      <c r="K5" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="139"/>
-      <c r="O5" s="136" t="s">
+      <c r="L5" s="125"/>
+      <c r="M5" s="126"/>
+      <c r="O5" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="138" t="s">
+      <c r="P5" s="123"/>
+      <c r="Q5" s="124" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="119"/>
-      <c r="S5" s="139"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3293,22 +3293,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="128" t="s">
+      <c r="J6" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="128"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="128" t="s">
+      <c r="P6" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="128"/>
-      <c r="R6" s="128"/>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="127"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3335,22 +3335,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="140" t="s">
+      <c r="J7" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="129" t="s">
+      <c r="P7" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
+      <c r="Q7" s="143"/>
+      <c r="R7" s="143"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
@@ -3392,11 +3392,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="119" t="s">
+      <c r="P8" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="119"/>
-      <c r="R8" s="119"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
@@ -3570,15 +3570,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="124"/>
-      <c r="K12" s="125" t="s">
+      <c r="J12" s="138"/>
+      <c r="K12" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="126"/>
-      <c r="M12" s="127"/>
+      <c r="L12" s="140"/>
+      <c r="M12" s="141"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3701,15 +3701,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="123" t="s">
+      <c r="O16" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="125" t="s">
+      <c r="P16" s="138"/>
+      <c r="Q16" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="R16" s="126"/>
-      <c r="S16" s="127"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="141"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3751,23 +3751,23 @@
       <c r="G18" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="120" t="s">
+      <c r="I18" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J18" s="121"/>
-      <c r="K18" s="120" t="s">
+      <c r="K18" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="122"/>
+      <c r="L18" s="120"/>
       <c r="M18" s="121"/>
-      <c r="O18" s="120" t="s">
+      <c r="O18" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P18" s="121"/>
-      <c r="Q18" s="120" t="s">
+      <c r="Q18" s="119" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="122"/>
+      <c r="R18" s="120"/>
       <c r="S18" s="121"/>
     </row>
     <row r="19" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -3790,24 +3790,24 @@
       <c r="G19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="130" t="s">
+      <c r="I19" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="131"/>
-      <c r="K19" s="132" t="s">
+      <c r="J19" s="129"/>
+      <c r="K19" s="130" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="133"/>
-      <c r="M19" s="134"/>
-      <c r="O19" s="130" t="s">
+      <c r="L19" s="131"/>
+      <c r="M19" s="132"/>
+      <c r="O19" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="132" t="s">
+      <c r="P19" s="129"/>
+      <c r="Q19" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="R19" s="131"/>
+      <c r="S19" s="132"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3829,24 +3829,24 @@
       <c r="G20" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="I20" s="130" t="s">
+      <c r="I20" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="131"/>
-      <c r="K20" s="132" t="s">
+      <c r="J20" s="129"/>
+      <c r="K20" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
-      <c r="O20" s="130" t="s">
+      <c r="L20" s="131"/>
+      <c r="M20" s="132"/>
+      <c r="O20" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="130" t="s">
+      <c r="P20" s="129"/>
+      <c r="Q20" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="135"/>
-      <c r="S20" s="131"/>
+      <c r="R20" s="142"/>
+      <c r="S20" s="129"/>
     </row>
     <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
@@ -3868,24 +3868,24 @@
       <c r="G21" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="I21" s="136" t="s">
+      <c r="I21" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="137"/>
-      <c r="K21" s="138" t="s">
+      <c r="J21" s="123"/>
+      <c r="K21" s="124" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="119"/>
-      <c r="M21" s="139"/>
-      <c r="O21" s="136" t="s">
+      <c r="L21" s="125"/>
+      <c r="M21" s="126"/>
+      <c r="O21" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="138" t="s">
+      <c r="P21" s="123"/>
+      <c r="Q21" s="124" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="119"/>
-      <c r="S21" s="139"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="126"/>
     </row>
     <row r="22" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
@@ -3910,22 +3910,22 @@
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="128" t="s">
+      <c r="J22" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="128" t="s">
+      <c r="P22" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q22" s="128"/>
-      <c r="R22" s="128"/>
+      <c r="Q22" s="127"/>
+      <c r="R22" s="127"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
@@ -3953,22 +3953,22 @@
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="140" t="s">
+      <c r="J23" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="129" t="s">
+      <c r="P23" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="129"/>
-      <c r="R23" s="129"/>
+      <c r="Q23" s="143"/>
+      <c r="R23" s="143"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
@@ -4011,11 +4011,11 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="119" t="s">
+      <c r="P24" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="119"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="125"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
@@ -4397,15 +4397,15 @@
       <c r="G32" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="I32" s="123" t="s">
+      <c r="I32" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="124"/>
-      <c r="K32" s="125" t="s">
+      <c r="J32" s="138"/>
+      <c r="K32" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="126"/>
-      <c r="M32" s="127"/>
+      <c r="L32" s="140"/>
+      <c r="M32" s="141"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4550,15 +4550,15 @@
       <c r="G36" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="O36" s="123" t="s">
+      <c r="O36" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="125" t="s">
+      <c r="P36" s="138"/>
+      <c r="Q36" s="139" t="s">
         <v>236</v>
       </c>
-      <c r="R36" s="126"/>
-      <c r="S36" s="127"/>
+      <c r="R36" s="140"/>
+      <c r="S36" s="141"/>
     </row>
     <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4601,23 +4601,23 @@
       <c r="G38" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="I38" s="120" t="s">
+      <c r="I38" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J38" s="121"/>
-      <c r="K38" s="120" t="s">
+      <c r="K38" s="119" t="s">
         <v>122</v>
       </c>
-      <c r="L38" s="122"/>
+      <c r="L38" s="120"/>
       <c r="M38" s="121"/>
-      <c r="O38" s="120" t="s">
+      <c r="O38" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P38" s="121"/>
-      <c r="Q38" s="120" t="s">
+      <c r="Q38" s="119" t="s">
         <v>173</v>
       </c>
-      <c r="R38" s="122"/>
+      <c r="R38" s="120"/>
       <c r="S38" s="121"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.3">
@@ -4640,24 +4640,24 @@
       <c r="G39" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I39" s="130" t="s">
+      <c r="I39" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J39" s="131"/>
-      <c r="K39" s="132" t="s">
+      <c r="J39" s="129"/>
+      <c r="K39" s="130" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="133"/>
-      <c r="M39" s="134"/>
-      <c r="O39" s="130" t="s">
+      <c r="L39" s="131"/>
+      <c r="M39" s="132"/>
+      <c r="O39" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="132" t="s">
+      <c r="P39" s="129"/>
+      <c r="Q39" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="R39" s="133"/>
-      <c r="S39" s="134"/>
+      <c r="R39" s="131"/>
+      <c r="S39" s="132"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
@@ -4679,24 +4679,24 @@
       <c r="G40" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I40" s="130" t="s">
+      <c r="I40" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J40" s="131"/>
-      <c r="K40" s="132" t="s">
+      <c r="J40" s="129"/>
+      <c r="K40" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L40" s="133"/>
-      <c r="M40" s="134"/>
-      <c r="O40" s="130" t="s">
+      <c r="L40" s="131"/>
+      <c r="M40" s="132"/>
+      <c r="O40" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P40" s="131"/>
-      <c r="Q40" s="130" t="s">
+      <c r="P40" s="129"/>
+      <c r="Q40" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="135"/>
-      <c r="S40" s="131"/>
+      <c r="R40" s="142"/>
+      <c r="S40" s="129"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4718,24 +4718,24 @@
       <c r="G41" s="99" t="s">
         <v>274</v>
       </c>
-      <c r="I41" s="136" t="s">
+      <c r="I41" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="137"/>
-      <c r="K41" s="138" t="s">
+      <c r="J41" s="123"/>
+      <c r="K41" s="124" t="s">
         <v>125</v>
       </c>
-      <c r="L41" s="119"/>
-      <c r="M41" s="139"/>
-      <c r="O41" s="136" t="s">
+      <c r="L41" s="125"/>
+      <c r="M41" s="126"/>
+      <c r="O41" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="137"/>
-      <c r="Q41" s="138" t="s">
+      <c r="P41" s="123"/>
+      <c r="Q41" s="124" t="s">
         <v>174</v>
       </c>
-      <c r="R41" s="119"/>
-      <c r="S41" s="139"/>
+      <c r="R41" s="125"/>
+      <c r="S41" s="126"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
@@ -4760,22 +4760,22 @@
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="128" t="s">
+      <c r="J42" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="128" t="s">
+      <c r="P42" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q42" s="128"/>
-      <c r="R42" s="128"/>
+      <c r="Q42" s="127"/>
+      <c r="R42" s="127"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4803,22 +4803,22 @@
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="140" t="s">
+      <c r="J43" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="129" t="s">
+      <c r="P43" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="129"/>
-      <c r="R43" s="129"/>
+      <c r="Q43" s="143"/>
+      <c r="R43" s="143"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
@@ -4861,11 +4861,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="119" t="s">
+      <c r="P44" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="119"/>
-      <c r="R44" s="119"/>
+      <c r="Q44" s="125"/>
+      <c r="R44" s="125"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
@@ -5043,15 +5043,15 @@
       <c r="G48" s="112" t="s">
         <v>220</v>
       </c>
-      <c r="I48" s="123" t="s">
+      <c r="I48" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="124"/>
-      <c r="K48" s="125" t="s">
+      <c r="J48" s="138"/>
+      <c r="K48" s="139" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="126"/>
-      <c r="M48" s="127"/>
+      <c r="L48" s="140"/>
+      <c r="M48" s="141"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5160,14 +5160,14 @@
       <c r="G51" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I51" s="120" t="s">
+      <c r="I51" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J51" s="121"/>
-      <c r="K51" s="120" t="s">
+      <c r="K51" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="122"/>
+      <c r="L51" s="120"/>
       <c r="M51" s="121"/>
       <c r="O51" s="83">
         <v>6</v>
@@ -5205,15 +5205,15 @@
       <c r="G52" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I52" s="130" t="s">
+      <c r="I52" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="131"/>
-      <c r="K52" s="132" t="s">
+      <c r="J52" s="129"/>
+      <c r="K52" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="133"/>
-      <c r="M52" s="134"/>
+      <c r="L52" s="131"/>
+      <c r="M52" s="132"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5250,15 +5250,15 @@
       <c r="G53" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="I53" s="130" t="s">
+      <c r="I53" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="131"/>
-      <c r="K53" s="132" t="s">
+      <c r="J53" s="129"/>
+      <c r="K53" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="133"/>
-      <c r="M53" s="134"/>
+      <c r="L53" s="131"/>
+      <c r="M53" s="132"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5295,15 +5295,15 @@
       <c r="G54" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="I54" s="136" t="s">
+      <c r="I54" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="137"/>
-      <c r="K54" s="138" t="s">
+      <c r="J54" s="123"/>
+      <c r="K54" s="124" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="119"/>
-      <c r="M54" s="139"/>
+      <c r="L54" s="125"/>
+      <c r="M54" s="126"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5343,11 +5343,11 @@
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="128" t="s">
+      <c r="J55" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K55" s="128"/>
-      <c r="L55" s="128"/>
+      <c r="K55" s="127"/>
+      <c r="L55" s="127"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5390,23 +5390,23 @@
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="129" t="s">
+      <c r="J56" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="129"/>
-      <c r="L56" s="129"/>
+      <c r="K56" s="143"/>
+      <c r="L56" s="143"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="123" t="s">
+      <c r="O56" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="124"/>
-      <c r="Q56" s="125" t="s">
+      <c r="P56" s="138"/>
+      <c r="Q56" s="139" t="s">
         <v>237</v>
       </c>
-      <c r="R56" s="126"/>
-      <c r="S56" s="127"/>
+      <c r="R56" s="140"/>
+      <c r="S56" s="141"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5431,11 +5431,11 @@
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="119" t="s">
+      <c r="J57" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="119"/>
-      <c r="L57" s="119"/>
+      <c r="K57" s="125"/>
+      <c r="L57" s="125"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
@@ -5475,14 +5475,14 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="120" t="s">
+      <c r="O58" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P58" s="121"/>
-      <c r="Q58" s="120" t="s">
+      <c r="Q58" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="122"/>
+      <c r="R58" s="120"/>
       <c r="S58" s="121"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
@@ -5520,15 +5520,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="130" t="s">
+      <c r="O59" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="131"/>
-      <c r="Q59" s="132" t="s">
+      <c r="P59" s="129"/>
+      <c r="Q59" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="R59" s="133"/>
-      <c r="S59" s="134"/>
+      <c r="R59" s="131"/>
+      <c r="S59" s="132"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5565,15 +5565,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="130" t="s">
+      <c r="O60" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="131"/>
-      <c r="Q60" s="130" t="s">
+      <c r="P60" s="129"/>
+      <c r="Q60" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="135"/>
-      <c r="S60" s="131"/>
+      <c r="R60" s="142"/>
+      <c r="S60" s="129"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5610,15 +5610,15 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="136" t="s">
+      <c r="O61" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="137"/>
-      <c r="Q61" s="138" t="s">
+      <c r="P61" s="123"/>
+      <c r="Q61" s="124" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="119"/>
-      <c r="S61" s="139"/>
+      <c r="R61" s="125"/>
+      <c r="S61" s="126"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5658,11 +5658,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="128" t="s">
+      <c r="P62" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="128"/>
-      <c r="R62" s="128"/>
+      <c r="Q62" s="127"/>
+      <c r="R62" s="127"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5705,11 +5705,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="129" t="s">
+      <c r="P63" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="129"/>
-      <c r="R63" s="129"/>
+      <c r="Q63" s="143"/>
+      <c r="R63" s="143"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
@@ -5752,11 +5752,11 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="119" t="s">
+      <c r="P64" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="119"/>
-      <c r="R64" s="119"/>
+      <c r="Q64" s="125"/>
+      <c r="R64" s="125"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
@@ -6138,24 +6138,24 @@
       <c r="G72" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I72" s="123" t="s">
+      <c r="I72" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="124"/>
-      <c r="K72" s="125" t="s">
+      <c r="J72" s="138"/>
+      <c r="K72" s="139" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="126"/>
-      <c r="M72" s="127"/>
-      <c r="O72" s="123" t="s">
+      <c r="L72" s="140"/>
+      <c r="M72" s="141"/>
+      <c r="O72" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P72" s="124"/>
-      <c r="Q72" s="125" t="s">
+      <c r="P72" s="138"/>
+      <c r="Q72" s="139" t="s">
         <v>238</v>
       </c>
-      <c r="R72" s="126"/>
-      <c r="S72" s="127"/>
+      <c r="R72" s="140"/>
+      <c r="S72" s="141"/>
     </row>
     <row r="73" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
@@ -6582,20 +6582,20 @@
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C93" s="104" t="s">
-        <v>249</v>
-      </c>
-      <c r="D93" s="105">
-        <v>1</v>
-      </c>
-      <c r="E93" s="105" t="s">
+      <c r="C93" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D93" s="1">
+        <v>2</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F93" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G93" s="107" t="s">
-        <v>251</v>
+      <c r="F93" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
@@ -6603,167 +6603,167 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D94" s="1">
+      <c r="C94" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="D94" s="105">
         <v>1</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E94" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F94" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" s="107" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="33">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C95" s="104" t="s">
-        <v>250</v>
-      </c>
-      <c r="D95" s="105">
+      <c r="C95" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D95" s="1">
         <v>1</v>
       </c>
-      <c r="E95" s="105" t="s">
+      <c r="E95" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F95" s="108" t="s">
-        <v>73</v>
-      </c>
-      <c r="G95" s="107" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F95" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B96" s="33">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="112" t="s">
-        <v>259</v>
-      </c>
-      <c r="D96" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="E96" s="111" t="s">
+      <c r="C96" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="D96" s="105">
+        <v>1</v>
+      </c>
+      <c r="E96" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="118" t="s">
-        <v>331</v>
-      </c>
-      <c r="G96" s="112" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F96" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="G96" s="107" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="33">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>323</v>
+        <v>403</v>
       </c>
       <c r="D97" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E97" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F97" s="103" t="s">
-        <v>335</v>
+      <c r="F97" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="33">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D98" s="1">
-        <v>1</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="C98" s="112" t="s">
+        <v>259</v>
+      </c>
+      <c r="D98" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" s="111" t="s">
         <v>237</v>
       </c>
-      <c r="F98" s="103" t="s">
-        <v>329</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F98" s="118" t="s">
+        <v>331</v>
+      </c>
+      <c r="G98" s="112" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B99" s="33">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C99" s="104" t="s">
-        <v>351</v>
-      </c>
-      <c r="D99" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E99" s="117" t="s">
-        <v>331</v>
-      </c>
-      <c r="F99" s="106" t="s">
-        <v>17</v>
-      </c>
-      <c r="G99" s="107" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C99" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D99" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F99" s="103" t="s">
+        <v>335</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B100" s="33">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D100" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>331</v>
+      <c r="F100" s="103" t="s">
+        <v>329</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" s="33">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D101" s="90" t="s">
+      <c r="C101" s="104" t="s">
+        <v>351</v>
+      </c>
+      <c r="D101" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F101" s="103" t="s">
-        <v>371</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>272</v>
+      <c r="E101" s="117" t="s">
+        <v>331</v>
+      </c>
+      <c r="F101" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="107" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -6772,40 +6772,40 @@
         <v>85</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D102" s="1">
-        <v>1</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>80</v>
+        <v>363</v>
+      </c>
+      <c r="D102" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B103" s="33">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="D103" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>62</v>
+        <v>238</v>
+      </c>
+      <c r="F103" s="103" t="s">
+        <v>371</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6814,19 +6814,19 @@
         <v>87</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D104" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E104" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D104" s="1">
+        <v>2</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F104" s="103" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>312</v>
+        <v>398</v>
       </c>
     </row>
     <row r="105" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6856,40 +6856,40 @@
         <v>89</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>395</v>
+        <v>267</v>
       </c>
       <c r="D106" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" s="33">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D107" s="1">
-        <v>2</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F107" s="103" t="s">
-        <v>406</v>
+        <v>288</v>
+      </c>
+      <c r="D107" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>398</v>
+        <v>289</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
@@ -6898,19 +6898,19 @@
         <v>91</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D108" s="90" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>401</v>
+        <v>238</v>
       </c>
       <c r="F108" s="103" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
@@ -6919,40 +6919,40 @@
         <v>92</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D109" s="90" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>238</v>
+        <v>401</v>
+      </c>
+      <c r="F109" s="103" t="s">
+        <v>62</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B110" s="33">
         <f>IF(C110="","",B109+1)</f>
         <v>93</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>404</v>
+        <v>311</v>
       </c>
       <c r="D110" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E110" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>238</v>
       </c>
       <c r="F110" s="103" t="s">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>409</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
@@ -7142,39 +7142,51 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="K72:M72"/>
     <mergeCell ref="J57:L57"/>
@@ -7199,51 +7211,39 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:M40"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="Q59:S59"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54974AFD-0562-4AE2-B869-771DCA299A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F2A8C6-3745-48F0-9CAF-2E05DA71981D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="정리용" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$17:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$17:$G$140</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="413">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1712,6 +1712,21 @@
   </si>
   <si>
     <t>PC ADDR (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_control_unit
+u_id_ex_bridge
+u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_negative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Negative Out</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2695,13 +2710,55 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2713,28 +2770,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2744,30 +2783,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3130,31 +3145,31 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="133" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135"/>
-      <c r="I2" s="119" t="s">
+      <c r="B2" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="143"/>
+      <c r="I2" s="120" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="121"/>
-      <c r="K2" s="119" t="s">
+      <c r="K2" s="120" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="120"/>
+      <c r="L2" s="122"/>
       <c r="M2" s="121"/>
-      <c r="O2" s="119" t="s">
+      <c r="O2" s="120" t="s">
         <v>102</v>
       </c>
       <c r="P2" s="121"/>
-      <c r="Q2" s="119" t="s">
+      <c r="Q2" s="120" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="120"/>
+      <c r="R2" s="122"/>
       <c r="S2" s="121"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3176,24 +3191,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="128" t="s">
+      <c r="I3" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="130" t="s">
+      <c r="J3" s="131"/>
+      <c r="K3" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="131"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="128" t="s">
+      <c r="L3" s="133"/>
+      <c r="M3" s="134"/>
+      <c r="O3" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="130" t="s">
+      <c r="P3" s="131"/>
+      <c r="Q3" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R3" s="131"/>
-      <c r="S3" s="132"/>
+      <c r="R3" s="133"/>
+      <c r="S3" s="134"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3214,24 +3229,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="128" t="s">
+      <c r="I4" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="129"/>
-      <c r="K4" s="128" t="s">
+      <c r="J4" s="131"/>
+      <c r="K4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="142"/>
-      <c r="M4" s="129"/>
-      <c r="O4" s="128" t="s">
+      <c r="L4" s="135"/>
+      <c r="M4" s="131"/>
+      <c r="O4" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="128" t="s">
+      <c r="P4" s="131"/>
+      <c r="Q4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="142"/>
-      <c r="S4" s="129"/>
+      <c r="R4" s="135"/>
+      <c r="S4" s="131"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3252,24 +3267,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="122" t="s">
+      <c r="I5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="123"/>
-      <c r="K5" s="124" t="s">
+      <c r="J5" s="137"/>
+      <c r="K5" s="138" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="125"/>
-      <c r="M5" s="126"/>
-      <c r="O5" s="122" t="s">
+      <c r="L5" s="119"/>
+      <c r="M5" s="139"/>
+      <c r="O5" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="124" t="s">
+      <c r="P5" s="137"/>
+      <c r="Q5" s="138" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="125"/>
-      <c r="S5" s="126"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="139"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3293,22 +3308,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="127" t="s">
+      <c r="J6" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="128"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="127" t="s">
+      <c r="P6" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="127"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="128"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3335,22 +3350,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="136" t="s">
+      <c r="J7" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="143" t="s">
+      <c r="P7" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="143"/>
-      <c r="R7" s="143"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
@@ -3392,11 +3407,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="125" t="s">
+      <c r="P8" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
@@ -3570,15 +3585,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="137" t="s">
+      <c r="I12" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="138"/>
-      <c r="K12" s="139" t="s">
+      <c r="J12" s="124"/>
+      <c r="K12" s="125" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="140"/>
-      <c r="M12" s="141"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="127"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3701,15 +3716,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="137" t="s">
+      <c r="O16" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="139" t="s">
+      <c r="P16" s="124"/>
+      <c r="Q16" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="R16" s="140"/>
-      <c r="S16" s="141"/>
+      <c r="R16" s="126"/>
+      <c r="S16" s="127"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3751,23 +3766,23 @@
       <c r="G18" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="119" t="s">
+      <c r="I18" s="120" t="s">
         <v>102</v>
       </c>
       <c r="J18" s="121"/>
-      <c r="K18" s="119" t="s">
+      <c r="K18" s="120" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="120"/>
+      <c r="L18" s="122"/>
       <c r="M18" s="121"/>
-      <c r="O18" s="119" t="s">
+      <c r="O18" s="120" t="s">
         <v>102</v>
       </c>
       <c r="P18" s="121"/>
-      <c r="Q18" s="119" t="s">
+      <c r="Q18" s="120" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="120"/>
+      <c r="R18" s="122"/>
       <c r="S18" s="121"/>
     </row>
     <row r="19" spans="2:19" ht="33" x14ac:dyDescent="0.3">
@@ -3790,24 +3805,24 @@
       <c r="G19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="128" t="s">
+      <c r="I19" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="129"/>
-      <c r="K19" s="130" t="s">
+      <c r="J19" s="131"/>
+      <c r="K19" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="131"/>
-      <c r="M19" s="132"/>
-      <c r="O19" s="128" t="s">
+      <c r="L19" s="133"/>
+      <c r="M19" s="134"/>
+      <c r="O19" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="129"/>
-      <c r="Q19" s="130" t="s">
+      <c r="P19" s="131"/>
+      <c r="Q19" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R19" s="131"/>
-      <c r="S19" s="132"/>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3829,24 +3844,24 @@
       <c r="G20" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="I20" s="128" t="s">
+      <c r="I20" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="129"/>
-      <c r="K20" s="130" t="s">
+      <c r="J20" s="131"/>
+      <c r="K20" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="131"/>
-      <c r="M20" s="132"/>
-      <c r="O20" s="128" t="s">
+      <c r="L20" s="133"/>
+      <c r="M20" s="134"/>
+      <c r="O20" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="128" t="s">
+      <c r="P20" s="131"/>
+      <c r="Q20" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="142"/>
-      <c r="S20" s="129"/>
+      <c r="R20" s="135"/>
+      <c r="S20" s="131"/>
     </row>
     <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
@@ -3868,107 +3883,107 @@
       <c r="G21" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="I21" s="122" t="s">
+      <c r="I21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="123"/>
-      <c r="K21" s="124" t="s">
+      <c r="J21" s="137"/>
+      <c r="K21" s="138" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="125"/>
-      <c r="M21" s="126"/>
-      <c r="O21" s="122" t="s">
+      <c r="L21" s="119"/>
+      <c r="M21" s="139"/>
+      <c r="O21" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="124" t="s">
+      <c r="P21" s="137"/>
+      <c r="Q21" s="138" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="125"/>
-      <c r="S21" s="126"/>
-    </row>
-    <row r="22" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R21" s="119"/>
+      <c r="S21" s="139"/>
+    </row>
+    <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D22" s="90" t="s">
-        <v>20</v>
+        <v>411</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="103" t="s">
-        <v>368</v>
+      <c r="F22" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>257</v>
+        <v>412</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="127" t="s">
+      <c r="J22" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="127" t="s">
+      <c r="P22" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q22" s="127"/>
-      <c r="R22" s="127"/>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="128"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="33">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="D23" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>297</v>
+      <c r="F23" s="103" t="s">
+        <v>368</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>84</v>
+        <v>257</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="136" t="s">
+      <c r="J23" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="136"/>
-      <c r="L23" s="136"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="143" t="s">
+      <c r="P23" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="143"/>
-      <c r="R23" s="143"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="129"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
@@ -3979,19 +3994,19 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>243</v>
+        <v>292</v>
       </c>
       <c r="D24" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>297</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
@@ -4011,34 +4026,34 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="125" t="s">
+      <c r="P24" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="125"/>
-      <c r="R24" s="125"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="119"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="33">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D25" s="90" t="s">
-        <v>20</v>
+        <v>243</v>
+      </c>
+      <c r="D25" s="1">
+        <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="103" t="s">
-        <v>75</v>
+        <v>236</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
@@ -4071,25 +4086,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B26" s="33">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
+      </c>
+      <c r="D26" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="103" t="s">
+        <v>75</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
@@ -4128,19 +4143,19 @@
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D27" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>40</v>
+        <v>261</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>53</v>
+        <v>297</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
@@ -4179,19 +4194,19 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G28" s="5" t="s">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
@@ -4230,19 +4245,19 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
+        <v>295</v>
+      </c>
+      <c r="D29" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>226</v>
+        <v>88</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
@@ -4275,25 +4290,25 @@
         <v>168</v>
       </c>
     </row>
-    <row r="30" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30" s="33">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
-      <c r="E30" s="102" t="s">
-        <v>296</v>
-      </c>
-      <c r="F30" s="103" t="s">
-        <v>383</v>
+      <c r="E30" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
@@ -4332,19 +4347,19 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="D31" s="1">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>236</v>
+        <v>1</v>
+      </c>
+      <c r="E31" s="102" t="s">
+        <v>296</v>
       </c>
       <c r="F31" s="103" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
@@ -4377,35 +4392,35 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="33">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>236</v>
       </c>
       <c r="F32" s="103" t="s">
-        <v>63</v>
+        <v>384</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I32" s="137" t="s">
+        <v>264</v>
+      </c>
+      <c r="I32" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="138"/>
-      <c r="K32" s="139" t="s">
+      <c r="J32" s="124"/>
+      <c r="K32" s="125" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="140"/>
-      <c r="M32" s="141"/>
+      <c r="L32" s="126"/>
+      <c r="M32" s="127"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4428,19 +4443,19 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>241</v>
+        <v>309</v>
       </c>
       <c r="D33" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>65</v>
+        <v>236</v>
+      </c>
+      <c r="F33" s="103" t="s">
+        <v>63</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
@@ -4464,19 +4479,19 @@
         <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D34" s="90" t="s">
-        <v>56</v>
+        <v>241</v>
+      </c>
+      <c r="D34" s="1">
+        <v>6</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F34" s="103" t="s">
-        <v>63</v>
+        <v>233</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
@@ -4500,7 +4515,7 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="D35" s="90" t="s">
         <v>56</v>
@@ -4509,10 +4524,10 @@
         <v>236</v>
       </c>
       <c r="F35" s="103" t="s">
-        <v>341</v>
+        <v>63</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
@@ -4530,13 +4545,13 @@
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="33">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="D36" s="90" t="s">
         <v>56</v>
@@ -4545,20 +4560,20 @@
         <v>236</v>
       </c>
       <c r="F36" s="103" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="O36" s="137" t="s">
+        <v>321</v>
+      </c>
+      <c r="O36" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="138"/>
-      <c r="Q36" s="139" t="s">
+      <c r="P36" s="124"/>
+      <c r="Q36" s="125" t="s">
         <v>236</v>
       </c>
-      <c r="R36" s="140"/>
-      <c r="S36" s="141"/>
+      <c r="R36" s="126"/>
+      <c r="S36" s="127"/>
     </row>
     <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4566,98 +4581,98 @@
         <v>20</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D37" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F37" s="103" t="s">
+        <v>336</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B38" s="33">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="102" t="s">
-        <v>377</v>
-      </c>
-      <c r="F37" s="103" t="s">
-        <v>392</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B38" s="33">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="102" t="s">
+        <v>377</v>
+      </c>
+      <c r="F38" s="103" t="s">
+        <v>392</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="I38" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="J38" s="121"/>
+      <c r="K38" s="120" t="s">
+        <v>122</v>
+      </c>
+      <c r="L38" s="122"/>
+      <c r="M38" s="121"/>
+      <c r="O38" s="120" t="s">
+        <v>102</v>
+      </c>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="120" t="s">
+        <v>173</v>
+      </c>
+      <c r="R38" s="122"/>
+      <c r="S38" s="121"/>
+    </row>
+    <row r="39" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B39" s="33">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="102" t="s">
         <v>344</v>
       </c>
-      <c r="F38" s="103" t="s">
+      <c r="F39" s="103" t="s">
         <v>369</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="I38" s="119" t="s">
-        <v>102</v>
-      </c>
-      <c r="J38" s="121"/>
-      <c r="K38" s="119" t="s">
-        <v>122</v>
-      </c>
-      <c r="L38" s="120"/>
-      <c r="M38" s="121"/>
-      <c r="O38" s="119" t="s">
-        <v>102</v>
-      </c>
-      <c r="P38" s="121"/>
-      <c r="Q38" s="119" t="s">
-        <v>173</v>
-      </c>
-      <c r="R38" s="120"/>
-      <c r="S38" s="121"/>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B39" s="33">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D39" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I39" s="128" t="s">
+      <c r="I39" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J39" s="129"/>
-      <c r="K39" s="130" t="s">
+      <c r="J39" s="131"/>
+      <c r="K39" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="131"/>
-      <c r="M39" s="132"/>
-      <c r="O39" s="128" t="s">
+      <c r="L39" s="133"/>
+      <c r="M39" s="134"/>
+      <c r="O39" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P39" s="129"/>
-      <c r="Q39" s="130" t="s">
+      <c r="P39" s="131"/>
+      <c r="Q39" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R39" s="131"/>
-      <c r="S39" s="132"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="134"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
@@ -4665,183 +4680,183 @@
         <v>23</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D40" s="101" t="s">
+        <v>293</v>
+      </c>
+      <c r="D40" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="102" t="s">
-        <v>233</v>
+      <c r="E40" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I40" s="128" t="s">
+        <v>86</v>
+      </c>
+      <c r="I40" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J40" s="129"/>
-      <c r="K40" s="130" t="s">
+      <c r="J40" s="131"/>
+      <c r="K40" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L40" s="131"/>
-      <c r="M40" s="132"/>
-      <c r="O40" s="128" t="s">
+      <c r="L40" s="133"/>
+      <c r="M40" s="134"/>
+      <c r="O40" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P40" s="129"/>
-      <c r="Q40" s="128" t="s">
+      <c r="P40" s="131"/>
+      <c r="Q40" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="142"/>
-      <c r="S40" s="129"/>
+      <c r="R40" s="135"/>
+      <c r="S40" s="131"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C41" s="97" t="s">
-        <v>273</v>
-      </c>
-      <c r="D41" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="33" t="s">
+      <c r="C41" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="102" t="s">
+        <v>233</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F41" s="98" t="s">
-        <v>326</v>
-      </c>
-      <c r="G41" s="99" t="s">
-        <v>274</v>
-      </c>
-      <c r="I41" s="122" t="s">
+      <c r="G41" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="I41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="123"/>
-      <c r="K41" s="124" t="s">
+      <c r="J41" s="137"/>
+      <c r="K41" s="138" t="s">
         <v>125</v>
       </c>
-      <c r="L41" s="125"/>
-      <c r="M41" s="126"/>
-      <c r="O41" s="122" t="s">
+      <c r="L41" s="119"/>
+      <c r="M41" s="139"/>
+      <c r="O41" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="123"/>
-      <c r="Q41" s="124" t="s">
+      <c r="P41" s="137"/>
+      <c r="Q41" s="138" t="s">
         <v>174</v>
       </c>
-      <c r="R41" s="125"/>
-      <c r="S41" s="126"/>
+      <c r="R41" s="119"/>
+      <c r="S41" s="139"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>294</v>
+      <c r="C42" s="97" t="s">
+        <v>273</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>87</v>
+        <v>21</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="98" t="s">
+        <v>326</v>
+      </c>
+      <c r="G42" s="99" t="s">
+        <v>274</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="127" t="s">
+      <c r="J42" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K42" s="127"/>
-      <c r="L42" s="127"/>
+      <c r="K42" s="128"/>
+      <c r="L42" s="128"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="127" t="s">
+      <c r="P42" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q42" s="127"/>
-      <c r="R42" s="127"/>
+      <c r="Q42" s="128"/>
+      <c r="R42" s="128"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="33">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="114" t="s">
-        <v>236</v>
-      </c>
-      <c r="F43" s="98" t="s">
-        <v>386</v>
+        <v>294</v>
+      </c>
+      <c r="D43" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="136" t="s">
+      <c r="J43" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="136"/>
-      <c r="L43" s="136"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="140"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="143" t="s">
+      <c r="P43" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="143"/>
-      <c r="R43" s="143"/>
+      <c r="Q43" s="129"/>
+      <c r="R43" s="129"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="33">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="114" t="s">
         <v>236</v>
       </c>
-      <c r="F44" s="103" t="s">
-        <v>237</v>
+      <c r="F44" s="98" t="s">
+        <v>386</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
@@ -4861,11 +4876,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="125" t="s">
+      <c r="P44" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="125"/>
-      <c r="R44" s="125"/>
+      <c r="Q44" s="119"/>
+      <c r="R44" s="119"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
@@ -4876,19 +4891,19 @@
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
       </c>
-      <c r="E45" s="114" t="s">
+      <c r="E45" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F45" s="114" t="s">
+      <c r="F45" s="103" t="s">
         <v>237</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
@@ -4921,25 +4936,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B46" s="33">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D46" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F46" s="103" t="s">
-        <v>254</v>
-      </c>
-      <c r="G46" s="99" t="s">
-        <v>194</v>
+        <v>246</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="114" t="s">
+        <v>236</v>
+      </c>
+      <c r="F46" s="114" t="s">
+        <v>237</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
@@ -4978,19 +4993,19 @@
         <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>217</v>
+        <v>382</v>
       </c>
       <c r="D47" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>233</v>
       </c>
       <c r="F47" s="103" t="s">
-        <v>394</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>219</v>
+        <v>254</v>
+      </c>
+      <c r="G47" s="99" t="s">
+        <v>194</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
@@ -5023,35 +5038,35 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C48" s="112" t="s">
-        <v>218</v>
-      </c>
-      <c r="D48" s="113" t="s">
+      <c r="C48" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D48" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="111" t="s">
+      <c r="E48" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="115" t="s">
-        <v>370</v>
-      </c>
-      <c r="G48" s="112" t="s">
-        <v>220</v>
-      </c>
-      <c r="I48" s="137" t="s">
+      <c r="F48" s="103" t="s">
+        <v>394</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="I48" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="138"/>
-      <c r="K48" s="139" t="s">
+      <c r="J48" s="124"/>
+      <c r="K48" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="140"/>
-      <c r="M48" s="141"/>
+      <c r="L48" s="126"/>
+      <c r="M48" s="127"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5068,25 +5083,25 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B49" s="33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D49" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F49" s="103" t="s">
-        <v>386</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>334</v>
+      <c r="C49" s="112" t="s">
+        <v>218</v>
+      </c>
+      <c r="D49" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="111" t="s">
+        <v>233</v>
+      </c>
+      <c r="F49" s="115" t="s">
+        <v>370</v>
+      </c>
+      <c r="G49" s="112" t="s">
+        <v>220</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
@@ -5104,25 +5119,25 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="116">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>236</v>
+        <v>333</v>
+      </c>
+      <c r="D50" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="F50" s="103" t="s">
-        <v>237</v>
+        <v>386</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
@@ -5146,28 +5161,28 @@
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D51" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>279</v>
+        <v>298</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F51" s="103" t="s">
+        <v>237</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="I51" s="119" t="s">
+        <v>299</v>
+      </c>
+      <c r="I51" s="120" t="s">
         <v>102</v>
       </c>
       <c r="J51" s="121"/>
-      <c r="K51" s="119" t="s">
+      <c r="K51" s="120" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="120"/>
+      <c r="L51" s="122"/>
       <c r="M51" s="121"/>
       <c r="O51" s="83">
         <v>6</v>
@@ -5191,29 +5206,29 @@
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D52" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D52" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G52" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I52" s="128" t="s">
+        <v>54</v>
+      </c>
+      <c r="I52" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="129"/>
-      <c r="K52" s="130" t="s">
+      <c r="J52" s="131"/>
+      <c r="K52" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="131"/>
-      <c r="M52" s="132"/>
+      <c r="L52" s="133"/>
+      <c r="M52" s="134"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5230,35 +5245,35 @@
         <v>182</v>
       </c>
     </row>
-    <row r="53" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B53" s="33">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>221</v>
+        <v>279</v>
       </c>
       <c r="D53" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F53" s="103" t="s">
-        <v>48</v>
+        <v>278</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I53" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="I53" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="129"/>
-      <c r="K53" s="130" t="s">
+      <c r="J53" s="131"/>
+      <c r="K53" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="131"/>
-      <c r="M53" s="132"/>
+      <c r="L53" s="133"/>
+      <c r="M53" s="134"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5275,35 +5290,35 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="33">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>372</v>
+        <v>221</v>
       </c>
       <c r="D54" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
+      </c>
+      <c r="F54" s="103" t="s">
+        <v>48</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="I54" s="122" t="s">
+        <v>223</v>
+      </c>
+      <c r="I54" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="123"/>
-      <c r="K54" s="124" t="s">
+      <c r="J54" s="137"/>
+      <c r="K54" s="138" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="125"/>
-      <c r="M54" s="126"/>
+      <c r="L54" s="119"/>
+      <c r="M54" s="139"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5326,28 +5341,28 @@
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
+      </c>
+      <c r="D55" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="127" t="s">
+      <c r="J55" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="K55" s="127"/>
-      <c r="L55" s="127"/>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5373,7 +5388,7 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -5385,28 +5400,28 @@
         <v>365</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="143" t="s">
+      <c r="J56" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="143"/>
-      <c r="L56" s="143"/>
+      <c r="K56" s="129"/>
+      <c r="L56" s="129"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="137" t="s">
+      <c r="O56" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="138"/>
-      <c r="Q56" s="139" t="s">
+      <c r="P56" s="124"/>
+      <c r="Q56" s="125" t="s">
         <v>237</v>
       </c>
-      <c r="R56" s="140"/>
-      <c r="S56" s="141"/>
+      <c r="R56" s="126"/>
+      <c r="S56" s="127"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5414,7 +5429,7 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
@@ -5423,19 +5438,19 @@
         <v>364</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="125" t="s">
+      <c r="J57" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="125"/>
-      <c r="L57" s="125"/>
+      <c r="K57" s="119"/>
+      <c r="L57" s="119"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
@@ -5446,7 +5461,7 @@
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
@@ -5458,7 +5473,7 @@
         <v>366</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
@@ -5475,14 +5490,14 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="119" t="s">
+      <c r="O58" s="120" t="s">
         <v>102</v>
       </c>
       <c r="P58" s="121"/>
-      <c r="Q58" s="119" t="s">
+      <c r="Q58" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="120"/>
+      <c r="R58" s="122"/>
       <c r="S58" s="121"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
@@ -5491,19 +5506,19 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="D59" s="33">
+        <v>349</v>
+      </c>
+      <c r="D59" s="1">
         <v>1</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>344</v>
+      <c r="E59" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
@@ -5520,15 +5535,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="128" t="s">
+      <c r="O59" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="129"/>
-      <c r="Q59" s="130" t="s">
+      <c r="P59" s="131"/>
+      <c r="Q59" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R59" s="131"/>
-      <c r="S59" s="132"/>
+      <c r="R59" s="133"/>
+      <c r="S59" s="134"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5536,19 +5551,19 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D60" s="90" t="s">
-        <v>20</v>
+        <v>350</v>
+      </c>
+      <c r="D60" s="33">
+        <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>234</v>
+        <v>344</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>44</v>
+        <v>331</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>193</v>
+        <v>360</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
@@ -5565,15 +5580,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="128" t="s">
+      <c r="O60" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="129"/>
-      <c r="Q60" s="128" t="s">
+      <c r="P60" s="131"/>
+      <c r="Q60" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="142"/>
-      <c r="S60" s="129"/>
+      <c r="R60" s="135"/>
+      <c r="S60" s="131"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5581,19 +5596,19 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D61" s="1">
-        <v>3</v>
+        <v>192</v>
+      </c>
+      <c r="D61" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>236</v>
+        <v>44</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
@@ -5610,15 +5625,15 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="122" t="s">
+      <c r="O61" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="123"/>
-      <c r="Q61" s="124" t="s">
+      <c r="P61" s="137"/>
+      <c r="Q61" s="138" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="125"/>
-      <c r="S61" s="126"/>
+      <c r="R61" s="119"/>
+      <c r="S61" s="139"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5626,10 +5641,10 @@
         <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D62" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>58</v>
@@ -5638,7 +5653,7 @@
         <v>236</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
@@ -5658,11 +5673,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="127" t="s">
+      <c r="P62" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="127"/>
-      <c r="R62" s="127"/>
+      <c r="Q62" s="128"/>
+      <c r="R62" s="128"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5673,19 +5688,19 @@
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D63" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
@@ -5705,11 +5720,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="143" t="s">
+      <c r="P63" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="143"/>
-      <c r="R63" s="143"/>
+      <c r="Q63" s="129"/>
+      <c r="R63" s="129"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
@@ -5720,19 +5735,19 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D64" s="90" t="s">
-        <v>57</v>
+        <v>196</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
@@ -5752,34 +5767,34 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="125" t="s">
+      <c r="P64" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="125"/>
-      <c r="R64" s="125"/>
+      <c r="Q64" s="119"/>
+      <c r="R64" s="119"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="33">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D65" s="1">
-        <v>6</v>
+        <v>286</v>
+      </c>
+      <c r="D65" s="90" t="s">
+        <v>57</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="103" t="s">
-        <v>393</v>
+      <c r="F65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>240</v>
+        <v>61</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
@@ -5817,20 +5832,20 @@
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="C66" s="97" t="s">
-        <v>275</v>
-      </c>
-      <c r="D66" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E66" s="33" t="s">
+      <c r="C66" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D66" s="1">
+        <v>6</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F66" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="99" t="s">
-        <v>50</v>
+      <c r="F66" s="103" t="s">
+        <v>393</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
@@ -5863,25 +5878,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B67" s="33">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D67" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="C67" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="D67" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>59</v>
+      <c r="F67" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="99" t="s">
+        <v>50</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
@@ -5920,19 +5935,19 @@
         <v>51</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D68" s="90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
@@ -5965,13 +5980,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B69" s="33">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D69" s="90" t="s">
         <v>56</v>
@@ -5979,11 +5994,11 @@
       <c r="E69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F69" s="103" t="s">
-        <v>387</v>
+      <c r="F69" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
@@ -6022,7 +6037,7 @@
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D70" s="90" t="s">
         <v>56</v>
@@ -6034,7 +6049,7 @@
         <v>387</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
@@ -6067,25 +6082,25 @@
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="33">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D71" s="1">
-        <v>5</v>
+        <v>283</v>
+      </c>
+      <c r="D71" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>64</v>
+      <c r="F71" s="103" t="s">
+        <v>410</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>60</v>
+        <v>303</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
@@ -6124,79 +6139,79 @@
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D72" s="1">
+        <v>5</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I72" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="J72" s="124"/>
+      <c r="K72" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="L72" s="126"/>
+      <c r="M72" s="127"/>
+      <c r="O72" s="123" t="s">
+        <v>104</v>
+      </c>
+      <c r="P72" s="124"/>
+      <c r="Q72" s="125" t="s">
+        <v>238</v>
+      </c>
+      <c r="R72" s="126"/>
+      <c r="S72" s="127"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B73" s="33">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D73" s="1">
         <v>2</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I72" s="137" t="s">
-        <v>104</v>
-      </c>
-      <c r="J72" s="138"/>
-      <c r="K72" s="139" t="s">
-        <v>58</v>
-      </c>
-      <c r="L72" s="140"/>
-      <c r="M72" s="141"/>
-      <c r="O72" s="137" t="s">
-        <v>104</v>
-      </c>
-      <c r="P72" s="138"/>
-      <c r="Q72" s="139" t="s">
-        <v>238</v>
-      </c>
-      <c r="R72" s="140"/>
-      <c r="S72" s="141"/>
-    </row>
-    <row r="73" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B73" s="33">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D73" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" s="102" t="s">
-        <v>380</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>236</v>
       </c>
       <c r="G73" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B74" s="33">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D74" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" s="102" t="s">
+        <v>380</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B74" s="33">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D74" s="1">
-        <v>1</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F74" s="114" t="s">
-        <v>236</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="75" spans="2:19" x14ac:dyDescent="0.3">
@@ -6205,7 +6220,7 @@
         <v>58</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -6213,11 +6228,11 @@
       <c r="E75" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>233</v>
+      <c r="F75" s="114" t="s">
+        <v>236</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
@@ -6226,7 +6241,7 @@
         <v>59</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -6234,53 +6249,53 @@
       <c r="E76" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F76" s="114" t="s">
+      <c r="F76" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B77" s="33">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F77" s="114" t="s">
         <v>236</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="77" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B77" s="33">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="C77" s="3" t="s">
+    <row r="78" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B78" s="33">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D77" s="90" t="s">
+      <c r="D78" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F77" s="103" t="s">
+      <c r="F78" s="103" t="s">
         <v>253</v>
       </c>
-      <c r="G77" s="99" t="s">
+      <c r="G78" s="99" t="s">
         <v>407</v>
-      </c>
-    </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B78" s="33">
-        <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D78" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F78" s="111" t="s">
-        <v>233</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.3">
@@ -6288,10 +6303,10 @@
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C79" s="112" t="s">
-        <v>204</v>
-      </c>
-      <c r="D79" s="113" t="s">
+      <c r="C79" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D79" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
@@ -6300,8 +6315,8 @@
       <c r="F79" s="111" t="s">
         <v>233</v>
       </c>
-      <c r="G79" s="112" t="s">
-        <v>206</v>
+      <c r="G79" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6309,20 +6324,20 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D80" s="1">
-        <v>1</v>
+      <c r="C80" s="112" t="s">
+        <v>204</v>
+      </c>
+      <c r="D80" s="113" t="s">
+        <v>20</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>208</v>
+        <v>62</v>
+      </c>
+      <c r="F80" s="111" t="s">
+        <v>233</v>
+      </c>
+      <c r="G80" s="112" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
@@ -6331,7 +6346,7 @@
         <v>64</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>198</v>
+        <v>337</v>
       </c>
       <c r="D81" s="1">
         <v>1</v>
@@ -6339,53 +6354,53 @@
       <c r="E81" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F81" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G81" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B82" s="33">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G82" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B82" s="33">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D82" s="101" t="s">
-        <v>46</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B83" s="33">
         <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
         <v>66</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D83" s="1">
-        <v>1</v>
+        <v>277</v>
+      </c>
+      <c r="D83" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>216</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -6394,19 +6409,19 @@
         <v>67</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D84" s="90" t="s">
-        <v>20</v>
+        <v>202</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F84" s="103" t="s">
-        <v>233</v>
-      </c>
       <c r="G84" s="5" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
@@ -6414,20 +6429,20 @@
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="C85" s="97" t="s">
-        <v>190</v>
+      <c r="C85" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="D85" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E85" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F85" s="98" t="s">
-        <v>326</v>
-      </c>
-      <c r="G85" s="99" t="s">
-        <v>191</v>
+        <v>20</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="103" t="s">
+        <v>233</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
@@ -6435,125 +6450,125 @@
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="C86" s="93" t="s">
-        <v>276</v>
-      </c>
-      <c r="D86" s="92">
-        <v>1</v>
-      </c>
-      <c r="E86" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F86" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="G86" s="96" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="C86" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="D86" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F86" s="98" t="s">
+        <v>326</v>
+      </c>
+      <c r="G86" s="99" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="33">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="C87" s="93" t="s">
-        <v>381</v>
-      </c>
-      <c r="D87" s="94" t="s">
-        <v>21</v>
+        <v>276</v>
+      </c>
+      <c r="D87" s="92">
+        <v>1</v>
       </c>
       <c r="E87" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="F87" s="95" t="s">
-        <v>375</v>
+      <c r="F87" s="100" t="s">
+        <v>11</v>
       </c>
       <c r="G87" s="96" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B88" s="33">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D88" s="90" t="s">
+      <c r="C88" s="93" t="s">
+        <v>381</v>
+      </c>
+      <c r="D88" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F88" s="2" t="s">
+      <c r="E88" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F88" s="95" t="s">
+        <v>375</v>
+      </c>
+      <c r="G88" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="33">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D89" s="1">
-        <v>1</v>
+        <v>325</v>
+      </c>
+      <c r="D89" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F89" s="103" t="s">
-        <v>391</v>
+        <v>326</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B90" s="33">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C90" s="104" t="s">
-        <v>255</v>
-      </c>
-      <c r="D90" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E90" s="105" t="s">
-        <v>237</v>
-      </c>
-      <c r="F90" s="110" t="s">
-        <v>340</v>
-      </c>
-      <c r="G90" s="107" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C90" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F90" s="103" t="s">
+        <v>391</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B91" s="33">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D91" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E91" s="103" t="s">
+      <c r="C91" s="104" t="s">
+        <v>255</v>
+      </c>
+      <c r="D91" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E91" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F91" s="103" t="s">
-        <v>344</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>308</v>
+      <c r="F91" s="110" t="s">
+        <v>340</v>
+      </c>
+      <c r="G91" s="107" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
@@ -6562,19 +6577,19 @@
         <v>75</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D92" s="1">
-        <v>1</v>
-      </c>
-      <c r="E92" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D92" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E92" s="103" t="s">
         <v>237</v>
       </c>
       <c r="F92" s="103" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>362</v>
+        <v>308</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6583,19 +6598,19 @@
         <v>76</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>395</v>
+        <v>345</v>
       </c>
       <c r="D93" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>238</v>
+      <c r="F93" s="103" t="s">
+        <v>331</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
@@ -6603,20 +6618,20 @@
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C94" s="104" t="s">
-        <v>249</v>
-      </c>
-      <c r="D94" s="105">
-        <v>1</v>
-      </c>
-      <c r="E94" s="105" t="s">
+      <c r="C94" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D94" s="1">
+        <v>2</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F94" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G94" s="107" t="s">
-        <v>251</v>
+      <c r="F94" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -6624,62 +6639,62 @@
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D95" s="1">
+      <c r="C95" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="D95" s="105">
         <v>1</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F95" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" s="107" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="33">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="104" t="s">
-        <v>250</v>
-      </c>
-      <c r="D96" s="105">
+      <c r="C96" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D96" s="1">
         <v>1</v>
       </c>
-      <c r="E96" s="105" t="s">
+      <c r="E96" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="108" t="s">
-        <v>73</v>
-      </c>
-      <c r="G96" s="107" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F96" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B97" s="33">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D97" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E97" s="2" t="s">
+      <c r="C97" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="D97" s="105">
+        <v>1</v>
+      </c>
+      <c r="E97" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>408</v>
+      <c r="F97" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="G97" s="107" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
@@ -6687,41 +6702,41 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C98" s="112" t="s">
-        <v>259</v>
-      </c>
-      <c r="D98" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="E98" s="111" t="s">
+      <c r="C98" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D98" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F98" s="118" t="s">
-        <v>331</v>
-      </c>
-      <c r="G98" s="112" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F98" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="33">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D99" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="C99" s="112" t="s">
+        <v>259</v>
+      </c>
+      <c r="D99" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" s="111" t="s">
         <v>237</v>
       </c>
-      <c r="F99" s="103" t="s">
-        <v>335</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>324</v>
+      <c r="F99" s="118" t="s">
+        <v>331</v>
+      </c>
+      <c r="G99" s="112" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="100" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6730,40 +6745,40 @@
         <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D100" s="1">
-        <v>1</v>
-      </c>
-      <c r="E100" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D100" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F100" s="103" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B101" s="33">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C101" s="104" t="s">
-        <v>351</v>
-      </c>
-      <c r="D101" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" s="117" t="s">
-        <v>331</v>
-      </c>
-      <c r="F101" s="106" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="107" t="s">
-        <v>332</v>
+      <c r="C101" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F101" s="103" t="s">
+        <v>329</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -6771,62 +6786,62 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D102" s="90" t="s">
+      <c r="C102" s="104" t="s">
+        <v>351</v>
+      </c>
+      <c r="D102" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="E102" s="117" t="s">
         <v>331</v>
       </c>
-      <c r="G102" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="F102" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="G102" s="107" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" s="33">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="D103" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F103" s="103" t="s">
-        <v>371</v>
+        <v>237</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B104" s="33">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D104" s="1">
-        <v>2</v>
-      </c>
-      <c r="E104" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D104" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>238</v>
       </c>
       <c r="F104" s="103" t="s">
-        <v>406</v>
+        <v>371</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>398</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6835,28 +6850,28 @@
         <v>88</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D105" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F105" s="103" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B106" s="33">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>267</v>
+        <v>405</v>
       </c>
       <c r="D106" s="1">
         <v>1</v>
@@ -6864,11 +6879,11 @@
       <c r="E106" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>80</v>
+      <c r="F106" s="103" t="s">
+        <v>342</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
@@ -6877,19 +6892,19 @@
         <v>90</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D107" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E107" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D107" s="1">
+        <v>1</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="G107" s="5" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
@@ -6898,19 +6913,19 @@
         <v>91</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>404</v>
+        <v>288</v>
       </c>
       <c r="D108" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F108" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="F108" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G108" s="5" t="s">
-        <v>409</v>
+        <v>289</v>
       </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
@@ -6919,46 +6934,61 @@
         <v>92</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D109" s="90" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>401</v>
+        <v>238</v>
       </c>
       <c r="F109" s="103" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110" s="33">
         <f>IF(C110="","",B109+1)</f>
         <v>93</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>311</v>
+        <v>399</v>
       </c>
       <c r="D110" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E110" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F110" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B111" s="33">
+        <f>IF(C111="","",B110+1)</f>
+        <v>94</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D111" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F110" s="103" t="s">
+      <c r="F111" s="103" t="s">
         <v>400</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G111" s="5" t="s">
         <v>312</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B111" s="33" t="str">
-        <f>IF(C111="","",B110+1)</f>
-        <v/>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
@@ -7136,21 +7166,81 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C17:G17" xr:uid="{4C55C11C-1620-411A-9B2F-3F513CAF246A}">
+  <autoFilter ref="C17:G140" xr:uid="{4C55C11C-1620-411A-9B2F-3F513CAF246A}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C18:G140">
-      <sortCondition ref="C17"/>
+      <sortCondition ref="C17:C140"/>
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="O72:P72"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="P8:R8"/>
@@ -7175,75 +7265,15 @@
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F2A8C6-3745-48F0-9CAF-2E05DA71981D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F41185-97E6-4CA9-A1E6-D5C101061345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="416">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1048,11 +1048,6 @@
   </si>
   <si>
     <t>MemWrite Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_id_ex_bridge
-w_id_jump_addr</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1595,20 +1590,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_branch_mux
-w_ex_flush</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_jump_mux
-w_ex_flush</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_flush</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>u_ex_mem_bridge
 u_load_stall_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1620,20 +1601,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w_load_stall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>u_load_stall_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Load Stall Flag Signal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_if_id_bridge
-u_id_ex_bridge</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1727,6 +1699,44 @@
   </si>
   <si>
     <t>ALU Negative Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_branch_mux
+w_ex_ctr_flush</t>
+  </si>
+  <si>
+    <t>u_jump_mux
+w_ex_ctr_flush</t>
+  </si>
+  <si>
+    <t>w_ex_ctr_flush</t>
+  </si>
+  <si>
+    <t>w_ctr_load_stall</t>
+  </si>
+  <si>
+    <t>u_if_id_bridge
+u_id_ex_bridge
+u_pc_stall_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_pc_stall_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_pc_stall_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-MEM RADDR (Next) (Not Applied Load Stall)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge
+w_id_jump_addr
+w_pc_stall_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2710,16 +2720,58 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2737,52 +2789,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3145,31 +3155,31 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="143"/>
-      <c r="I2" s="120" t="s">
+      <c r="B2" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="135"/>
+      <c r="I2" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="121"/>
-      <c r="K2" s="120" t="s">
+      <c r="K2" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="122"/>
+      <c r="L2" s="120"/>
       <c r="M2" s="121"/>
-      <c r="O2" s="120" t="s">
+      <c r="O2" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P2" s="121"/>
-      <c r="Q2" s="120" t="s">
+      <c r="Q2" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="122"/>
+      <c r="R2" s="120"/>
       <c r="S2" s="121"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3191,24 +3201,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="131"/>
-      <c r="K3" s="132" t="s">
+      <c r="J3" s="129"/>
+      <c r="K3" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="133"/>
-      <c r="M3" s="134"/>
-      <c r="O3" s="130" t="s">
+      <c r="L3" s="131"/>
+      <c r="M3" s="132"/>
+      <c r="O3" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="132" t="s">
+      <c r="P3" s="129"/>
+      <c r="Q3" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="R3" s="133"/>
-      <c r="S3" s="134"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="132"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3229,24 +3239,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="130" t="s">
+      <c r="J4" s="129"/>
+      <c r="K4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="135"/>
-      <c r="M4" s="131"/>
-      <c r="O4" s="130" t="s">
+      <c r="L4" s="142"/>
+      <c r="M4" s="129"/>
+      <c r="O4" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="130" t="s">
+      <c r="P4" s="129"/>
+      <c r="Q4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="135"/>
-      <c r="S4" s="131"/>
+      <c r="R4" s="142"/>
+      <c r="S4" s="129"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3267,24 +3277,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="136" t="s">
+      <c r="I5" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="137"/>
-      <c r="K5" s="138" t="s">
+      <c r="J5" s="123"/>
+      <c r="K5" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="139"/>
-      <c r="O5" s="136" t="s">
+      <c r="L5" s="125"/>
+      <c r="M5" s="126"/>
+      <c r="O5" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="138" t="s">
+      <c r="P5" s="123"/>
+      <c r="Q5" s="124" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="119"/>
-      <c r="S5" s="139"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="126"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3308,22 +3318,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="128" t="s">
+      <c r="J6" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="128"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="128" t="s">
+      <c r="P6" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="128"/>
-      <c r="R6" s="128"/>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="127"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3350,22 +3360,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="140" t="s">
+      <c r="J7" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="129" t="s">
+      <c r="P7" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
+      <c r="Q7" s="143"/>
+      <c r="R7" s="143"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
@@ -3407,11 +3417,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="119" t="s">
+      <c r="P8" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="119"/>
-      <c r="R8" s="119"/>
+      <c r="Q8" s="125"/>
+      <c r="R8" s="125"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
@@ -3585,15 +3595,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="124"/>
-      <c r="K12" s="125" t="s">
+      <c r="J12" s="138"/>
+      <c r="K12" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="126"/>
-      <c r="M12" s="127"/>
+      <c r="L12" s="140"/>
+      <c r="M12" s="141"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3716,15 +3726,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="123" t="s">
+      <c r="O16" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="125" t="s">
+      <c r="P16" s="138"/>
+      <c r="Q16" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="R16" s="126"/>
-      <c r="S16" s="127"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="141"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3746,83 +3756,83 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B18" s="33">
         <f>IF(C18="","",1)</f>
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>291</v>
+        <v>410</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>64</v>
+        <v>384</v>
+      </c>
+      <c r="F18" s="103" t="s">
+        <v>411</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="120" t="s">
+        <v>385</v>
+      </c>
+      <c r="I18" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J18" s="121"/>
-      <c r="K18" s="120" t="s">
+      <c r="K18" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="122"/>
+      <c r="L18" s="120"/>
       <c r="M18" s="121"/>
-      <c r="O18" s="120" t="s">
+      <c r="O18" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P18" s="121"/>
-      <c r="Q18" s="120" t="s">
+      <c r="Q18" s="119" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="122"/>
+      <c r="R18" s="120"/>
       <c r="S18" s="121"/>
     </row>
-    <row r="19" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="33">
         <f t="shared" ref="B19:B50" si="0">IF(C19="","",B18+1)</f>
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D19" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="103" t="s">
-        <v>75</v>
+        <v>78</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="130" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="131"/>
-      <c r="K19" s="132" t="s">
+      <c r="J19" s="129"/>
+      <c r="K19" s="130" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="133"/>
-      <c r="M19" s="134"/>
-      <c r="O19" s="130" t="s">
+      <c r="L19" s="131"/>
+      <c r="M19" s="132"/>
+      <c r="O19" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="132" t="s">
+      <c r="P19" s="129"/>
+      <c r="Q19" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
+      <c r="R19" s="131"/>
+      <c r="S19" s="132"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3830,77 +3840,77 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="D20" s="90" t="s">
-        <v>20</v>
+        <v>286</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="F20" s="103" t="s">
         <v>75</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="I20" s="130" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="131"/>
-      <c r="K20" s="132" t="s">
+      <c r="J20" s="129"/>
+      <c r="K20" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
-      <c r="O20" s="130" t="s">
+      <c r="L20" s="131"/>
+      <c r="M20" s="132"/>
+      <c r="O20" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="130" t="s">
+      <c r="P20" s="129"/>
+      <c r="Q20" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="135"/>
-      <c r="S20" s="131"/>
-    </row>
-    <row r="21" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R20" s="142"/>
+      <c r="S20" s="129"/>
+    </row>
+    <row r="21" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F21" s="103" t="s">
-        <v>330</v>
+        <v>75</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="I21" s="136" t="s">
+        <v>352</v>
+      </c>
+      <c r="I21" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="137"/>
-      <c r="K21" s="138" t="s">
+      <c r="J21" s="123"/>
+      <c r="K21" s="124" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="119"/>
-      <c r="M21" s="139"/>
-      <c r="O21" s="136" t="s">
+      <c r="L21" s="125"/>
+      <c r="M21" s="126"/>
+      <c r="O21" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="138" t="s">
+      <c r="P21" s="123"/>
+      <c r="Q21" s="124" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="119"/>
-      <c r="S21" s="139"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="126"/>
     </row>
     <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
@@ -3908,105 +3918,105 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
+        <v>353</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>297</v>
+        <v>338</v>
+      </c>
+      <c r="F22" s="103" t="s">
+        <v>329</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="128" t="s">
+      <c r="J22" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="128" t="s">
+      <c r="P22" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q22" s="128"/>
-      <c r="R22" s="128"/>
+      <c r="Q22" s="127"/>
+      <c r="R22" s="127"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="33">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D23" s="90" t="s">
-        <v>20</v>
+        <v>405</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="103" t="s">
-        <v>368</v>
+      <c r="F23" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>257</v>
+        <v>406</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="140" t="s">
+      <c r="J23" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="129" t="s">
+      <c r="P23" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="129"/>
-      <c r="R23" s="129"/>
+      <c r="Q23" s="143"/>
+      <c r="R23" s="143"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="33">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
+        <v>255</v>
+      </c>
+      <c r="D24" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>297</v>
+      <c r="F24" s="103" t="s">
+        <v>367</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
@@ -4026,11 +4036,11 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="119" t="s">
+      <c r="P24" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="119"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="125"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
@@ -4041,19 +4051,19 @@
         <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>65</v>
+        <v>296</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
@@ -4086,25 +4096,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="33">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D26" s="90" t="s">
-        <v>20</v>
+        <v>243</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="103" t="s">
-        <v>75</v>
+        <v>236</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
@@ -4137,25 +4147,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B27" s="33">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
+      </c>
+      <c r="D27" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="103" t="s">
+        <v>75</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
@@ -4194,19 +4204,19 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D28" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>40</v>
+        <v>260</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>53</v>
+        <v>296</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
@@ -4245,19 +4255,19 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D29" s="90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G29" s="5" t="s">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
@@ -4296,19 +4306,19 @@
         <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1</v>
+        <v>294</v>
+      </c>
+      <c r="D30" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>226</v>
+        <v>88</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
@@ -4341,25 +4351,25 @@
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="33">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
-      <c r="E31" s="102" t="s">
-        <v>296</v>
-      </c>
-      <c r="F31" s="103" t="s">
-        <v>383</v>
+      <c r="E31" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
@@ -4398,29 +4408,29 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>236</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="102" t="s">
+        <v>295</v>
       </c>
       <c r="F32" s="103" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I32" s="123" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="124"/>
-      <c r="K32" s="125" t="s">
+      <c r="J32" s="138"/>
+      <c r="K32" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="126"/>
-      <c r="M32" s="127"/>
+      <c r="L32" s="140"/>
+      <c r="M32" s="141"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4437,25 +4447,25 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B33" s="33">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>309</v>
+        <v>409</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>236</v>
+      <c r="E33" s="102" t="s">
+        <v>376</v>
       </c>
       <c r="F33" s="103" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
@@ -4473,25 +4483,25 @@
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B34" s="33">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="D34" s="1">
-        <v>6</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>65</v>
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F34" s="103" t="s">
+        <v>408</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
@@ -4515,10 +4525,10 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D35" s="90" t="s">
-        <v>56</v>
+        <v>308</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>236</v>
@@ -4527,7 +4537,7 @@
         <v>63</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
@@ -4551,31 +4561,31 @@
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D36" s="90" t="s">
-        <v>56</v>
+        <v>241</v>
+      </c>
+      <c r="D36" s="1">
+        <v>6</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O36" s="137" t="s">
+        <v>104</v>
+      </c>
+      <c r="P36" s="138"/>
+      <c r="Q36" s="139" t="s">
         <v>236</v>
       </c>
-      <c r="F36" s="103" t="s">
-        <v>341</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="O36" s="123" t="s">
-        <v>104</v>
-      </c>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="125" t="s">
-        <v>236</v>
-      </c>
-      <c r="R36" s="126"/>
-      <c r="S36" s="127"/>
-    </row>
-    <row r="37" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R36" s="140"/>
+      <c r="S36" s="141"/>
+    </row>
+    <row r="37" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -4590,128 +4600,128 @@
         <v>236</v>
       </c>
       <c r="F37" s="103" t="s">
-        <v>336</v>
+        <v>63</v>
       </c>
       <c r="G37" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B38" s="33">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D38" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F38" s="103" t="s">
+        <v>340</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="I38" s="119" t="s">
+        <v>102</v>
+      </c>
+      <c r="J38" s="121"/>
+      <c r="K38" s="119" t="s">
+        <v>122</v>
+      </c>
+      <c r="L38" s="120"/>
+      <c r="M38" s="121"/>
+      <c r="O38" s="119" t="s">
+        <v>102</v>
+      </c>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="119" t="s">
+        <v>173</v>
+      </c>
+      <c r="R38" s="120"/>
+      <c r="S38" s="121"/>
+    </row>
+    <row r="39" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B39" s="33">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="38" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="33">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="D38" s="1">
+      <c r="D39" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" s="103" t="s">
+        <v>335</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I39" s="128" t="s">
+        <v>108</v>
+      </c>
+      <c r="J39" s="129"/>
+      <c r="K39" s="130" t="s">
+        <v>123</v>
+      </c>
+      <c r="L39" s="131"/>
+      <c r="M39" s="132"/>
+      <c r="O39" s="128" t="s">
+        <v>108</v>
+      </c>
+      <c r="P39" s="129"/>
+      <c r="Q39" s="130" t="s">
+        <v>232</v>
+      </c>
+      <c r="R39" s="131"/>
+      <c r="S39" s="132"/>
+    </row>
+    <row r="40" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B40" s="33">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D40" s="1">
         <v>1</v>
       </c>
-      <c r="E38" s="102" t="s">
-        <v>377</v>
-      </c>
-      <c r="F38" s="103" t="s">
-        <v>392</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="I38" s="120" t="s">
-        <v>102</v>
-      </c>
-      <c r="J38" s="121"/>
-      <c r="K38" s="120" t="s">
-        <v>122</v>
-      </c>
-      <c r="L38" s="122"/>
-      <c r="M38" s="121"/>
-      <c r="O38" s="120" t="s">
-        <v>102</v>
-      </c>
-      <c r="P38" s="121"/>
-      <c r="Q38" s="120" t="s">
-        <v>173</v>
-      </c>
-      <c r="R38" s="122"/>
-      <c r="S38" s="121"/>
-    </row>
-    <row r="39" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B39" s="33">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="E40" s="102" t="s">
         <v>343</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="102" t="s">
-        <v>344</v>
-      </c>
-      <c r="F39" s="103" t="s">
-        <v>369</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="I39" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="J39" s="131"/>
-      <c r="K39" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="L39" s="133"/>
-      <c r="M39" s="134"/>
-      <c r="O39" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="132" t="s">
-        <v>232</v>
-      </c>
-      <c r="R39" s="133"/>
-      <c r="S39" s="134"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B40" s="33">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D40" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="103" t="s">
+        <v>368</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="I40" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="J40" s="129"/>
+      <c r="K40" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="L40" s="131"/>
+      <c r="M40" s="132"/>
+      <c r="O40" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="P40" s="129"/>
+      <c r="Q40" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I40" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="J40" s="131"/>
-      <c r="K40" s="132" t="s">
-        <v>107</v>
-      </c>
-      <c r="L40" s="133"/>
-      <c r="M40" s="134"/>
-      <c r="O40" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="P40" s="131"/>
-      <c r="Q40" s="130" t="s">
-        <v>64</v>
-      </c>
-      <c r="R40" s="135"/>
-      <c r="S40" s="131"/>
+      <c r="R40" s="142"/>
+      <c r="S40" s="129"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4719,78 +4729,78 @@
         <v>24</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D41" s="101" t="s">
+        <v>292</v>
+      </c>
+      <c r="D41" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="102" t="s">
-        <v>233</v>
+      <c r="E41" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I41" s="136" t="s">
+        <v>86</v>
+      </c>
+      <c r="I41" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="137"/>
-      <c r="K41" s="138" t="s">
+      <c r="J41" s="123"/>
+      <c r="K41" s="124" t="s">
         <v>125</v>
       </c>
-      <c r="L41" s="119"/>
-      <c r="M41" s="139"/>
-      <c r="O41" s="136" t="s">
+      <c r="L41" s="125"/>
+      <c r="M41" s="126"/>
+      <c r="O41" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="137"/>
-      <c r="Q41" s="138" t="s">
+      <c r="P41" s="123"/>
+      <c r="Q41" s="124" t="s">
         <v>174</v>
       </c>
-      <c r="R41" s="119"/>
-      <c r="S41" s="139"/>
+      <c r="R41" s="125"/>
+      <c r="S41" s="126"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C42" s="97" t="s">
-        <v>273</v>
-      </c>
-      <c r="D42" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="33" t="s">
+      <c r="C42" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D42" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="102" t="s">
+        <v>233</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F42" s="98" t="s">
-        <v>326</v>
-      </c>
-      <c r="G42" s="99" t="s">
-        <v>274</v>
+      <c r="G42" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="128" t="s">
+      <c r="J42" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K42" s="128"/>
-      <c r="L42" s="128"/>
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="128" t="s">
+      <c r="P42" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q42" s="128"/>
-      <c r="R42" s="128"/>
+      <c r="Q42" s="127"/>
+      <c r="R42" s="127"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4800,63 +4810,63 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>294</v>
+      <c r="C43" s="97" t="s">
+        <v>272</v>
       </c>
       <c r="D43" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>87</v>
+        <v>21</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" s="98" t="s">
+        <v>325</v>
+      </c>
+      <c r="G43" s="99" t="s">
+        <v>273</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="140" t="s">
+      <c r="J43" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="129" t="s">
+      <c r="P43" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="129"/>
-      <c r="R43" s="129"/>
+      <c r="Q43" s="143"/>
+      <c r="R43" s="143"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="33">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="114" t="s">
-        <v>236</v>
-      </c>
-      <c r="F44" s="98" t="s">
-        <v>386</v>
+        <v>293</v>
+      </c>
+      <c r="D44" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
@@ -4876,34 +4886,34 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="119" t="s">
+      <c r="P44" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="119"/>
-      <c r="R44" s="119"/>
+      <c r="Q44" s="125"/>
+      <c r="R44" s="125"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="33">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="114" t="s">
         <v>236</v>
       </c>
-      <c r="F45" s="103" t="s">
-        <v>237</v>
+      <c r="F45" s="98" t="s">
+        <v>382</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
@@ -4942,19 +4952,19 @@
         <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
       </c>
-      <c r="E46" s="114" t="s">
+      <c r="E46" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F46" s="114" t="s">
+      <c r="F46" s="103" t="s">
         <v>237</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
@@ -4987,25 +4997,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="33">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D47" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F47" s="103" t="s">
-        <v>254</v>
-      </c>
-      <c r="G47" s="99" t="s">
-        <v>194</v>
+        <v>246</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="114" t="s">
+        <v>236</v>
+      </c>
+      <c r="F47" s="114" t="s">
+        <v>237</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>248</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
@@ -5044,29 +5054,29 @@
         <v>31</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>217</v>
+        <v>381</v>
       </c>
       <c r="D48" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>233</v>
       </c>
       <c r="F48" s="103" t="s">
-        <v>394</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="I48" s="123" t="s">
+        <v>253</v>
+      </c>
+      <c r="G48" s="99" t="s">
+        <v>194</v>
+      </c>
+      <c r="I48" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="124"/>
-      <c r="K48" s="125" t="s">
+      <c r="J48" s="138"/>
+      <c r="K48" s="139" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="126"/>
-      <c r="M48" s="127"/>
+      <c r="L48" s="140"/>
+      <c r="M48" s="141"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5083,25 +5093,25 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B49" s="33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C49" s="112" t="s">
-        <v>218</v>
-      </c>
-      <c r="D49" s="113" t="s">
+      <c r="C49" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="111" t="s">
+      <c r="E49" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F49" s="115" t="s">
-        <v>370</v>
-      </c>
-      <c r="G49" s="112" t="s">
-        <v>220</v>
+      <c r="F49" s="103" t="s">
+        <v>388</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
@@ -5119,25 +5129,25 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="116">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D50" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F50" s="103" t="s">
-        <v>386</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>334</v>
+      <c r="C50" s="112" t="s">
+        <v>218</v>
+      </c>
+      <c r="D50" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="111" t="s">
+        <v>233</v>
+      </c>
+      <c r="F50" s="115" t="s">
+        <v>369</v>
+      </c>
+      <c r="G50" s="112" t="s">
+        <v>220</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
@@ -5155,34 +5165,34 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B51" s="33">
         <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D51" s="1">
-        <v>1</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>236</v>
+        <v>332</v>
+      </c>
+      <c r="D51" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="F51" s="103" t="s">
-        <v>237</v>
+        <v>382</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="I51" s="120" t="s">
+        <v>333</v>
+      </c>
+      <c r="I51" s="119" t="s">
         <v>102</v>
       </c>
       <c r="J51" s="121"/>
-      <c r="K51" s="120" t="s">
+      <c r="K51" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="122"/>
+      <c r="L51" s="120"/>
       <c r="M51" s="121"/>
       <c r="O51" s="83">
         <v>6</v>
@@ -5206,29 +5216,29 @@
         <v>35</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D52" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F52" s="103" t="s">
+        <v>237</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="I52" s="130" t="s">
+        <v>298</v>
+      </c>
+      <c r="I52" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="131"/>
-      <c r="K52" s="132" t="s">
+      <c r="J52" s="129"/>
+      <c r="K52" s="130" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="133"/>
-      <c r="M52" s="134"/>
+      <c r="L52" s="131"/>
+      <c r="M52" s="132"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5251,29 +5261,29 @@
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D53" s="90" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G53" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I53" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="I53" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="131"/>
-      <c r="K53" s="132" t="s">
+      <c r="J53" s="129"/>
+      <c r="K53" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="133"/>
-      <c r="M53" s="134"/>
+      <c r="L53" s="131"/>
+      <c r="M53" s="132"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5290,35 +5300,35 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="33">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="D54" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F54" s="103" t="s">
-        <v>48</v>
+        <v>277</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I54" s="136" t="s">
+        <v>52</v>
+      </c>
+      <c r="I54" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="137"/>
-      <c r="K54" s="138" t="s">
+      <c r="J54" s="123"/>
+      <c r="K54" s="124" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="119"/>
-      <c r="M54" s="139"/>
+      <c r="L54" s="125"/>
+      <c r="M54" s="126"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5335,34 +5345,34 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="33">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>372</v>
+        <v>221</v>
       </c>
       <c r="D55" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
+      </c>
+      <c r="F55" s="103" t="s">
+        <v>48</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>373</v>
+        <v>223</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="128" t="s">
+      <c r="J55" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="K55" s="128"/>
-      <c r="L55" s="128"/>
+      <c r="K55" s="127"/>
+      <c r="L55" s="127"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5388,40 +5398,40 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D56" s="1">
-        <v>1</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
+      </c>
+      <c r="D56" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="129" t="s">
+      <c r="J56" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="129"/>
-      <c r="L56" s="129"/>
+      <c r="K56" s="143"/>
+      <c r="L56" s="143"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="123" t="s">
+      <c r="O56" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="124"/>
-      <c r="Q56" s="125" t="s">
+      <c r="P56" s="138"/>
+      <c r="Q56" s="139" t="s">
         <v>237</v>
       </c>
-      <c r="R56" s="126"/>
-      <c r="S56" s="127"/>
+      <c r="R56" s="140"/>
+      <c r="S56" s="141"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5429,28 +5439,28 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="G57" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="119" t="s">
+      <c r="J57" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="119"/>
-      <c r="L57" s="119"/>
+      <c r="K57" s="125"/>
+      <c r="L57" s="125"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
@@ -5467,10 +5477,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>357</v>
@@ -5490,14 +5500,14 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="120" t="s">
+      <c r="O58" s="119" t="s">
         <v>102</v>
       </c>
       <c r="P58" s="121"/>
-      <c r="Q58" s="120" t="s">
+      <c r="Q58" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="122"/>
+      <c r="R58" s="120"/>
       <c r="S58" s="121"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
@@ -5506,19 +5516,19 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
@@ -5535,15 +5545,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="130" t="s">
+      <c r="O59" s="128" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="131"/>
-      <c r="Q59" s="132" t="s">
+      <c r="P59" s="129"/>
+      <c r="Q59" s="130" t="s">
         <v>232</v>
       </c>
-      <c r="R59" s="133"/>
-      <c r="S59" s="134"/>
+      <c r="R59" s="131"/>
+      <c r="S59" s="132"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5551,19 +5561,19 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="D60" s="33">
+        <v>348</v>
+      </c>
+      <c r="D60" s="1">
         <v>1</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>344</v>
+      <c r="E60" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
@@ -5580,15 +5590,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="130" t="s">
+      <c r="O60" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="131"/>
-      <c r="Q60" s="130" t="s">
+      <c r="P60" s="129"/>
+      <c r="Q60" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="135"/>
-      <c r="S60" s="131"/>
+      <c r="R60" s="142"/>
+      <c r="S60" s="129"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5596,19 +5606,19 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D61" s="90" t="s">
-        <v>20</v>
+        <v>349</v>
+      </c>
+      <c r="D61" s="33">
+        <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>234</v>
+        <v>343</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>44</v>
+        <v>330</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>193</v>
+        <v>359</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
@@ -5625,15 +5635,15 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="136" t="s">
+      <c r="O61" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="137"/>
-      <c r="Q61" s="138" t="s">
+      <c r="P61" s="123"/>
+      <c r="Q61" s="124" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="119"/>
-      <c r="S61" s="139"/>
+      <c r="R61" s="125"/>
+      <c r="S61" s="126"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5641,19 +5651,19 @@
         <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D62" s="1">
-        <v>4</v>
+        <v>192</v>
+      </c>
+      <c r="D62" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>236</v>
+        <v>44</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
@@ -5673,11 +5683,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="128" t="s">
+      <c r="P62" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="128"/>
-      <c r="R62" s="128"/>
+      <c r="Q62" s="127"/>
+      <c r="R62" s="127"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5688,10 +5698,10 @@
         <v>46</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D63" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>58</v>
@@ -5700,7 +5710,7 @@
         <v>236</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
@@ -5720,11 +5730,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="129" t="s">
+      <c r="P63" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="129"/>
-      <c r="R63" s="129"/>
+      <c r="Q63" s="143"/>
+      <c r="R63" s="143"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
@@ -5735,19 +5745,19 @@
         <v>47</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
@@ -5767,11 +5777,11 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="119" t="s">
+      <c r="P64" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="119"/>
-      <c r="R64" s="119"/>
+      <c r="Q64" s="125"/>
+      <c r="R64" s="125"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
@@ -5782,19 +5792,19 @@
         <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D65" s="90" t="s">
-        <v>57</v>
+        <v>196</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
@@ -5827,25 +5837,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B66" s="33">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D66" s="1">
-        <v>6</v>
+        <v>285</v>
+      </c>
+      <c r="D66" s="90" t="s">
+        <v>57</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F66" s="103" t="s">
-        <v>393</v>
+      <c r="F66" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>240</v>
+        <v>61</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
@@ -5883,20 +5893,20 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="C67" s="97" t="s">
-        <v>275</v>
-      </c>
-      <c r="D67" s="101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E67" s="33" t="s">
+      <c r="C67" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D67" s="1">
+        <v>6</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="98" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="99" t="s">
-        <v>50</v>
+      <c r="F67" s="103" t="s">
+        <v>387</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
@@ -5929,25 +5939,25 @@
         <v>155</v>
       </c>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B68" s="33">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D68" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="C68" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="D68" s="101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>59</v>
+      <c r="F68" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="99" t="s">
+        <v>50</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
@@ -5986,19 +5996,19 @@
         <v>52</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D69" s="90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
@@ -6031,13 +6041,13 @@
         <v>181</v>
       </c>
     </row>
-    <row r="70" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B70" s="33">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D70" s="90" t="s">
         <v>56</v>
@@ -6045,11 +6055,11 @@
       <c r="E70" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F70" s="103" t="s">
-        <v>387</v>
+      <c r="F70" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
@@ -6082,13 +6092,13 @@
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="2:19" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="33">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D71" s="90" t="s">
         <v>56</v>
@@ -6097,10 +6107,10 @@
         <v>44</v>
       </c>
       <c r="F71" s="103" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
@@ -6133,44 +6143,44 @@
         <v>189</v>
       </c>
     </row>
-    <row r="72" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:19" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="33">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D72" s="1">
-        <v>5</v>
+        <v>282</v>
+      </c>
+      <c r="D72" s="90" t="s">
+        <v>56</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>64</v>
+      <c r="F72" s="103" t="s">
+        <v>404</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I72" s="123" t="s">
+        <v>302</v>
+      </c>
+      <c r="I72" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="124"/>
-      <c r="K72" s="125" t="s">
+      <c r="J72" s="138"/>
+      <c r="K72" s="139" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="126"/>
-      <c r="M72" s="127"/>
-      <c r="O72" s="123" t="s">
+      <c r="L72" s="140"/>
+      <c r="M72" s="141"/>
+      <c r="O72" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="P72" s="124"/>
-      <c r="Q72" s="125" t="s">
+      <c r="P72" s="138"/>
+      <c r="Q72" s="139" t="s">
         <v>238</v>
       </c>
-      <c r="R72" s="126"/>
-      <c r="S72" s="127"/>
+      <c r="R72" s="140"/>
+      <c r="S72" s="141"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
@@ -6178,61 +6188,61 @@
         <v>56</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>376</v>
+        <v>284</v>
       </c>
       <c r="D73" s="1">
+        <v>5</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B74" s="33">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D74" s="1">
         <v>2</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="74" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B74" s="33">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D74" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="E74" s="102" t="s">
-        <v>380</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>236</v>
       </c>
       <c r="G74" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+      <c r="B75" s="33">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D75" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" s="102" t="s">
+        <v>379</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G75" s="5" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B75" s="33">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D75" s="1">
-        <v>1</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F75" s="114" t="s">
-        <v>236</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="76" spans="2:19" x14ac:dyDescent="0.3">
@@ -6241,7 +6251,7 @@
         <v>59</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -6249,11 +6259,11 @@
       <c r="E76" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>233</v>
+      <c r="F76" s="114" t="s">
+        <v>236</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="2:19" x14ac:dyDescent="0.3">
@@ -6262,7 +6272,7 @@
         <v>60</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -6270,53 +6280,53 @@
       <c r="E77" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="114" t="s">
+      <c r="F77" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B78" s="33">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F78" s="114" t="s">
         <v>236</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="G78" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="78" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B78" s="33">
-        <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="D78" s="90" t="s">
+    <row r="79" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B79" s="33">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D79" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F78" s="103" t="s">
-        <v>253</v>
-      </c>
-      <c r="G78" s="99" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B79" s="33">
-        <f t="shared" si="1"/>
-        <v>62</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D79" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F79" s="111" t="s">
-        <v>233</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>205</v>
+      <c r="F79" s="103" t="s">
+        <v>415</v>
+      </c>
+      <c r="G79" s="99" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6324,10 +6334,10 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C80" s="112" t="s">
-        <v>204</v>
-      </c>
-      <c r="D80" s="113" t="s">
+      <c r="C80" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D80" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E80" s="1" t="s">
@@ -6336,8 +6346,8 @@
       <c r="F80" s="111" t="s">
         <v>233</v>
       </c>
-      <c r="G80" s="112" t="s">
-        <v>206</v>
+      <c r="G80" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
@@ -6345,20 +6355,20 @@
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D81" s="1">
-        <v>1</v>
+      <c r="C81" s="112" t="s">
+        <v>204</v>
+      </c>
+      <c r="D81" s="113" t="s">
+        <v>20</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>208</v>
+        <v>62</v>
+      </c>
+      <c r="F81" s="111" t="s">
+        <v>233</v>
+      </c>
+      <c r="G81" s="112" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
@@ -6367,7 +6377,7 @@
         <v>65</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>198</v>
+        <v>336</v>
       </c>
       <c r="D82" s="1">
         <v>1</v>
@@ -6375,53 +6385,53 @@
       <c r="E82" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F82" s="2" t="s">
+      <c r="F82" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="33">
         <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
         <v>66</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D83" s="101" t="s">
-        <v>46</v>
+        <v>198</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B84" s="33">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D84" s="1">
-        <v>1</v>
+        <v>276</v>
+      </c>
+      <c r="D84" s="101" t="s">
+        <v>46</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>216</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
@@ -6430,19 +6440,19 @@
         <v>68</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D85" s="90" t="s">
-        <v>20</v>
+        <v>202</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F85" s="103" t="s">
-        <v>233</v>
-      </c>
       <c r="G85" s="5" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
@@ -6450,20 +6460,20 @@
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="C86" s="97" t="s">
-        <v>190</v>
+      <c r="C86" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="D86" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E86" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F86" s="98" t="s">
-        <v>326</v>
-      </c>
-      <c r="G86" s="99" t="s">
-        <v>191</v>
+        <v>20</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="103" t="s">
+        <v>233</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
@@ -6471,125 +6481,125 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C87" s="93" t="s">
-        <v>276</v>
-      </c>
-      <c r="D87" s="92">
-        <v>1</v>
-      </c>
-      <c r="E87" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F87" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="G87" s="96" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="C87" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="D87" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F87" s="98" t="s">
+        <v>325</v>
+      </c>
+      <c r="G87" s="99" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="33">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
       <c r="C88" s="93" t="s">
-        <v>381</v>
-      </c>
-      <c r="D88" s="94" t="s">
-        <v>21</v>
+        <v>275</v>
+      </c>
+      <c r="D88" s="92">
+        <v>1</v>
       </c>
       <c r="E88" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="F88" s="95" t="s">
-        <v>375</v>
+      <c r="F88" s="100" t="s">
+        <v>11</v>
       </c>
       <c r="G88" s="96" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B89" s="33">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D89" s="90" t="s">
+      <c r="C89" s="93" t="s">
+        <v>380</v>
+      </c>
+      <c r="D89" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F89" s="2" t="s">
+      <c r="E89" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F89" s="95" t="s">
+        <v>374</v>
+      </c>
+      <c r="G89" s="96" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="33">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D90" s="1">
-        <v>1</v>
+        <v>324</v>
+      </c>
+      <c r="D90" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F90" s="103" t="s">
-        <v>391</v>
+        <v>325</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>412</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="33">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C91" s="104" t="s">
-        <v>255</v>
-      </c>
-      <c r="D91" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E91" s="105" t="s">
-        <v>237</v>
-      </c>
-      <c r="F91" s="110" t="s">
-        <v>340</v>
-      </c>
-      <c r="G91" s="107" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C91" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D91" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B92" s="33">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D92" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E92" s="103" t="s">
+      <c r="C92" s="104" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E92" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F92" s="103" t="s">
-        <v>344</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>308</v>
+      <c r="F92" s="110" t="s">
+        <v>339</v>
+      </c>
+      <c r="G92" s="107" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -6598,19 +6608,19 @@
         <v>76</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D93" s="1">
-        <v>1</v>
-      </c>
-      <c r="E93" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D93" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E93" s="103" t="s">
         <v>237</v>
       </c>
       <c r="F93" s="103" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>362</v>
+        <v>307</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
@@ -6619,19 +6629,19 @@
         <v>77</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>395</v>
+        <v>344</v>
       </c>
       <c r="D94" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>238</v>
+      <c r="F94" s="103" t="s">
+        <v>330</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>397</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -6639,20 +6649,20 @@
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C95" s="104" t="s">
-        <v>249</v>
-      </c>
-      <c r="D95" s="105">
-        <v>1</v>
-      </c>
-      <c r="E95" s="105" t="s">
+      <c r="C95" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D95" s="1">
+        <v>2</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F95" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G95" s="107" t="s">
-        <v>251</v>
+      <c r="F95" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6660,62 +6670,62 @@
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D96" s="1">
+      <c r="C96" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="D96" s="105">
         <v>1</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F96" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" s="107" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="33">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C97" s="104" t="s">
-        <v>250</v>
-      </c>
-      <c r="D97" s="105">
+      <c r="C97" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D97" s="1">
         <v>1</v>
       </c>
-      <c r="E97" s="105" t="s">
+      <c r="E97" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F97" s="108" t="s">
-        <v>73</v>
-      </c>
-      <c r="G97" s="107" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F97" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B98" s="33">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D98" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="C98" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="D98" s="105">
+        <v>1</v>
+      </c>
+      <c r="E98" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>408</v>
+      <c r="F98" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="G98" s="107" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
@@ -6723,41 +6733,41 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C99" s="112" t="s">
-        <v>259</v>
-      </c>
-      <c r="D99" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="E99" s="111" t="s">
+      <c r="C99" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D99" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F99" s="118" t="s">
-        <v>331</v>
-      </c>
-      <c r="G99" s="112" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F99" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" s="33">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D100" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E100" s="1" t="s">
+      <c r="C100" s="112" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" s="113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E100" s="111" t="s">
         <v>237</v>
       </c>
-      <c r="F100" s="103" t="s">
-        <v>335</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>324</v>
+      <c r="F100" s="118" t="s">
+        <v>330</v>
+      </c>
+      <c r="G100" s="112" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="101" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6766,40 +6776,40 @@
         <v>84</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D101" s="1">
-        <v>1</v>
-      </c>
-      <c r="E101" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D101" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>237</v>
       </c>
       <c r="F101" s="103" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B102" s="33">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C102" s="104" t="s">
-        <v>351</v>
-      </c>
-      <c r="D102" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E102" s="117" t="s">
-        <v>331</v>
-      </c>
-      <c r="F102" s="106" t="s">
-        <v>17</v>
-      </c>
-      <c r="G102" s="107" t="s">
-        <v>332</v>
+      <c r="C102" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F102" s="103" t="s">
+        <v>328</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
@@ -6807,62 +6817,62 @@
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C103" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D103" s="90" t="s">
+      <c r="C103" s="104" t="s">
+        <v>350</v>
+      </c>
+      <c r="D103" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F103" s="1" t="s">
+      <c r="E103" s="117" t="s">
+        <v>330</v>
+      </c>
+      <c r="F103" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="107" t="s">
         <v>331</v>
       </c>
-      <c r="G103" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" s="33">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>271</v>
+        <v>362</v>
       </c>
       <c r="D104" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F104" s="103" t="s">
-        <v>371</v>
+        <v>237</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B105" s="33">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D105" s="1">
-        <v>2</v>
-      </c>
-      <c r="E105" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D105" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>238</v>
       </c>
       <c r="F105" s="103" t="s">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>398</v>
+        <v>271</v>
       </c>
     </row>
     <row r="106" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6871,28 +6881,28 @@
         <v>89</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="D106" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F106" s="103" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B107" s="33">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>267</v>
+        <v>399</v>
       </c>
       <c r="D107" s="1">
         <v>1</v>
@@ -6900,11 +6910,11 @@
       <c r="E107" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>80</v>
+      <c r="F107" s="103" t="s">
+        <v>341</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
@@ -6913,19 +6923,19 @@
         <v>91</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D108" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E108" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="G108" s="5" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
@@ -6934,19 +6944,19 @@
         <v>92</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>404</v>
+        <v>287</v>
       </c>
       <c r="D109" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F109" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="F109" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G109" s="5" t="s">
-        <v>409</v>
+        <v>288</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
@@ -6955,46 +6965,61 @@
         <v>93</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D110" s="90" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>401</v>
+        <v>238</v>
       </c>
       <c r="F110" s="103" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" s="33">
         <f>IF(C111="","",B110+1)</f>
         <v>94</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>311</v>
+        <v>393</v>
       </c>
       <c r="D111" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E111" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F111" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B112" s="33">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D112" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F111" s="103" t="s">
-        <v>400</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B112" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="F112" s="103" t="s">
+        <v>394</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.3">
@@ -7172,39 +7197,51 @@
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="K72:M72"/>
     <mergeCell ref="J57:L57"/>
@@ -7229,51 +7266,39 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:M40"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="Q59:S59"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7295,25 +7320,25 @@
   <sheetData>
     <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="102" t="s">
         <v>317</v>
       </c>
-      <c r="G2" s="102" t="s">
+      <c r="H2" s="102" t="s">
         <v>318</v>
-      </c>
-      <c r="H2" s="102" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F41185-97E6-4CA9-A1E6-D5C101061345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCF9F4A-A226-48D0-82EF-1D2A44E45546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="419">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1390,13 +1390,6 @@
   </si>
   <si>
     <t>u_alu_forward_b_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge
-o_d_mem_addr
-u_alu_forward_a_mux
-u_alu_forward_b_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1531,8 +1524,182 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>w_id_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_branch
+w_ex_ctr_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instruction Flush Signal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_pc_addr</t>
+  </si>
+  <si>
+    <t>w_id_pc_addr
+w_id_shift_left2_dec_jaddr</t>
+  </si>
+  <si>
+    <t>w_ex_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_id_ex_bridge
+u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Load Stall Flag Signal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_pc_mux
+u_if_id_bridge
+u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_control_unit
+u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_jump_mux
+u_alu_forward_a_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regdst_jal_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux
+u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd or $ra Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux
+u_memtoreg_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_control_unit
+u_id_ex_bridge
+u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_negative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Negative Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_branch_mux
+w_ex_ctr_flush</t>
+  </si>
+  <si>
+    <t>u_jump_mux
+w_ex_ctr_flush</t>
+  </si>
+  <si>
+    <t>w_ex_ctr_flush</t>
+  </si>
+  <si>
+    <t>w_ctr_load_stall</t>
+  </si>
+  <si>
+    <t>u_pc_stall_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_pc_stall_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-MEM RADDR (Next) (Not Applied Load Stall)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_i_mem_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (IF)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">u_addr_4_addr
+      <t xml:space="preserve">u_mem_wb_bridge
 </t>
     </r>
     <r>
@@ -1545,198 +1712,45 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>o_i_mem_addr</t>
+      <t>o_d_mem_addr</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
+        <family val="2"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-u_if_id_bridge</t>
+u_alu_forward_a_mux
+u_alu_forward_b_mux</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_branch
-w_ex_ctr_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instruction Flush Signal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_pc_addr</t>
-  </si>
-  <si>
-    <t>w_id_pc_addr
-w_id_shift_left2_dec_jaddr</t>
-  </si>
-  <si>
-    <t>w_if_i_pc_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_pc_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_load_stall_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_id_ex_bridge
-u_load_stall_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_load_stall_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Load Stall Flag Signal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_pc_mux
-u_if_id_bridge
-u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_control_unit
-u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_jump_mux
-u_alu_forward_a_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_ctr_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump Flag (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regdst_jal_mux_reg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_regdst_jal_mux
-u_wdata_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_regdst_jal_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rt or rd or $ra Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_pc_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_pc_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_ctr_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_regdst_jal_mux
-u_memtoreg_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_control_unit
-u_id_ex_bridge
-u_load_stall_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_negative</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Negative Out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_branch_mux
-w_ex_ctr_flush</t>
-  </si>
-  <si>
-    <t>u_jump_mux
-w_ex_ctr_flush</t>
-  </si>
-  <si>
-    <t>w_ex_ctr_flush</t>
-  </si>
-  <si>
-    <t>w_ctr_load_stall</t>
   </si>
   <si>
     <t>u_if_id_bridge
 u_id_ex_bridge
-u_pc_stall_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_pc_stall_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_pc_stall_mux_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I-MEM RADDR (Next) (Not Applied Load Stall)</t>
+u_pc_stall_mux
+u_i_mem_addr_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_id_ex_bridge
 w_id_jump_addr
-w_pc_stall_mux</t>
+u_i_mem_addr_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_i_mem_addr_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_addr_4_addr
+u_i_mem_addr_mux
+u_if_id_bridge
+u_pc_stall_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2362,7 +2376,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2649,9 +2663,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2719,6 +2730,15 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3155,32 +3175,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="133" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="135"/>
-      <c r="I2" s="119" t="s">
+      <c r="B2" s="135" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="137"/>
+      <c r="I2" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="121"/>
-      <c r="K2" s="119" t="s">
+      <c r="J2" s="123"/>
+      <c r="K2" s="121" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="120"/>
-      <c r="M2" s="121"/>
-      <c r="O2" s="119" t="s">
+      <c r="L2" s="122"/>
+      <c r="M2" s="123"/>
+      <c r="O2" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="119" t="s">
+      <c r="P2" s="123"/>
+      <c r="Q2" s="121" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="120"/>
-      <c r="S2" s="121"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="123"/>
     </row>
     <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="34" t="s">
@@ -3201,24 +3221,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="128" t="s">
+      <c r="I3" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="130" t="s">
+      <c r="J3" s="131"/>
+      <c r="K3" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="131"/>
-      <c r="M3" s="132"/>
-      <c r="O3" s="128" t="s">
+      <c r="L3" s="133"/>
+      <c r="M3" s="134"/>
+      <c r="O3" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="130" t="s">
+      <c r="P3" s="131"/>
+      <c r="Q3" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R3" s="131"/>
-      <c r="S3" s="132"/>
+      <c r="R3" s="133"/>
+      <c r="S3" s="134"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4" s="35">
@@ -3239,24 +3259,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="128" t="s">
+      <c r="I4" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="129"/>
-      <c r="K4" s="128" t="s">
+      <c r="J4" s="131"/>
+      <c r="K4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="142"/>
-      <c r="M4" s="129"/>
-      <c r="O4" s="128" t="s">
+      <c r="L4" s="144"/>
+      <c r="M4" s="131"/>
+      <c r="O4" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="128" t="s">
+      <c r="P4" s="131"/>
+      <c r="Q4" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="142"/>
-      <c r="S4" s="129"/>
+      <c r="R4" s="144"/>
+      <c r="S4" s="131"/>
     </row>
     <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54">
@@ -3277,24 +3297,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="122" t="s">
+      <c r="I5" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="123"/>
-      <c r="K5" s="124" t="s">
+      <c r="J5" s="125"/>
+      <c r="K5" s="126" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="125"/>
-      <c r="M5" s="126"/>
-      <c r="O5" s="122" t="s">
+      <c r="L5" s="127"/>
+      <c r="M5" s="128"/>
+      <c r="O5" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="124" t="s">
+      <c r="P5" s="125"/>
+      <c r="Q5" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="125"/>
-      <c r="S5" s="126"/>
+      <c r="R5" s="127"/>
+      <c r="S5" s="128"/>
     </row>
     <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="55">
@@ -3318,22 +3338,22 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="127" t="s">
+      <c r="J6" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="127" t="s">
+      <c r="P6" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="127"/>
+      <c r="Q6" s="129"/>
+      <c r="R6" s="129"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
@@ -3360,22 +3380,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="136" t="s">
+      <c r="J7" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="143" t="s">
+      <c r="P7" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="143"/>
-      <c r="R7" s="143"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="145"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
@@ -3417,11 +3437,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="125" t="s">
+      <c r="P8" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
@@ -3595,15 +3615,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="137" t="s">
+      <c r="I12" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="138"/>
-      <c r="K12" s="139" t="s">
+      <c r="J12" s="140"/>
+      <c r="K12" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="140"/>
-      <c r="M12" s="141"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="143"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3726,15 +3746,15 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="137" t="s">
+      <c r="O16" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="139" t="s">
+      <c r="P16" s="140"/>
+      <c r="Q16" s="141" t="s">
         <v>235</v>
       </c>
-      <c r="R16" s="140"/>
-      <c r="S16" s="141"/>
+      <c r="R16" s="142"/>
+      <c r="S16" s="143"/>
     </row>
     <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="90" t="s">
@@ -3756,44 +3776,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" ht="66" x14ac:dyDescent="0.3">
       <c r="B18" s="33">
         <f>IF(C18="","",1)</f>
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="F18" s="103" t="s">
-        <v>411</v>
+        <v>381</v>
+      </c>
+      <c r="F18" s="102" t="s">
+        <v>415</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="I18" s="119" t="s">
+        <v>382</v>
+      </c>
+      <c r="I18" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="J18" s="121"/>
-      <c r="K18" s="119" t="s">
+      <c r="J18" s="123"/>
+      <c r="K18" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="120"/>
-      <c r="M18" s="121"/>
-      <c r="O18" s="119" t="s">
+      <c r="L18" s="122"/>
+      <c r="M18" s="123"/>
+      <c r="O18" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="P18" s="121"/>
-      <c r="Q18" s="119" t="s">
+      <c r="P18" s="123"/>
+      <c r="Q18" s="121" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="120"/>
-      <c r="S18" s="121"/>
+      <c r="R18" s="122"/>
+      <c r="S18" s="123"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="33">
@@ -3815,24 +3835,24 @@
       <c r="G19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I19" s="128" t="s">
+      <c r="I19" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="129"/>
-      <c r="K19" s="130" t="s">
+      <c r="J19" s="131"/>
+      <c r="K19" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="131"/>
-      <c r="M19" s="132"/>
-      <c r="O19" s="128" t="s">
+      <c r="L19" s="133"/>
+      <c r="M19" s="134"/>
+      <c r="O19" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="129"/>
-      <c r="Q19" s="130" t="s">
+      <c r="P19" s="131"/>
+      <c r="Q19" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R19" s="131"/>
-      <c r="S19" s="132"/>
+      <c r="R19" s="133"/>
+      <c r="S19" s="134"/>
     </row>
     <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B20" s="33">
@@ -3848,30 +3868,30 @@
       <c r="E20" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="103" t="s">
+      <c r="F20" s="102" t="s">
         <v>75</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I20" s="128" t="s">
+      <c r="I20" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="129"/>
-      <c r="K20" s="130" t="s">
+      <c r="J20" s="131"/>
+      <c r="K20" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="131"/>
-      <c r="M20" s="132"/>
-      <c r="O20" s="128" t="s">
+      <c r="L20" s="133"/>
+      <c r="M20" s="134"/>
+      <c r="O20" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="128" t="s">
+      <c r="P20" s="131"/>
+      <c r="Q20" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="142"/>
-      <c r="S20" s="129"/>
+      <c r="R20" s="144"/>
+      <c r="S20" s="131"/>
     </row>
     <row r="21" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="33">
@@ -3879,7 +3899,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D21" s="90" t="s">
         <v>20</v>
@@ -3887,30 +3907,30 @@
       <c r="E21" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="F21" s="103" t="s">
+      <c r="F21" s="102" t="s">
         <v>75</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="I21" s="122" t="s">
+        <v>351</v>
+      </c>
+      <c r="I21" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="123"/>
-      <c r="K21" s="124" t="s">
+      <c r="J21" s="125"/>
+      <c r="K21" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="125"/>
-      <c r="M21" s="126"/>
-      <c r="O21" s="122" t="s">
+      <c r="L21" s="127"/>
+      <c r="M21" s="128"/>
+      <c r="O21" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="124" t="s">
+      <c r="P21" s="125"/>
+      <c r="Q21" s="126" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="125"/>
-      <c r="S21" s="126"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="128"/>
     </row>
     <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="33">
@@ -3918,7 +3938,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>20</v>
@@ -3926,31 +3946,31 @@
       <c r="E22" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F22" s="103" t="s">
+      <c r="F22" s="102" t="s">
         <v>329</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="127" t="s">
+      <c r="J22" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="129"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="127" t="s">
+      <c r="P22" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="Q22" s="127"/>
-      <c r="R22" s="127"/>
+      <c r="Q22" s="129"/>
+      <c r="R22" s="129"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
@@ -3961,7 +3981,7 @@
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -3973,27 +3993,27 @@
         <v>296</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="136" t="s">
+      <c r="J23" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="136"/>
-      <c r="L23" s="136"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="138"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="143" t="s">
+      <c r="P23" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="143"/>
-      <c r="R23" s="143"/>
+      <c r="Q23" s="145"/>
+      <c r="R23" s="145"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
@@ -4012,8 +4032,8 @@
       <c r="E24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="103" t="s">
-        <v>367</v>
+      <c r="F24" s="102" t="s">
+        <v>366</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>256</v>
@@ -4036,11 +4056,11 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="125" t="s">
+      <c r="P24" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="125"/>
-      <c r="R24" s="125"/>
+      <c r="Q24" s="127"/>
+      <c r="R24" s="127"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
@@ -4161,7 +4181,7 @@
       <c r="E27" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="103" t="s">
+      <c r="F27" s="102" t="s">
         <v>75</v>
       </c>
       <c r="G27" s="5" t="s">
@@ -4413,24 +4433,24 @@
       <c r="D32" s="1">
         <v>1</v>
       </c>
-      <c r="E32" s="102" t="s">
+      <c r="E32" s="101" t="s">
         <v>295</v>
       </c>
-      <c r="F32" s="103" t="s">
-        <v>407</v>
+      <c r="F32" s="102" t="s">
+        <v>404</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="137" t="s">
+      <c r="I32" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="138"/>
-      <c r="K32" s="139" t="s">
+      <c r="J32" s="140"/>
+      <c r="K32" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="140"/>
-      <c r="M32" s="141"/>
+      <c r="L32" s="142"/>
+      <c r="M32" s="143"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4453,19 +4473,19 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
-      <c r="E33" s="102" t="s">
-        <v>376</v>
-      </c>
-      <c r="F33" s="103" t="s">
-        <v>386</v>
+      <c r="E33" s="101" t="s">
+        <v>374</v>
+      </c>
+      <c r="F33" s="102" t="s">
+        <v>383</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
@@ -4497,8 +4517,8 @@
       <c r="E34" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F34" s="103" t="s">
-        <v>408</v>
+      <c r="F34" s="102" t="s">
+        <v>405</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>263</v>
@@ -4533,7 +4553,7 @@
       <c r="E35" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F35" s="103" t="s">
+      <c r="F35" s="102" t="s">
         <v>63</v>
       </c>
       <c r="G35" s="5" t="s">
@@ -4575,15 +4595,15 @@
       <c r="G36" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="O36" s="137" t="s">
+      <c r="O36" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="138"/>
-      <c r="Q36" s="139" t="s">
+      <c r="P36" s="140"/>
+      <c r="Q36" s="141" t="s">
         <v>236</v>
       </c>
-      <c r="R36" s="140"/>
-      <c r="S36" s="141"/>
+      <c r="R36" s="142"/>
+      <c r="S36" s="143"/>
     </row>
     <row r="37" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="33">
@@ -4599,7 +4619,7 @@
       <c r="E37" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F37" s="103" t="s">
+      <c r="F37" s="102" t="s">
         <v>63</v>
       </c>
       <c r="G37" s="5" t="s">
@@ -4620,30 +4640,30 @@
       <c r="E38" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F38" s="103" t="s">
-        <v>340</v>
+      <c r="F38" s="102" t="s">
+        <v>339</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="I38" s="119" t="s">
+      <c r="I38" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="J38" s="121"/>
-      <c r="K38" s="119" t="s">
+      <c r="J38" s="123"/>
+      <c r="K38" s="121" t="s">
         <v>122</v>
       </c>
-      <c r="L38" s="120"/>
-      <c r="M38" s="121"/>
-      <c r="O38" s="119" t="s">
+      <c r="L38" s="122"/>
+      <c r="M38" s="123"/>
+      <c r="O38" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="P38" s="121"/>
-      <c r="Q38" s="119" t="s">
+      <c r="P38" s="123"/>
+      <c r="Q38" s="121" t="s">
         <v>173</v>
       </c>
-      <c r="R38" s="120"/>
-      <c r="S38" s="121"/>
+      <c r="R38" s="122"/>
+      <c r="S38" s="123"/>
     </row>
     <row r="39" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B39" s="33">
@@ -4659,30 +4679,30 @@
       <c r="E39" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="102" t="s">
         <v>335</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="I39" s="128" t="s">
+      <c r="I39" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J39" s="129"/>
-      <c r="K39" s="130" t="s">
+      <c r="J39" s="131"/>
+      <c r="K39" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="131"/>
-      <c r="M39" s="132"/>
-      <c r="O39" s="128" t="s">
+      <c r="L39" s="133"/>
+      <c r="M39" s="134"/>
+      <c r="O39" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P39" s="129"/>
-      <c r="Q39" s="130" t="s">
+      <c r="P39" s="131"/>
+      <c r="Q39" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R39" s="131"/>
-      <c r="S39" s="132"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="134"/>
     </row>
     <row r="40" spans="2:19" ht="33" x14ac:dyDescent="0.3">
       <c r="B40" s="33">
@@ -4690,38 +4710,38 @@
         <v>23</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
-      <c r="E40" s="102" t="s">
-        <v>343</v>
-      </c>
-      <c r="F40" s="103" t="s">
-        <v>368</v>
+      <c r="E40" s="101" t="s">
+        <v>342</v>
+      </c>
+      <c r="F40" s="102" t="s">
+        <v>367</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="I40" s="128" t="s">
+        <v>359</v>
+      </c>
+      <c r="I40" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J40" s="129"/>
-      <c r="K40" s="130" t="s">
+      <c r="J40" s="131"/>
+      <c r="K40" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L40" s="131"/>
-      <c r="M40" s="132"/>
-      <c r="O40" s="128" t="s">
+      <c r="L40" s="133"/>
+      <c r="M40" s="134"/>
+      <c r="O40" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P40" s="129"/>
-      <c r="Q40" s="128" t="s">
+      <c r="P40" s="131"/>
+      <c r="Q40" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="142"/>
-      <c r="S40" s="129"/>
+      <c r="R40" s="144"/>
+      <c r="S40" s="131"/>
     </row>
     <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="33">
@@ -4743,24 +4763,24 @@
       <c r="G41" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="122" t="s">
+      <c r="I41" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="123"/>
-      <c r="K41" s="124" t="s">
+      <c r="J41" s="125"/>
+      <c r="K41" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="L41" s="125"/>
-      <c r="M41" s="126"/>
-      <c r="O41" s="122" t="s">
+      <c r="L41" s="127"/>
+      <c r="M41" s="128"/>
+      <c r="O41" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="123"/>
-      <c r="Q41" s="124" t="s">
+      <c r="P41" s="125"/>
+      <c r="Q41" s="126" t="s">
         <v>174</v>
       </c>
-      <c r="R41" s="125"/>
-      <c r="S41" s="126"/>
+      <c r="R41" s="127"/>
+      <c r="S41" s="128"/>
     </row>
     <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="33">
@@ -4770,10 +4790,10 @@
       <c r="C42" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D42" s="101" t="s">
+      <c r="D42" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="102" t="s">
+      <c r="E42" s="101" t="s">
         <v>233</v>
       </c>
       <c r="F42" s="2" t="s">
@@ -4785,22 +4805,22 @@
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="127" t="s">
+      <c r="J42" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="K42" s="127"/>
-      <c r="L42" s="127"/>
+      <c r="K42" s="129"/>
+      <c r="L42" s="129"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="127" t="s">
+      <c r="P42" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="Q42" s="127"/>
-      <c r="R42" s="127"/>
+      <c r="Q42" s="129"/>
+      <c r="R42" s="129"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
@@ -4810,7 +4830,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C43" s="97" t="s">
+      <c r="C43" s="96" t="s">
         <v>272</v>
       </c>
       <c r="D43" s="90" t="s">
@@ -4819,31 +4839,31 @@
       <c r="E43" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="98" t="s">
+      <c r="F43" s="97" t="s">
         <v>325</v>
       </c>
-      <c r="G43" s="99" t="s">
+      <c r="G43" s="98" t="s">
         <v>273</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="136" t="s">
+      <c r="J43" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="136"/>
-      <c r="L43" s="136"/>
+      <c r="K43" s="138"/>
+      <c r="L43" s="138"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="143" t="s">
+      <c r="P43" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="143"/>
-      <c r="R43" s="143"/>
+      <c r="Q43" s="145"/>
+      <c r="R43" s="145"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
@@ -4886,11 +4906,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="125" t="s">
+      <c r="P44" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="125"/>
-      <c r="R44" s="125"/>
+      <c r="Q44" s="127"/>
+      <c r="R44" s="127"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
@@ -4906,11 +4926,11 @@
       <c r="D45" s="1">
         <v>1</v>
       </c>
-      <c r="E45" s="114" t="s">
+      <c r="E45" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="F45" s="98" t="s">
-        <v>382</v>
+      <c r="F45" s="97" t="s">
+        <v>379</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>247</v>
@@ -4960,7 +4980,7 @@
       <c r="E46" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F46" s="103" t="s">
+      <c r="F46" s="102" t="s">
         <v>237</v>
       </c>
       <c r="G46" s="5" t="s">
@@ -5008,10 +5028,10 @@
       <c r="D47" s="1">
         <v>1</v>
       </c>
-      <c r="E47" s="114" t="s">
+      <c r="E47" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="F47" s="114" t="s">
+      <c r="F47" s="113" t="s">
         <v>237</v>
       </c>
       <c r="G47" s="5" t="s">
@@ -5054,7 +5074,7 @@
         <v>31</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D48" s="90" t="s">
         <v>21</v>
@@ -5062,21 +5082,21 @@
       <c r="E48" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F48" s="103" t="s">
+      <c r="F48" s="102" t="s">
         <v>253</v>
       </c>
-      <c r="G48" s="99" t="s">
+      <c r="G48" s="98" t="s">
         <v>194</v>
       </c>
-      <c r="I48" s="137" t="s">
+      <c r="I48" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="138"/>
-      <c r="K48" s="139" t="s">
+      <c r="J48" s="140"/>
+      <c r="K48" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="140"/>
-      <c r="M48" s="141"/>
+      <c r="L48" s="142"/>
+      <c r="M48" s="143"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5107,8 +5127,8 @@
       <c r="E49" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F49" s="103" t="s">
-        <v>388</v>
+      <c r="F49" s="102" t="s">
+        <v>385</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>219</v>
@@ -5130,23 +5150,23 @@
       </c>
     </row>
     <row r="50" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="116">
+      <c r="B50" s="115">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C50" s="112" t="s">
+      <c r="C50" s="111" t="s">
         <v>218</v>
       </c>
-      <c r="D50" s="113" t="s">
+      <c r="D50" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="111" t="s">
+      <c r="E50" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="F50" s="115" t="s">
-        <v>369</v>
-      </c>
-      <c r="G50" s="112" t="s">
+      <c r="F50" s="114" t="s">
+        <v>368</v>
+      </c>
+      <c r="G50" s="111" t="s">
         <v>220</v>
       </c>
       <c r="O50" s="83">
@@ -5179,21 +5199,21 @@
       <c r="E51" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F51" s="103" t="s">
-        <v>382</v>
+      <c r="F51" s="102" t="s">
+        <v>379</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="I51" s="119" t="s">
+      <c r="I51" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="J51" s="121"/>
-      <c r="K51" s="119" t="s">
+      <c r="J51" s="123"/>
+      <c r="K51" s="121" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="120"/>
-      <c r="M51" s="121"/>
+      <c r="L51" s="122"/>
+      <c r="M51" s="123"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
@@ -5224,21 +5244,21 @@
       <c r="E52" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F52" s="103" t="s">
+      <c r="F52" s="102" t="s">
         <v>237</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="I52" s="128" t="s">
+      <c r="I52" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="129"/>
-      <c r="K52" s="130" t="s">
+      <c r="J52" s="131"/>
+      <c r="K52" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="131"/>
-      <c r="M52" s="132"/>
+      <c r="L52" s="133"/>
+      <c r="M52" s="134"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5275,15 +5295,15 @@
       <c r="G53" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I53" s="128" t="s">
+      <c r="I53" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="129"/>
-      <c r="K53" s="130" t="s">
+      <c r="J53" s="131"/>
+      <c r="K53" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="131"/>
-      <c r="M53" s="132"/>
+      <c r="L53" s="133"/>
+      <c r="M53" s="134"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5320,15 +5340,15 @@
       <c r="G54" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I54" s="122" t="s">
+      <c r="I54" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="123"/>
-      <c r="K54" s="124" t="s">
+      <c r="J54" s="125"/>
+      <c r="K54" s="126" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="125"/>
-      <c r="M54" s="126"/>
+      <c r="L54" s="127"/>
+      <c r="M54" s="128"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5359,7 +5379,7 @@
       <c r="E55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="102" t="s">
         <v>48</v>
       </c>
       <c r="G55" s="5" t="s">
@@ -5368,11 +5388,11 @@
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="127" t="s">
+      <c r="J55" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="K55" s="127"/>
-      <c r="L55" s="127"/>
+      <c r="K55" s="129"/>
+      <c r="L55" s="129"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5398,40 +5418,40 @@
         <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D56" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>237</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="143" t="s">
+      <c r="J56" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="143"/>
-      <c r="L56" s="143"/>
+      <c r="K56" s="145"/>
+      <c r="L56" s="145"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="137" t="s">
+      <c r="O56" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="138"/>
-      <c r="Q56" s="139" t="s">
+      <c r="P56" s="140"/>
+      <c r="Q56" s="141" t="s">
         <v>237</v>
       </c>
-      <c r="R56" s="140"/>
-      <c r="S56" s="141"/>
+      <c r="R56" s="142"/>
+      <c r="S56" s="143"/>
     </row>
     <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="33">
@@ -5439,28 +5459,28 @@
         <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="G57" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="125" t="s">
+      <c r="J57" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="125"/>
-      <c r="L57" s="125"/>
+      <c r="K57" s="127"/>
+      <c r="L57" s="127"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
@@ -5471,19 +5491,19 @@
         <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="G58" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
@@ -5500,15 +5520,15 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="119" t="s">
+      <c r="O58" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="P58" s="121"/>
-      <c r="Q58" s="119" t="s">
+      <c r="P58" s="123"/>
+      <c r="Q58" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="120"/>
-      <c r="S58" s="121"/>
+      <c r="R58" s="122"/>
+      <c r="S58" s="123"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
@@ -5516,19 +5536,19 @@
         <v>42</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
@@ -5545,15 +5565,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="128" t="s">
+      <c r="O59" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="129"/>
-      <c r="Q59" s="130" t="s">
+      <c r="P59" s="131"/>
+      <c r="Q59" s="132" t="s">
         <v>232</v>
       </c>
-      <c r="R59" s="131"/>
-      <c r="S59" s="132"/>
+      <c r="R59" s="133"/>
+      <c r="S59" s="134"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B60" s="33">
@@ -5561,19 +5581,19 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
@@ -5590,15 +5610,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="128" t="s">
+      <c r="O60" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="129"/>
-      <c r="Q60" s="128" t="s">
+      <c r="P60" s="131"/>
+      <c r="Q60" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="142"/>
-      <c r="S60" s="129"/>
+      <c r="R60" s="144"/>
+      <c r="S60" s="131"/>
     </row>
     <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="33">
@@ -5606,19 +5626,19 @@
         <v>44</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D61" s="33">
         <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>330</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
@@ -5635,15 +5655,15 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="122" t="s">
+      <c r="O61" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="123"/>
-      <c r="Q61" s="124" t="s">
+      <c r="P61" s="125"/>
+      <c r="Q61" s="126" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="125"/>
-      <c r="S61" s="126"/>
+      <c r="R61" s="127"/>
+      <c r="S61" s="128"/>
     </row>
     <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="33">
@@ -5683,11 +5703,11 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="127" t="s">
+      <c r="P62" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="127"/>
-      <c r="R62" s="127"/>
+      <c r="Q62" s="129"/>
+      <c r="R62" s="129"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
@@ -5730,11 +5750,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="143" t="s">
+      <c r="P63" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="143"/>
-      <c r="R63" s="143"/>
+      <c r="Q63" s="145"/>
+      <c r="R63" s="145"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
@@ -5777,11 +5797,11 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="125" t="s">
+      <c r="P64" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="125"/>
-      <c r="R64" s="125"/>
+      <c r="Q64" s="127"/>
+      <c r="R64" s="127"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
@@ -5902,8 +5922,8 @@
       <c r="E67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="103" t="s">
-        <v>387</v>
+      <c r="F67" s="102" t="s">
+        <v>384</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>240</v>
@@ -5944,19 +5964,19 @@
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="C68" s="97" t="s">
+      <c r="C68" s="96" t="s">
         <v>274</v>
       </c>
-      <c r="D68" s="101" t="s">
+      <c r="D68" s="100" t="s">
         <v>45</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="98" t="s">
+      <c r="F68" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="G68" s="99" t="s">
+      <c r="G68" s="98" t="s">
         <v>50</v>
       </c>
       <c r="I68" s="83">
@@ -6106,8 +6126,8 @@
       <c r="E71" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="103" t="s">
-        <v>383</v>
+      <c r="F71" s="102" t="s">
+        <v>380</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>321</v>
@@ -6157,30 +6177,30 @@
       <c r="E72" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F72" s="103" t="s">
-        <v>404</v>
+      <c r="F72" s="102" t="s">
+        <v>401</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="I72" s="137" t="s">
+      <c r="I72" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="138"/>
-      <c r="K72" s="139" t="s">
+      <c r="J72" s="140"/>
+      <c r="K72" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="140"/>
-      <c r="M72" s="141"/>
-      <c r="O72" s="137" t="s">
+      <c r="L72" s="142"/>
+      <c r="M72" s="143"/>
+      <c r="O72" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="P72" s="138"/>
-      <c r="Q72" s="139" t="s">
+      <c r="P72" s="140"/>
+      <c r="Q72" s="141" t="s">
         <v>238</v>
       </c>
-      <c r="R72" s="140"/>
-      <c r="S72" s="141"/>
+      <c r="R72" s="142"/>
+      <c r="S72" s="143"/>
     </row>
     <row r="73" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B73" s="33">
@@ -6209,7 +6229,7 @@
         <v>57</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D74" s="1">
         <v>2</v>
@@ -6232,11 +6252,11 @@
       <c r="C75" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D75" s="101" t="s">
+      <c r="D75" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="E75" s="102" t="s">
-        <v>379</v>
+      <c r="E75" s="101" t="s">
+        <v>377</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>236</v>
@@ -6259,7 +6279,7 @@
       <c r="E76" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F76" s="114" t="s">
+      <c r="F76" s="113" t="s">
         <v>236</v>
       </c>
       <c r="G76" s="5" t="s">
@@ -6301,7 +6321,7 @@
       <c r="E78" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F78" s="114" t="s">
+      <c r="F78" s="113" t="s">
         <v>236</v>
       </c>
       <c r="G78" s="5" t="s">
@@ -6314,7 +6334,7 @@
         <v>62</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D79" s="90" t="s">
         <v>21</v>
@@ -6322,11 +6342,11 @@
       <c r="E79" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F79" s="103" t="s">
-        <v>415</v>
-      </c>
-      <c r="G79" s="99" t="s">
-        <v>401</v>
+      <c r="F79" s="102" t="s">
+        <v>416</v>
+      </c>
+      <c r="G79" s="98" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="2:19" x14ac:dyDescent="0.3">
@@ -6343,7 +6363,7 @@
       <c r="E80" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F80" s="111" t="s">
+      <c r="F80" s="110" t="s">
         <v>233</v>
       </c>
       <c r="G80" s="5" t="s">
@@ -6355,19 +6375,19 @@
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="C81" s="112" t="s">
+      <c r="C81" s="111" t="s">
         <v>204</v>
       </c>
-      <c r="D81" s="113" t="s">
+      <c r="D81" s="112" t="s">
         <v>20</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F81" s="111" t="s">
+      <c r="F81" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="G81" s="112" t="s">
+      <c r="G81" s="111" t="s">
         <v>206</v>
       </c>
     </row>
@@ -6421,7 +6441,7 @@
       <c r="C84" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D84" s="101" t="s">
+      <c r="D84" s="100" t="s">
         <v>46</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -6469,7 +6489,7 @@
       <c r="E86" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="103" t="s">
+      <c r="F86" s="102" t="s">
         <v>233</v>
       </c>
       <c r="G86" s="5" t="s">
@@ -6481,7 +6501,7 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C87" s="97" t="s">
+      <c r="C87" s="96" t="s">
         <v>190</v>
       </c>
       <c r="D87" s="90" t="s">
@@ -6490,10 +6510,10 @@
       <c r="E87" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="F87" s="98" t="s">
+      <c r="F87" s="97" t="s">
         <v>325</v>
       </c>
-      <c r="G87" s="99" t="s">
+      <c r="G87" s="98" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6502,62 +6522,62 @@
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C88" s="93" t="s">
-        <v>275</v>
-      </c>
-      <c r="D88" s="92">
-        <v>1</v>
-      </c>
-      <c r="E88" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F88" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" s="96" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="C88" s="118" t="s">
+        <v>412</v>
+      </c>
+      <c r="D88" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="E88" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="F88" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="120" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="33">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="C89" s="93" t="s">
-        <v>380</v>
-      </c>
-      <c r="D89" s="94" t="s">
-        <v>21</v>
+        <v>275</v>
+      </c>
+      <c r="D89" s="92">
+        <v>1</v>
       </c>
       <c r="E89" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="F89" s="95" t="s">
-        <v>374</v>
-      </c>
-      <c r="G89" s="96" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F89" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="95" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B90" s="33">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>324</v>
+      <c r="C90" s="96" t="s">
+        <v>411</v>
       </c>
       <c r="D90" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>414</v>
+      <c r="E90" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="F90" s="97" t="s">
+        <v>418</v>
+      </c>
+      <c r="G90" s="98" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -6566,61 +6586,61 @@
         <v>74</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>413</v>
+        <v>324</v>
       </c>
       <c r="D91" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>35</v>
+        <v>408</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="33">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C92" s="104" t="s">
-        <v>254</v>
-      </c>
-      <c r="D92" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E92" s="105" t="s">
-        <v>237</v>
-      </c>
-      <c r="F92" s="110" t="s">
-        <v>339</v>
-      </c>
-      <c r="G92" s="107" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C92" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D92" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B93" s="33">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D93" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E93" s="103" t="s">
+      <c r="C93" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="D93" s="108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F93" s="103" t="s">
-        <v>343</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>307</v>
+      <c r="F93" s="109" t="s">
+        <v>414</v>
+      </c>
+      <c r="G93" s="106" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
@@ -6629,19 +6649,19 @@
         <v>77</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D94" s="1">
-        <v>1</v>
-      </c>
-      <c r="E94" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D94" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E94" s="102" t="s">
         <v>237</v>
       </c>
-      <c r="F94" s="103" t="s">
-        <v>330</v>
+      <c r="F94" s="102" t="s">
+        <v>342</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>361</v>
+        <v>307</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -6650,19 +6670,19 @@
         <v>78</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>389</v>
+        <v>343</v>
       </c>
       <c r="D95" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>238</v>
+      <c r="F95" s="102" t="s">
+        <v>330</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -6670,20 +6690,20 @@
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="104" t="s">
-        <v>249</v>
-      </c>
-      <c r="D96" s="105">
-        <v>1</v>
-      </c>
-      <c r="E96" s="105" t="s">
+      <c r="C96" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D96" s="1">
+        <v>2</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="106" t="s">
-        <v>14</v>
-      </c>
-      <c r="G96" s="107" t="s">
-        <v>251</v>
+      <c r="F96" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
@@ -6691,62 +6711,62 @@
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D97" s="1">
+      <c r="C97" s="103" t="s">
+        <v>249</v>
+      </c>
+      <c r="D97" s="104">
         <v>1</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F97" s="105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" s="106" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="33">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C98" s="104" t="s">
-        <v>250</v>
-      </c>
-      <c r="D98" s="105">
+      <c r="C98" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D98" s="1">
         <v>1</v>
       </c>
-      <c r="E98" s="105" t="s">
+      <c r="E98" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F98" s="108" t="s">
-        <v>73</v>
-      </c>
-      <c r="G98" s="107" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F98" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B99" s="33">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="D99" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E99" s="2" t="s">
+      <c r="C99" s="103" t="s">
+        <v>250</v>
+      </c>
+      <c r="D99" s="104">
+        <v>1</v>
+      </c>
+      <c r="E99" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>402</v>
+      <c r="F99" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="G99" s="106" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
@@ -6754,41 +6774,41 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C100" s="112" t="s">
-        <v>258</v>
-      </c>
-      <c r="D100" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="111" t="s">
+      <c r="C100" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D100" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F100" s="118" t="s">
-        <v>330</v>
-      </c>
-      <c r="G100" s="112" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F100" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" s="33">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D101" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="C101" s="111" t="s">
+        <v>258</v>
+      </c>
+      <c r="D101" s="112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="F101" s="103" t="s">
-        <v>334</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>323</v>
+      <c r="F101" s="117" t="s">
+        <v>330</v>
+      </c>
+      <c r="G101" s="111" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6797,40 +6817,40 @@
         <v>85</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D102" s="1">
-        <v>1</v>
-      </c>
-      <c r="E102" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D102" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F102" s="103" t="s">
-        <v>328</v>
+      <c r="F102" s="102" t="s">
+        <v>334</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B103" s="33">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C103" s="104" t="s">
-        <v>350</v>
-      </c>
-      <c r="D103" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E103" s="117" t="s">
-        <v>330</v>
-      </c>
-      <c r="F103" s="106" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="107" t="s">
-        <v>331</v>
+      <c r="C103" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D103" s="1">
+        <v>1</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F103" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.3">
@@ -6838,62 +6858,62 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D104" s="90" t="s">
+      <c r="C104" s="103" t="s">
+        <v>349</v>
+      </c>
+      <c r="D104" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F104" s="1" t="s">
+      <c r="E104" s="116" t="s">
         <v>330</v>
       </c>
-      <c r="G104" s="5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="F104" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="106" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" s="33">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>270</v>
+        <v>361</v>
       </c>
       <c r="D105" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F105" s="103" t="s">
-        <v>370</v>
+        <v>237</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B106" s="33">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D106" s="1">
-        <v>2</v>
-      </c>
-      <c r="E106" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D106" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F106" s="103" t="s">
-        <v>400</v>
+      <c r="F106" s="102" t="s">
+        <v>369</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>392</v>
+        <v>271</v>
       </c>
     </row>
     <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -6902,28 +6922,28 @@
         <v>90</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="D107" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F107" s="103" t="s">
-        <v>341</v>
+      <c r="F107" s="102" t="s">
+        <v>397</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B108" s="33">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>266</v>
+        <v>396</v>
       </c>
       <c r="D108" s="1">
         <v>1</v>
@@ -6931,11 +6951,11 @@
       <c r="E108" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>80</v>
+      <c r="F108" s="102" t="s">
+        <v>340</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
@@ -6944,19 +6964,19 @@
         <v>92</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D109" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E109" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D109" s="1">
+        <v>1</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="G109" s="5" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
@@ -6965,19 +6985,19 @@
         <v>93</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>398</v>
+        <v>287</v>
       </c>
       <c r="D110" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F110" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="F110" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G110" s="5" t="s">
-        <v>403</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
@@ -6986,133 +7006,148 @@
         <v>94</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D111" s="90" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F111" s="103" t="s">
-        <v>62</v>
+        <v>238</v>
+      </c>
+      <c r="F111" s="102" t="s">
+        <v>80</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" s="33">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="D112" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E112" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F112" s="102" t="s">
+        <v>62</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B113" s="33">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D113" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F112" s="103" t="s">
-        <v>394</v>
-      </c>
-      <c r="G112" s="5" t="s">
+      <c r="F113" s="102" t="s">
+        <v>391</v>
+      </c>
+      <c r="G113" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B113" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B114" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B115" s="33" t="str">
         <f t="shared" ref="B115:B140" si="3">IF(C115="","",B114+1)</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B116" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B117" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B118" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B119" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B120" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B121" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B122" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B123" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B124" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B125" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B126" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B127" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B128" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -7334,10 +7369,10 @@
       <c r="F2" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G2" s="102" t="s">
+      <c r="G2" s="101" t="s">
         <v>317</v>
       </c>
-      <c r="H2" s="102" t="s">
+      <c r="H2" s="101" t="s">
         <v>318</v>
       </c>
     </row>
@@ -7905,7 +7940,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F28" s="111"/>
+      <c r="F28" s="110"/>
       <c r="G28" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8457,7 +8492,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F53" s="111"/>
+      <c r="F53" s="110"/>
       <c r="G53" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8791,7 +8826,7 @@
         <f t="shared" ref="E68:E84" si="7">MID(B68,C68,D68-C68)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F68" s="111"/>
+      <c r="F68" s="110"/>
       <c r="G68" s="1">
         <f t="shared" ref="G68:G84" si="8">COUNTIF($E$3:$E$100,F68)</f>
         <v>0</v>

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCF9F4A-A226-48D0-82EF-1D2A44E45546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{813C5046-60F0-40FF-AAC7-48B46C31F73B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
     <sheet name="정리용" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$17:$G$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$18:$G$141</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="421">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1753,11 +1752,19 @@
 u_pc_stall_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>o_d_mem_strb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRB_BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="177" formatCode="0&quot;일&quot;"/>
@@ -2376,7 +2383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2740,13 +2747,55 @@
     <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2758,28 +2807,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2791,28 +2822,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3148,61 +3158,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C55C11C-1620-411A-9B2F-3F513CAF246A}">
-  <dimension ref="B1:S140"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:S141"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="45.625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="2.625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="3.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="12.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="40.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="2.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="10.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="40.625" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.625" style="1"/>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="3.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.59765625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="45.59765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="2.59765625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="3.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="12.59765625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="40.59765625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="2.59765625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.59765625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.59765625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.59765625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.59765625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="40.59765625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.59765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="135" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="136"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="137"/>
-      <c r="I2" s="121" t="s">
+    <row r="1" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="143" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="145"/>
+      <c r="I2" s="122" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="123"/>
-      <c r="K2" s="121" t="s">
+      <c r="K2" s="122" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="122"/>
+      <c r="L2" s="124"/>
       <c r="M2" s="123"/>
-      <c r="O2" s="121" t="s">
+      <c r="O2" s="122" t="s">
         <v>102</v>
       </c>
       <c r="P2" s="123"/>
-      <c r="Q2" s="121" t="s">
+      <c r="Q2" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="122"/>
+      <c r="R2" s="124"/>
       <c r="S2" s="123"/>
     </row>
-    <row r="3" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="34" t="s">
         <v>41</v>
       </c>
@@ -3221,26 +3231,26 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="131"/>
-      <c r="K3" s="132" t="s">
+      <c r="J3" s="133"/>
+      <c r="K3" s="134" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="133"/>
-      <c r="M3" s="134"/>
-      <c r="O3" s="130" t="s">
+      <c r="L3" s="135"/>
+      <c r="M3" s="136"/>
+      <c r="O3" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="132" t="s">
+      <c r="P3" s="133"/>
+      <c r="Q3" s="134" t="s">
         <v>232</v>
       </c>
-      <c r="R3" s="133"/>
-      <c r="S3" s="134"/>
-    </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="R3" s="135"/>
+      <c r="S3" s="136"/>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B4" s="35">
         <v>1</v>
       </c>
@@ -3259,26 +3269,26 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="132" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="130" t="s">
+      <c r="J4" s="133"/>
+      <c r="K4" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="144"/>
-      <c r="M4" s="131"/>
-      <c r="O4" s="130" t="s">
+      <c r="L4" s="137"/>
+      <c r="M4" s="133"/>
+      <c r="O4" s="132" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="130" t="s">
+      <c r="P4" s="133"/>
+      <c r="Q4" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="144"/>
-      <c r="S4" s="131"/>
-    </row>
-    <row r="5" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R4" s="137"/>
+      <c r="S4" s="133"/>
+    </row>
+    <row r="5" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="54">
         <v>2</v>
       </c>
@@ -3297,26 +3307,26 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="124" t="s">
+      <c r="I5" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="125"/>
-      <c r="K5" s="126" t="s">
+      <c r="J5" s="139"/>
+      <c r="K5" s="140" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="127"/>
-      <c r="M5" s="128"/>
-      <c r="O5" s="124" t="s">
+      <c r="L5" s="121"/>
+      <c r="M5" s="141"/>
+      <c r="O5" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="125"/>
-      <c r="Q5" s="126" t="s">
+      <c r="P5" s="139"/>
+      <c r="Q5" s="140" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="127"/>
-      <c r="S5" s="128"/>
-    </row>
-    <row r="6" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R5" s="121"/>
+      <c r="S5" s="141"/>
+    </row>
+    <row r="6" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="55">
         <v>3</v>
       </c>
@@ -3338,27 +3348,27 @@
       <c r="I6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="129" t="s">
+      <c r="J6" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
       <c r="M6" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="129" t="s">
+      <c r="P6" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" s="129"/>
-      <c r="R6" s="129"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
       <c r="S6" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="37">
         <v>4</v>
       </c>
@@ -3380,27 +3390,27 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="138" t="s">
+      <c r="J7" s="142" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="138"/>
-      <c r="L7" s="138"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="142"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="145" t="s">
+      <c r="P7" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="145"/>
-      <c r="R7" s="145"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="56">
         <v>5</v>
       </c>
@@ -3437,16 +3447,16 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="127" t="s">
+      <c r="P8" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="127"/>
-      <c r="R8" s="127"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="121"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="57">
         <v>6</v>
       </c>
@@ -3496,7 +3506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B10" s="39">
         <v>7</v>
       </c>
@@ -3546,7 +3556,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="39">
         <v>8</v>
       </c>
@@ -3596,7 +3606,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="39">
         <v>9</v>
       </c>
@@ -3615,15 +3625,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="139" t="s">
+      <c r="I12" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="140"/>
-      <c r="K12" s="141" t="s">
+      <c r="J12" s="126"/>
+      <c r="K12" s="127" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="142"/>
-      <c r="M12" s="143"/>
+      <c r="L12" s="128"/>
+      <c r="M12" s="129"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3640,8 +3650,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="58">
+    <row r="13" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="146">
         <v>10</v>
       </c>
       <c r="C13" s="65" t="s">
@@ -3675,24 +3685,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B14" s="52">
+    <row r="14" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="58">
         <v>11</v>
       </c>
-      <c r="C14" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="59">
-        <v>1</v>
-      </c>
-      <c r="E14" s="21" t="s">
+      <c r="C14" s="65" t="s">
+        <v>419</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>420</v>
+      </c>
+      <c r="E14" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>30</v>
+      <c r="F14" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>29</v>
       </c>
       <c r="O14" s="76">
         <v>5</v>
@@ -3710,24 +3720,24 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="41">
+    <row r="15" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="52">
         <v>12</v>
       </c>
-      <c r="C15" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="60">
+      <c r="C15" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="59">
         <v>1</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>31</v>
+      <c r="G15" s="22" t="s">
+        <v>30</v>
       </c>
       <c r="O15" s="80">
         <v>6</v>
@@ -3745,298 +3755,296 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O16" s="139" t="s">
+    <row r="16" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="41">
+        <v>13</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="60">
+        <v>1</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="141" t="s">
+      <c r="P16" s="126"/>
+      <c r="Q16" s="127" t="s">
         <v>235</v>
       </c>
-      <c r="R16" s="142"/>
-      <c r="S16" s="143"/>
-    </row>
-    <row r="17" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="90" t="s">
+      <c r="R16" s="128"/>
+      <c r="S16" s="129"/>
+    </row>
+    <row r="17" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B18" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="90" t="s">
+      <c r="C18" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="90" t="s">
+      <c r="D18" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="90" t="s">
+      <c r="E18" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="91" t="s">
+      <c r="F18" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="91" t="s">
+      <c r="G18" s="91" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="2:19" ht="66" x14ac:dyDescent="0.3">
-      <c r="B18" s="33">
-        <f>IF(C18="","",1)</f>
+      <c r="I18" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" s="123"/>
+      <c r="K18" s="122" t="s">
+        <v>103</v>
+      </c>
+      <c r="L18" s="124"/>
+      <c r="M18" s="123"/>
+      <c r="O18" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="122" t="s">
+        <v>159</v>
+      </c>
+      <c r="R18" s="124"/>
+      <c r="S18" s="123"/>
+    </row>
+    <row r="19" spans="2:19" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="B19" s="33">
+        <f>IF(C19="","",1)</f>
         <v>1</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="F18" s="102" t="s">
-        <v>415</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="I18" s="121" t="s">
-        <v>102</v>
-      </c>
-      <c r="J18" s="123"/>
-      <c r="K18" s="121" t="s">
-        <v>103</v>
-      </c>
-      <c r="L18" s="122"/>
-      <c r="M18" s="123"/>
-      <c r="O18" s="121" t="s">
-        <v>102</v>
-      </c>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="121" t="s">
-        <v>159</v>
-      </c>
-      <c r="R18" s="122"/>
-      <c r="S18" s="123"/>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B19" s="33">
-        <f t="shared" ref="B19:B50" si="0">IF(C19="","",B18+1)</f>
-        <v>2</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F19" s="102" t="s">
+        <v>415</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="I19" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="133"/>
+      <c r="K19" s="134" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="135"/>
+      <c r="M19" s="136"/>
+      <c r="O19" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="P19" s="133"/>
+      <c r="Q19" s="134" t="s">
+        <v>232</v>
+      </c>
+      <c r="R19" s="135"/>
+      <c r="S19" s="136"/>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B20" s="33">
+        <f t="shared" ref="B20:B51" si="0">IF(C20="","",B19+1)</f>
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I19" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="J19" s="131"/>
-      <c r="K19" s="132" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" s="133"/>
-      <c r="M19" s="134"/>
-      <c r="O19" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="132" t="s">
-        <v>232</v>
-      </c>
-      <c r="R19" s="133"/>
-      <c r="S19" s="134"/>
-    </row>
-    <row r="20" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B20" s="33">
+      <c r="I20" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="J20" s="133"/>
+      <c r="K20" s="134" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" s="135"/>
+      <c r="M20" s="136"/>
+      <c r="O20" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="P20" s="133"/>
+      <c r="Q20" s="132" t="s">
+        <v>64</v>
+      </c>
+      <c r="R20" s="137"/>
+      <c r="S20" s="133"/>
+    </row>
+    <row r="21" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="33">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>4</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="F20" s="102" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="J20" s="131"/>
-      <c r="K20" s="132" t="s">
-        <v>107</v>
-      </c>
-      <c r="L20" s="133"/>
-      <c r="M20" s="134"/>
-      <c r="O20" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="130" t="s">
-        <v>64</v>
-      </c>
-      <c r="R20" s="144"/>
-      <c r="S20" s="131"/>
-    </row>
-    <row r="21" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="33">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="D21" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="F21" s="102" t="s">
         <v>75</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="I21" s="124" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="125"/>
-      <c r="K21" s="126" t="s">
+      <c r="J21" s="139"/>
+      <c r="K21" s="140" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="127"/>
-      <c r="M21" s="128"/>
-      <c r="O21" s="124" t="s">
+      <c r="L21" s="121"/>
+      <c r="M21" s="141"/>
+      <c r="O21" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="125"/>
-      <c r="Q21" s="126" t="s">
+      <c r="P21" s="139"/>
+      <c r="Q21" s="140" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="127"/>
-      <c r="S21" s="128"/>
-    </row>
-    <row r="22" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R21" s="121"/>
+      <c r="S21" s="141"/>
+    </row>
+    <row r="22" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B22" s="33">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D22" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F22" s="102" t="s">
-        <v>329</v>
+        <v>75</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="129" t="s">
+      <c r="J22" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="129"/>
-      <c r="L22" s="129"/>
+      <c r="K22" s="130"/>
+      <c r="L22" s="130"/>
       <c r="M22" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O22" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P22" s="129" t="s">
+      <c r="P22" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="Q22" s="129"/>
-      <c r="R22" s="129"/>
+      <c r="Q22" s="130"/>
+      <c r="R22" s="130"/>
       <c r="S22" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B23" s="33">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1</v>
+        <v>352</v>
+      </c>
+      <c r="D23" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>296</v>
+        <v>338</v>
+      </c>
+      <c r="F23" s="102" t="s">
+        <v>329</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>403</v>
+        <v>353</v>
       </c>
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="138" t="s">
+      <c r="J23" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="138"/>
-      <c r="L23" s="138"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="145" t="s">
+      <c r="P23" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="145"/>
-      <c r="R23" s="145"/>
+      <c r="Q23" s="131"/>
+      <c r="R23" s="131"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="33">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="90" t="s">
-        <v>20</v>
+        <v>402</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="102" t="s">
-        <v>366</v>
+      <c r="F24" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>256</v>
+        <v>403</v>
       </c>
       <c r="I24" s="67" t="s">
         <v>41</v>
@@ -4056,34 +4064,34 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="127" t="s">
+      <c r="P24" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="127"/>
-      <c r="R24" s="127"/>
+      <c r="Q24" s="121"/>
+      <c r="R24" s="121"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B25" s="33">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1</v>
+        <v>255</v>
+      </c>
+      <c r="D25" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>296</v>
+      <c r="F25" s="102" t="s">
+        <v>366</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="I25" s="72">
         <v>1</v>
@@ -4116,25 +4124,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B26" s="33">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>65</v>
+        <v>296</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="I26" s="76">
         <v>2</v>
@@ -4167,25 +4175,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B27" s="33">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D27" s="90" t="s">
-        <v>20</v>
+        <v>243</v>
+      </c>
+      <c r="D27" s="1">
+        <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F27" s="102" t="s">
-        <v>75</v>
+        <v>236</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="I27" s="83">
         <v>3</v>
@@ -4218,25 +4226,25 @@
         <v>155</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B28" s="33">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D28" s="1">
-        <v>3</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
+      </c>
+      <c r="D28" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="102" t="s">
+        <v>75</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="I28" s="83">
         <v>4</v>
@@ -4269,25 +4277,25 @@
         <v>161</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B29" s="33">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D29" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>40</v>
+        <v>260</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>53</v>
+        <v>296</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="I29" s="83">
         <v>5</v>
@@ -4320,25 +4328,25 @@
         <v>168</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B30" s="33">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="D30" s="90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G30" s="5" t="s">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="I30" s="83">
         <v>6</v>
@@ -4371,25 +4379,25 @@
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B31" s="33">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
+        <v>294</v>
+      </c>
+      <c r="D31" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>226</v>
+        <v>88</v>
       </c>
       <c r="I31" s="80">
         <v>7</v>
@@ -4422,35 +4430,35 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B32" s="33">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>296</v>
+        <v>225</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
-      <c r="E32" s="101" t="s">
-        <v>295</v>
-      </c>
-      <c r="F32" s="102" t="s">
-        <v>404</v>
+      <c r="E32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I32" s="139" t="s">
+        <v>226</v>
+      </c>
+      <c r="I32" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="140"/>
-      <c r="K32" s="141" t="s">
+      <c r="J32" s="126"/>
+      <c r="K32" s="127" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="142"/>
-      <c r="M32" s="143"/>
+      <c r="L32" s="128"/>
+      <c r="M32" s="129"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4467,25 +4475,25 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B33" s="33">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>406</v>
+        <v>296</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="101" t="s">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="F33" s="102" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>375</v>
+        <v>89</v>
       </c>
       <c r="O33" s="83">
         <v>8</v>
@@ -4503,25 +4511,25 @@
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:19" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B34" s="33">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>262</v>
+        <v>406</v>
       </c>
       <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>236</v>
+        <v>1</v>
+      </c>
+      <c r="E34" s="101" t="s">
+        <v>374</v>
       </c>
       <c r="F34" s="102" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>263</v>
+        <v>375</v>
       </c>
       <c r="O34" s="83">
         <v>9</v>
@@ -4539,25 +4547,25 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B35" s="33">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>236</v>
       </c>
       <c r="F35" s="102" t="s">
-        <v>63</v>
+        <v>405</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O35" s="80">
         <v>10</v>
@@ -4575,64 +4583,64 @@
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B36" s="33">
         <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F36" s="102" t="s">
+        <v>63</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="O36" s="125" t="s">
+        <v>104</v>
+      </c>
+      <c r="P36" s="126"/>
+      <c r="Q36" s="127" t="s">
+        <v>236</v>
+      </c>
+      <c r="R36" s="128"/>
+      <c r="S36" s="129"/>
+    </row>
+    <row r="37" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B37" s="33">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D37" s="1">
         <v>6</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="O36" s="139" t="s">
-        <v>104</v>
-      </c>
-      <c r="P36" s="140"/>
-      <c r="Q36" s="141" t="s">
-        <v>236</v>
-      </c>
-      <c r="R36" s="142"/>
-      <c r="S36" s="143"/>
-    </row>
-    <row r="37" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="33">
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B38" s="33">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="D37" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F37" s="102" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B38" s="33">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="D38" s="90" t="s">
         <v>56</v>
@@ -4641,37 +4649,37 @@
         <v>236</v>
       </c>
       <c r="F38" s="102" t="s">
-        <v>339</v>
+        <v>63</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="I38" s="121" t="s">
+        <v>306</v>
+      </c>
+      <c r="I38" s="122" t="s">
         <v>102</v>
       </c>
       <c r="J38" s="123"/>
-      <c r="K38" s="121" t="s">
+      <c r="K38" s="122" t="s">
         <v>122</v>
       </c>
-      <c r="L38" s="122"/>
+      <c r="L38" s="124"/>
       <c r="M38" s="123"/>
-      <c r="O38" s="121" t="s">
+      <c r="O38" s="122" t="s">
         <v>102</v>
       </c>
       <c r="P38" s="123"/>
-      <c r="Q38" s="121" t="s">
+      <c r="Q38" s="122" t="s">
         <v>173</v>
       </c>
-      <c r="R38" s="122"/>
+      <c r="R38" s="124"/>
       <c r="S38" s="123"/>
     </row>
-    <row r="39" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B39" s="33">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="D39" s="90" t="s">
         <v>56</v>
@@ -4680,213 +4688,213 @@
         <v>236</v>
       </c>
       <c r="F39" s="102" t="s">
+        <v>339</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="I39" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="J39" s="133"/>
+      <c r="K39" s="134" t="s">
+        <v>123</v>
+      </c>
+      <c r="L39" s="135"/>
+      <c r="M39" s="136"/>
+      <c r="O39" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="P39" s="133"/>
+      <c r="Q39" s="134" t="s">
+        <v>232</v>
+      </c>
+      <c r="R39" s="135"/>
+      <c r="S39" s="136"/>
+    </row>
+    <row r="40" spans="2:19" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B40" s="33">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D40" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F40" s="102" t="s">
         <v>335</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="I39" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="J39" s="131"/>
-      <c r="K39" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="L39" s="133"/>
-      <c r="M39" s="134"/>
-      <c r="O39" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="132" t="s">
-        <v>232</v>
-      </c>
-      <c r="R39" s="133"/>
-      <c r="S39" s="134"/>
-    </row>
-    <row r="40" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B40" s="33">
+      <c r="I40" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="J40" s="133"/>
+      <c r="K40" s="134" t="s">
+        <v>107</v>
+      </c>
+      <c r="L40" s="135"/>
+      <c r="M40" s="136"/>
+      <c r="O40" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="P40" s="133"/>
+      <c r="Q40" s="132" t="s">
+        <v>64</v>
+      </c>
+      <c r="R40" s="137"/>
+      <c r="S40" s="133"/>
+    </row>
+    <row r="41" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B41" s="33">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D41" s="1">
         <v>1</v>
       </c>
-      <c r="E40" s="101" t="s">
+      <c r="E41" s="101" t="s">
         <v>342</v>
       </c>
-      <c r="F40" s="102" t="s">
+      <c r="F41" s="102" t="s">
         <v>367</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="I40" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="J40" s="131"/>
-      <c r="K40" s="132" t="s">
-        <v>107</v>
-      </c>
-      <c r="L40" s="133"/>
-      <c r="M40" s="134"/>
-      <c r="O40" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="P40" s="131"/>
-      <c r="Q40" s="130" t="s">
+      <c r="I41" s="138" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="139"/>
+      <c r="K41" s="140" t="s">
+        <v>125</v>
+      </c>
+      <c r="L41" s="121"/>
+      <c r="M41" s="141"/>
+      <c r="O41" s="138" t="s">
+        <v>8</v>
+      </c>
+      <c r="P41" s="139"/>
+      <c r="Q41" s="140" t="s">
+        <v>174</v>
+      </c>
+      <c r="R41" s="121"/>
+      <c r="S41" s="141"/>
+    </row>
+    <row r="42" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="33">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D42" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="144"/>
-      <c r="S40" s="131"/>
-    </row>
-    <row r="41" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="33">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D41" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="I41" s="124" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="125"/>
-      <c r="K41" s="126" t="s">
-        <v>125</v>
-      </c>
-      <c r="L41" s="127"/>
-      <c r="M41" s="128"/>
-      <c r="O41" s="124" t="s">
-        <v>8</v>
-      </c>
-      <c r="P41" s="125"/>
-      <c r="Q41" s="126" t="s">
-        <v>174</v>
-      </c>
-      <c r="R41" s="127"/>
-      <c r="S41" s="128"/>
-    </row>
-    <row r="42" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="33">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D42" s="100" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="101" t="s">
-        <v>233</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="I42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="129" t="s">
+      <c r="J42" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="K42" s="129"/>
-      <c r="L42" s="129"/>
+      <c r="K42" s="130"/>
+      <c r="L42" s="130"/>
       <c r="M42" s="69" t="s">
         <v>8</v>
       </c>
       <c r="O42" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P42" s="129" t="s">
+      <c r="P42" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="Q42" s="129"/>
-      <c r="R42" s="129"/>
+      <c r="Q42" s="130"/>
+      <c r="R42" s="130"/>
       <c r="S42" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B43" s="33">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C43" s="96" t="s">
-        <v>272</v>
-      </c>
-      <c r="D43" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D43" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="101" t="s">
+        <v>233</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="97" t="s">
-        <v>325</v>
-      </c>
-      <c r="G43" s="98" t="s">
-        <v>273</v>
+      <c r="G43" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="138" t="s">
+      <c r="J43" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="138"/>
-      <c r="L43" s="138"/>
+      <c r="K43" s="142"/>
+      <c r="L43" s="142"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="145" t="s">
+      <c r="P43" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="145"/>
-      <c r="R43" s="145"/>
+      <c r="Q43" s="131"/>
+      <c r="R43" s="131"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B44" s="33">
         <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>293</v>
+        <v>26</v>
+      </c>
+      <c r="C44" s="96" t="s">
+        <v>272</v>
       </c>
       <c r="D44" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>87</v>
+        <v>21</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="97" t="s">
+        <v>325</v>
+      </c>
+      <c r="G44" s="98" t="s">
+        <v>273</v>
       </c>
       <c r="I44" s="67" t="s">
         <v>41</v>
@@ -4906,34 +4914,34 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="127" t="s">
+      <c r="P44" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="127"/>
-      <c r="R44" s="127"/>
+      <c r="Q44" s="121"/>
+      <c r="R44" s="121"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B45" s="33">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="113" t="s">
-        <v>236</v>
-      </c>
-      <c r="F45" s="97" t="s">
-        <v>379</v>
+        <v>293</v>
+      </c>
+      <c r="D45" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="I45" s="72">
         <v>1</v>
@@ -4966,25 +4974,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B46" s="33">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="F46" s="102" t="s">
-        <v>237</v>
+      <c r="F46" s="97" t="s">
+        <v>379</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="I46" s="76">
         <v>2</v>
@@ -5017,25 +5025,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B47" s="33">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
       </c>
-      <c r="E47" s="113" t="s">
+      <c r="E47" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F47" s="113" t="s">
+      <c r="F47" s="102" t="s">
         <v>237</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="I47" s="80">
         <v>3</v>
@@ -5068,35 +5076,35 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B48" s="33">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D48" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F48" s="102" t="s">
-        <v>253</v>
-      </c>
-      <c r="G48" s="98" t="s">
-        <v>194</v>
-      </c>
-      <c r="I48" s="139" t="s">
+        <v>246</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+      <c r="E48" s="113" t="s">
+        <v>236</v>
+      </c>
+      <c r="F48" s="113" t="s">
+        <v>237</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I48" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="140"/>
-      <c r="K48" s="141" t="s">
+      <c r="J48" s="126"/>
+      <c r="K48" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="142"/>
-      <c r="M48" s="143"/>
+      <c r="L48" s="128"/>
+      <c r="M48" s="129"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5113,25 +5121,25 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B49" s="33">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>217</v>
+        <v>378</v>
       </c>
       <c r="D49" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>233</v>
       </c>
       <c r="F49" s="102" t="s">
-        <v>385</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>219</v>
+        <v>253</v>
+      </c>
+      <c r="G49" s="98" t="s">
+        <v>194</v>
       </c>
       <c r="O49" s="83">
         <v>4</v>
@@ -5149,25 +5157,25 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="115">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C50" s="111" t="s">
-        <v>218</v>
-      </c>
-      <c r="D50" s="112" t="s">
+    <row r="50" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B50" s="33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D50" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="110" t="s">
+      <c r="E50" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F50" s="114" t="s">
-        <v>368</v>
-      </c>
-      <c r="G50" s="111" t="s">
-        <v>220</v>
+      <c r="F50" s="102" t="s">
+        <v>385</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="O50" s="83">
         <v>5</v>
@@ -5185,34 +5193,34 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B51" s="33">
-        <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
-        <v>34</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D51" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" s="102" t="s">
-        <v>379</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="I51" s="121" t="s">
+    <row r="51" spans="2:19" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B51" s="115">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C51" s="111" t="s">
+        <v>218</v>
+      </c>
+      <c r="D51" s="112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="110" t="s">
+        <v>233</v>
+      </c>
+      <c r="F51" s="114" t="s">
+        <v>368</v>
+      </c>
+      <c r="G51" s="111" t="s">
+        <v>220</v>
+      </c>
+      <c r="I51" s="122" t="s">
         <v>102</v>
       </c>
       <c r="J51" s="123"/>
-      <c r="K51" s="121" t="s">
+      <c r="K51" s="122" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="122"/>
+      <c r="L51" s="124"/>
       <c r="M51" s="123"/>
       <c r="O51" s="83">
         <v>6</v>
@@ -5230,35 +5238,35 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B52" s="33">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f t="shared" ref="B52:B83" si="1">IF(C52="","",B51+1)</f>
+        <v>34</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>236</v>
+        <v>332</v>
+      </c>
+      <c r="D52" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="F52" s="102" t="s">
-        <v>237</v>
+        <v>379</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="I52" s="130" t="s">
+        <v>333</v>
+      </c>
+      <c r="I52" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="131"/>
-      <c r="K52" s="132" t="s">
+      <c r="J52" s="133"/>
+      <c r="K52" s="134" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="133"/>
-      <c r="M52" s="134"/>
+      <c r="L52" s="135"/>
+      <c r="M52" s="136"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5275,35 +5283,35 @@
         <v>182</v>
       </c>
     </row>
-    <row r="53" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B53" s="33">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D53" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>278</v>
+        <v>297</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F53" s="102" t="s">
+        <v>237</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="I53" s="130" t="s">
+        <v>298</v>
+      </c>
+      <c r="I53" s="132" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="131"/>
-      <c r="K53" s="132" t="s">
+      <c r="J53" s="133"/>
+      <c r="K53" s="134" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="133"/>
-      <c r="M53" s="134"/>
+      <c r="L53" s="135"/>
+      <c r="M53" s="136"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5320,35 +5328,35 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B54" s="33">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D54" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D54" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G54" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I54" s="124" t="s">
+        <v>54</v>
+      </c>
+      <c r="I54" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="125"/>
-      <c r="K54" s="126" t="s">
+      <c r="J54" s="139"/>
+      <c r="K54" s="140" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="127"/>
-      <c r="M54" s="128"/>
+      <c r="L54" s="121"/>
+      <c r="M54" s="141"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5365,34 +5373,34 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B55" s="33">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="D55" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F55" s="102" t="s">
-        <v>48</v>
+        <v>277</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="I55" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="J55" s="129" t="s">
+      <c r="J55" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="K55" s="129"/>
-      <c r="L55" s="129"/>
+      <c r="K55" s="130"/>
+      <c r="L55" s="130"/>
       <c r="M55" s="69" t="s">
         <v>8</v>
       </c>
@@ -5412,86 +5420,86 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B56" s="33">
         <f t="shared" si="1"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>370</v>
+        <v>221</v>
       </c>
       <c r="D56" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
+      </c>
+      <c r="F56" s="102" t="s">
+        <v>48</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>371</v>
+        <v>223</v>
       </c>
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="145" t="s">
+      <c r="J56" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="145"/>
-      <c r="L56" s="145"/>
+      <c r="K56" s="131"/>
+      <c r="L56" s="131"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="139" t="s">
+      <c r="O56" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="140"/>
-      <c r="Q56" s="141" t="s">
+      <c r="P56" s="126"/>
+      <c r="Q56" s="127" t="s">
         <v>237</v>
       </c>
-      <c r="R56" s="142"/>
-      <c r="S56" s="143"/>
-    </row>
-    <row r="57" spans="2:19" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R56" s="128"/>
+      <c r="S56" s="129"/>
+    </row>
+    <row r="57" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B57" s="33">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D57" s="1">
-        <v>1</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
+      </c>
+      <c r="D57" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="127" t="s">
+      <c r="J57" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="127"/>
-      <c r="L57" s="127"/>
+      <c r="K57" s="121"/>
+      <c r="L57" s="121"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="58" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B58" s="33">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
@@ -5503,7 +5511,7 @@
         <v>363</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I58" s="67" t="s">
         <v>41</v>
@@ -5520,23 +5528,23 @@
       <c r="M58" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="121" t="s">
+      <c r="O58" s="122" t="s">
         <v>102</v>
       </c>
       <c r="P58" s="123"/>
-      <c r="Q58" s="121" t="s">
+      <c r="Q58" s="122" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="122"/>
+      <c r="R58" s="124"/>
       <c r="S58" s="123"/>
     </row>
-    <row r="59" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B59" s="33">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -5545,10 +5553,10 @@
         <v>362</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I59" s="72">
         <v>1</v>
@@ -5565,23 +5573,23 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="130" t="s">
+      <c r="O59" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="131"/>
-      <c r="Q59" s="132" t="s">
+      <c r="P59" s="133"/>
+      <c r="Q59" s="134" t="s">
         <v>232</v>
       </c>
-      <c r="R59" s="133"/>
-      <c r="S59" s="134"/>
-    </row>
-    <row r="60" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="R59" s="135"/>
+      <c r="S59" s="136"/>
+    </row>
+    <row r="60" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B60" s="33">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
@@ -5593,7 +5601,7 @@
         <v>364</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I60" s="76">
         <v>2</v>
@@ -5610,35 +5618,35 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="130" t="s">
+      <c r="O60" s="132" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="131"/>
-      <c r="Q60" s="130" t="s">
+      <c r="P60" s="133"/>
+      <c r="Q60" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="144"/>
-      <c r="S60" s="131"/>
-    </row>
-    <row r="61" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R60" s="137"/>
+      <c r="S60" s="133"/>
+    </row>
+    <row r="61" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B61" s="33">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D61" s="33">
+        <v>347</v>
+      </c>
+      <c r="D61" s="1">
         <v>1</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>342</v>
+      <c r="E61" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I61" s="83">
         <v>3</v>
@@ -5655,35 +5663,35 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="124" t="s">
+      <c r="O61" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="125"/>
-      <c r="Q61" s="126" t="s">
+      <c r="P61" s="139"/>
+      <c r="Q61" s="140" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="127"/>
-      <c r="S61" s="128"/>
-    </row>
-    <row r="62" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R61" s="121"/>
+      <c r="S61" s="141"/>
+    </row>
+    <row r="62" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B62" s="33">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D62" s="90" t="s">
-        <v>20</v>
+        <v>348</v>
+      </c>
+      <c r="D62" s="33">
+        <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>234</v>
+        <v>342</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>44</v>
+        <v>330</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>193</v>
+        <v>358</v>
       </c>
       <c r="I62" s="83">
         <v>4</v>
@@ -5703,34 +5711,34 @@
       <c r="O62" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="P62" s="129" t="s">
+      <c r="P62" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="Q62" s="129"/>
-      <c r="R62" s="129"/>
+      <c r="Q62" s="130"/>
+      <c r="R62" s="130"/>
       <c r="S62" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B63" s="33">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D63" s="1">
-        <v>4</v>
+        <v>192</v>
+      </c>
+      <c r="D63" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>236</v>
+        <v>44</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="I63" s="83">
         <v>5</v>
@@ -5750,25 +5758,25 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="145" t="s">
+      <c r="P63" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="145"/>
-      <c r="R63" s="145"/>
+      <c r="Q63" s="131"/>
+      <c r="R63" s="131"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="64" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B64" s="33">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>58</v>
@@ -5777,7 +5785,7 @@
         <v>236</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I64" s="83">
         <v>6</v>
@@ -5797,34 +5805,34 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="127" t="s">
+      <c r="P64" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="127"/>
-      <c r="R64" s="127"/>
+      <c r="Q64" s="121"/>
+      <c r="R64" s="121"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="2:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B65" s="33">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D65" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I65" s="83">
         <v>7</v>
@@ -5857,25 +5865,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B66" s="33">
         <f t="shared" si="1"/>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D66" s="90" t="s">
-        <v>57</v>
+        <v>196</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="I66" s="83">
         <v>8</v>
@@ -5908,25 +5916,25 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B67" s="33">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D67" s="1">
-        <v>6</v>
+        <v>285</v>
+      </c>
+      <c r="D67" s="90" t="s">
+        <v>57</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="102" t="s">
-        <v>384</v>
+      <c r="F67" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>240</v>
+        <v>61</v>
       </c>
       <c r="I67" s="83">
         <v>9</v>
@@ -5959,25 +5967,25 @@
         <v>155</v>
       </c>
     </row>
-    <row r="68" spans="2:19" ht="33" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B68" s="33">
         <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="C68" s="96" t="s">
-        <v>274</v>
-      </c>
-      <c r="D68" s="100" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D68" s="1">
+        <v>6</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="97" t="s">
-        <v>42</v>
-      </c>
-      <c r="G68" s="98" t="s">
-        <v>50</v>
+      <c r="F68" s="102" t="s">
+        <v>384</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="I68" s="83">
         <v>10</v>
@@ -6010,25 +6018,25 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B69" s="33">
         <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D69" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="E69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C69" s="96" t="s">
+        <v>274</v>
+      </c>
+      <c r="D69" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E69" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>59</v>
+      <c r="F69" s="97" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" s="98" t="s">
+        <v>50</v>
       </c>
       <c r="I69" s="83">
         <v>11</v>
@@ -6061,25 +6069,25 @@
         <v>181</v>
       </c>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B70" s="33">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D70" s="90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>301</v>
+        <v>59</v>
       </c>
       <c r="I70" s="83">
         <v>12</v>
@@ -6112,13 +6120,13 @@
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="2:19" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B71" s="33">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D71" s="90" t="s">
         <v>56</v>
@@ -6126,11 +6134,11 @@
       <c r="E71" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="102" t="s">
-        <v>380</v>
+      <c r="F71" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="I71" s="80">
         <v>13</v>
@@ -6163,13 +6171,13 @@
         <v>189</v>
       </c>
     </row>
-    <row r="72" spans="2:19" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:19" ht="52.8" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B72" s="33">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D72" s="90" t="s">
         <v>56</v>
@@ -6178,121 +6186,121 @@
         <v>44</v>
       </c>
       <c r="F72" s="102" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="I72" s="139" t="s">
+        <v>321</v>
+      </c>
+      <c r="I72" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="140"/>
-      <c r="K72" s="141" t="s">
+      <c r="J72" s="126"/>
+      <c r="K72" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="142"/>
-      <c r="M72" s="143"/>
-      <c r="O72" s="139" t="s">
+      <c r="L72" s="128"/>
+      <c r="M72" s="129"/>
+      <c r="O72" s="125" t="s">
         <v>104</v>
       </c>
-      <c r="P72" s="140"/>
-      <c r="Q72" s="141" t="s">
+      <c r="P72" s="126"/>
+      <c r="Q72" s="127" t="s">
         <v>238</v>
       </c>
-      <c r="R72" s="142"/>
-      <c r="S72" s="143"/>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="R72" s="128"/>
+      <c r="S72" s="129"/>
+    </row>
+    <row r="73" spans="2:19" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B73" s="33">
         <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D73" s="90" t="s">
         <v>56</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D73" s="1">
-        <v>5</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="F73" s="102" t="s">
+        <v>401</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B74" s="33">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D74" s="1">
+        <v>5</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="G74" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B74" s="33">
+    <row r="75" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B75" s="33">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D75" s="1">
         <v>2</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="75" spans="2:19" ht="33" x14ac:dyDescent="0.3">
-      <c r="B75" s="33">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D75" s="100" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75" s="101" t="s">
-        <v>377</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>236</v>
       </c>
       <c r="G75" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B76" s="33">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D76" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="101" t="s">
+        <v>377</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G76" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B76" s="33">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B77" s="33">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="D76" s="1">
-        <v>1</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F76" s="113" t="s">
-        <v>236</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B77" s="33">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -6300,20 +6308,20 @@
       <c r="E77" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>233</v>
+      <c r="F77" s="113" t="s">
+        <v>236</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="78" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B78" s="33">
         <f t="shared" si="1"/>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D78" s="1">
         <v>1</v>
@@ -6321,64 +6329,64 @@
       <c r="E78" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F78" s="113" t="s">
+      <c r="F78" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B79" s="33">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F79" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G79" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="79" spans="2:19" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B79" s="33">
+    <row r="80" spans="2:19" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B80" s="33">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D79" s="90" t="s">
+      <c r="D80" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F79" s="102" t="s">
+      <c r="F80" s="102" t="s">
         <v>416</v>
       </c>
-      <c r="G79" s="98" t="s">
+      <c r="G80" s="98" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B80" s="33">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B81" s="33">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D80" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F80" s="110" t="s">
-        <v>233</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B81" s="33">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-      <c r="C81" s="111" t="s">
-        <v>204</v>
-      </c>
-      <c r="D81" s="112" t="s">
+      <c r="D81" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -6387,38 +6395,38 @@
       <c r="F81" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="G81" s="111" t="s">
+      <c r="G81" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B82" s="33">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="C82" s="111" t="s">
+        <v>204</v>
+      </c>
+      <c r="D82" s="112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F82" s="110" t="s">
+        <v>233</v>
+      </c>
+      <c r="G82" s="111" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B82" s="33">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B83" s="33">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="D82" s="1">
-        <v>1</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B83" s="33">
-        <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
-        <v>66</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -6426,545 +6434,545 @@
       <c r="E83" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="F83" s="1" t="s">
         <v>236</v>
       </c>
       <c r="G83" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B84" s="33">
+        <f t="shared" ref="B84:B115" si="2">IF(C84="","",B83+1)</f>
+        <v>66</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G84" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B84" s="33">
+    <row r="85" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B85" s="33">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D84" s="100" t="s">
+      <c r="D85" s="100" t="s">
         <v>46</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="G85" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B85" s="33">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B86" s="33">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D86" s="1">
         <v>1</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G85" s="5" t="s">
+      <c r="G86" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B86" s="33">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B87" s="33">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D86" s="90" t="s">
+      <c r="D87" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F86" s="102" t="s">
+      <c r="F87" s="102" t="s">
         <v>233</v>
       </c>
-      <c r="G86" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B87" s="33">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B88" s="33">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C87" s="96" t="s">
+      <c r="C88" s="96" t="s">
         <v>190</v>
       </c>
-      <c r="D87" s="90" t="s">
+      <c r="D88" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E87" s="33" t="s">
+      <c r="E88" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="F87" s="97" t="s">
+      <c r="F88" s="97" t="s">
         <v>325</v>
       </c>
-      <c r="G87" s="98" t="s">
+      <c r="G88" s="98" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B88" s="33">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B89" s="33">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C88" s="118" t="s">
+      <c r="C89" s="118" t="s">
         <v>412</v>
       </c>
-      <c r="D88" s="94" t="s">
+      <c r="D89" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="E88" s="119" t="s">
+      <c r="E89" s="119" t="s">
         <v>417</v>
       </c>
-      <c r="F88" s="99" t="s">
+      <c r="F89" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="120" t="s">
+      <c r="G89" s="120" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B89" s="33">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B90" s="33">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C89" s="93" t="s">
+      <c r="C90" s="93" t="s">
         <v>275</v>
       </c>
-      <c r="D89" s="92">
+      <c r="D90" s="92">
         <v>1</v>
       </c>
-      <c r="E89" s="92" t="s">
+      <c r="E90" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="F89" s="99" t="s">
+      <c r="F90" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="G89" s="95" t="s">
+      <c r="G90" s="95" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="90" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B90" s="33">
+    <row r="91" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="B91" s="33">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C90" s="96" t="s">
+      <c r="C91" s="96" t="s">
         <v>411</v>
       </c>
-      <c r="D90" s="90" t="s">
+      <c r="D91" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E90" s="33" t="s">
+      <c r="E91" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="F90" s="97" t="s">
+      <c r="F91" s="97" t="s">
         <v>418</v>
       </c>
-      <c r="G90" s="98" t="s">
+      <c r="G91" s="98" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B91" s="33">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B92" s="33">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D91" s="90" t="s">
+      <c r="D92" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G92" s="5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B92" s="33">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B93" s="33">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D92" s="90" t="s">
+      <c r="D93" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G93" s="5" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="93" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B93" s="33">
+    <row r="94" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="B94" s="33">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C93" s="103" t="s">
+      <c r="C94" s="103" t="s">
         <v>254</v>
       </c>
-      <c r="D93" s="108" t="s">
+      <c r="D94" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="E93" s="104" t="s">
+      <c r="E94" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F93" s="109" t="s">
+      <c r="F94" s="109" t="s">
         <v>414</v>
       </c>
-      <c r="G93" s="106" t="s">
+      <c r="G94" s="106" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B94" s="33">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B95" s="33">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D94" s="90" t="s">
+      <c r="D95" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E94" s="102" t="s">
+      <c r="E95" s="102" t="s">
         <v>237</v>
       </c>
-      <c r="F94" s="102" t="s">
+      <c r="F95" s="102" t="s">
         <v>342</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G95" s="5" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B95" s="33">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B96" s="33">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D96" s="1">
         <v>1</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F95" s="102" t="s">
+      <c r="F96" s="102" t="s">
         <v>330</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="G96" s="5" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B96" s="33">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B97" s="33">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D96" s="1">
+      <c r="D97" s="1">
         <v>2</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G97" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B97" s="33">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B98" s="33">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C97" s="103" t="s">
+      <c r="C98" s="103" t="s">
         <v>249</v>
       </c>
-      <c r="D97" s="104">
+      <c r="D98" s="104">
         <v>1</v>
       </c>
-      <c r="E97" s="104" t="s">
+      <c r="E98" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F97" s="105" t="s">
+      <c r="F98" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="G97" s="106" t="s">
+      <c r="G98" s="106" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B98" s="33">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B99" s="33">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D99" s="1">
         <v>1</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G99" s="5" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="99" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B99" s="33">
+    <row r="100" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B100" s="33">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C99" s="103" t="s">
+      <c r="C100" s="103" t="s">
         <v>250</v>
       </c>
-      <c r="D99" s="104">
+      <c r="D100" s="104">
         <v>1</v>
       </c>
-      <c r="E99" s="104" t="s">
+      <c r="E100" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F99" s="107" t="s">
+      <c r="F100" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="G99" s="106" t="s">
+      <c r="G100" s="106" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B100" s="33">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B101" s="33">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="D100" s="90" t="s">
+      <c r="D101" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G101" s="5" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B101" s="33">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B102" s="33">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C101" s="111" t="s">
+      <c r="C102" s="111" t="s">
         <v>258</v>
       </c>
-      <c r="D101" s="112" t="s">
+      <c r="D102" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="E101" s="110" t="s">
+      <c r="E102" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="F101" s="117" t="s">
+      <c r="F102" s="117" t="s">
         <v>330</v>
       </c>
-      <c r="G101" s="111" t="s">
+      <c r="G102" s="111" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="102" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B102" s="33">
+    <row r="103" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B103" s="33">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D102" s="90" t="s">
+      <c r="D103" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F102" s="102" t="s">
+      <c r="F103" s="102" t="s">
         <v>334</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G103" s="5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="103" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B103" s="33">
+    <row r="104" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B104" s="33">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D104" s="1">
         <v>1</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F103" s="102" t="s">
+      <c r="F104" s="102" t="s">
         <v>328</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G104" s="5" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B104" s="33">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B105" s="33">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="C104" s="103" t="s">
+      <c r="C105" s="103" t="s">
         <v>349</v>
       </c>
-      <c r="D104" s="108" t="s">
+      <c r="D105" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="E104" s="116" t="s">
+      <c r="E105" s="116" t="s">
         <v>330</v>
       </c>
-      <c r="F104" s="105" t="s">
+      <c r="F105" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="G104" s="106" t="s">
+      <c r="G105" s="106" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B105" s="33">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B106" s="33">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D105" s="90" t="s">
+      <c r="D106" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F106" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G106" s="5" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="106" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B106" s="33">
+    <row r="107" spans="2:7" ht="87" x14ac:dyDescent="0.4">
+      <c r="B107" s="33">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C107" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D106" s="90" t="s">
+      <c r="D107" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F106" s="102" t="s">
+      <c r="F107" s="102" t="s">
         <v>369</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G107" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="107" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B107" s="33">
+    <row r="108" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B108" s="33">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D108" s="1">
         <v>2</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="E108" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F107" s="102" t="s">
+      <c r="F108" s="102" t="s">
         <v>397</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="G108" s="5" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="108" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B108" s="33">
+    <row r="109" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B109" s="33">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="D108" s="1">
-        <v>1</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F108" s="102" t="s">
-        <v>340</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B109" s="33">
-        <f>IF(C109="","",B108+1)</f>
-        <v>92</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D109" s="1">
         <v>1</v>
@@ -6972,275 +6980,356 @@
       <c r="E109" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>80</v>
+      <c r="F109" s="102" t="s">
+        <v>340</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B110" s="33">
         <f>IF(C110="","",B109+1)</f>
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D110" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E110" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D110" s="1">
+        <v>1</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="G110" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B111" s="33">
         <f>IF(C111="","",B110+1)</f>
+        <v>93</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D111" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B112" s="33">
+        <f>IF(C112="","",B111+1)</f>
         <v>94</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D111" s="90" t="s">
+      <c r="D112" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E112" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F111" s="102" t="s">
+      <c r="F112" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="G112" s="5" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B112" s="33">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B113" s="33">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C113" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D112" s="90" t="s">
+      <c r="D113" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E113" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F112" s="102" t="s">
+      <c r="F113" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="G113" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="113" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B113" s="33">
+    <row r="114" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B114" s="33">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D113" s="90" t="s">
+      <c r="D114" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F113" s="102" t="s">
+      <c r="F114" s="102" t="s">
         <v>391</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="G114" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B114" s="33" t="str">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B115" s="33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B115" s="33" t="str">
-        <f t="shared" ref="B115:B140" si="3">IF(C115="","",B114+1)</f>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B116" s="33" t="str">
+        <f t="shared" ref="B116:B141" si="3">IF(C116="","",B115+1)</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B116" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B117" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B118" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B119" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B120" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B121" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B122" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B123" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B124" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B125" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B126" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B127" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B128" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B129" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B130" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B131" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B132" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B133" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B134" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B135" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B136" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B137" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B138" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B139" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B140" s="33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B141" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="C17:G140" xr:uid="{4C55C11C-1620-411A-9B2F-3F513CAF246A}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C18:G140">
+  <autoFilter ref="C18:G141">
+    <sortState ref="C18:G140">
       <sortCondition ref="C17:C140"/>
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="O72:P72"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="P8:R8"/>
@@ -7265,95 +7354,36 @@
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="J55:L55"/>
-    <mergeCell ref="J56:L56"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3AACD3-19B9-4F27-A163-F65AFD95CDAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H84"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.19921875" style="3" customWidth="1"/>
     <col min="3" max="4" width="9" style="1"/>
-    <col min="5" max="6" width="30.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="30.59765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.59765625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>312</v>
       </c>
@@ -7376,7 +7406,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C3" s="1" t="e">
         <f>FIND("w_",B3)</f>
         <v>#VALUE!</v>
@@ -7398,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C4" s="1" t="e">
         <f t="shared" ref="C4:C67" si="0">FIND("w_",B4)</f>
         <v>#VALUE!</v>
@@ -7420,7 +7450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C5" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7442,7 +7472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C6" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7464,7 +7494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C7" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7486,7 +7516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C8" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7508,7 +7538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C9" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7530,7 +7560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C10" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7552,7 +7582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C11" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7574,7 +7604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C12" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7596,7 +7626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C13" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7618,7 +7648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C14" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7640,7 +7670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C15" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7662,7 +7692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C16" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7684,7 +7714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C17" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7706,7 +7736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C18" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7728,7 +7758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C19" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7750,7 +7780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C20" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7772,7 +7802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C21" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7794,7 +7824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C22" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7817,7 +7847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C23" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7839,7 +7869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C24" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7861,7 +7891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C25" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7883,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C26" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7905,7 +7935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C27" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7927,7 +7957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C28" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7950,7 +7980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C29" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7972,7 +8002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C30" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -7994,7 +8024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C31" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8016,7 +8046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C32" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8038,7 +8068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C33" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8060,7 +8090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C34" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8082,7 +8112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C35" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8104,7 +8134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C36" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8126,7 +8156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C37" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8148,7 +8178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C38" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8170,7 +8200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C39" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8192,7 +8222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C40" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8214,7 +8244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C41" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8236,7 +8266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C42" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8259,7 +8289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C43" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8281,7 +8311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C44" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8303,7 +8333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C45" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8325,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C46" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8347,7 +8377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C47" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8369,7 +8399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C48" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8391,7 +8421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C49" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8413,7 +8443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C50" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8435,7 +8465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C51" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8457,7 +8487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C52" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8479,7 +8509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C53" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8502,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C54" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8524,7 +8554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C55" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8546,7 +8576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C56" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8568,7 +8598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C57" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8590,7 +8620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C58" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8613,7 +8643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C59" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8636,7 +8666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C60" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8659,7 +8689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C61" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8681,7 +8711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C62" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8703,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C63" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8725,7 +8755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C64" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8747,7 +8777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C65" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8769,7 +8799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C66" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8791,7 +8821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C67" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
@@ -8813,7 +8843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C68" s="1" t="e">
         <f t="shared" ref="C68:C84" si="5">FIND("w_",B68)</f>
         <v>#VALUE!</v>
@@ -8836,7 +8866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C69" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -8858,7 +8888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C70" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -8880,7 +8910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C71" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -8902,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C72" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -8924,7 +8954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C73" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -8946,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C74" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -8968,7 +8998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C75" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -8990,7 +9020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C76" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9012,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C77" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9034,7 +9064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C78" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9056,7 +9086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C79" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9078,7 +9108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C80" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9100,7 +9130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C81" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9122,7 +9152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C82" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9144,7 +9174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C83" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
@@ -9166,7 +9196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:8" x14ac:dyDescent="0.4">
       <c r="C84" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="429">
   <si>
     <t>top_cpu</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1758,6 +1758,38 @@
   </si>
   <si>
     <t>STRB_BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_memrstrb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRB_BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_control_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemRead Strobe (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_memwstrb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemWrite Strobe (ID)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2383,7 +2415,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2747,16 +2779,61 @@
     <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2774,56 +2851,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3185,32 +3220,32 @@
   <sheetData>
     <row r="1" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="145"/>
+      <c r="B2" s="136" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="138"/>
       <c r="I2" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="123"/>
+      <c r="J2" s="124"/>
       <c r="K2" s="122" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="124"/>
-      <c r="M2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="124"/>
       <c r="O2" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="123"/>
+      <c r="P2" s="124"/>
       <c r="Q2" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="R2" s="124"/>
-      <c r="S2" s="123"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="124"/>
     </row>
     <row r="3" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="34" t="s">
@@ -3231,24 +3266,24 @@
       <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="132" t="s">
+      <c r="I3" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="133"/>
-      <c r="K3" s="134" t="s">
+      <c r="J3" s="132"/>
+      <c r="K3" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="135"/>
-      <c r="M3" s="136"/>
-      <c r="O3" s="132" t="s">
+      <c r="L3" s="134"/>
+      <c r="M3" s="135"/>
+      <c r="O3" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="134" t="s">
+      <c r="P3" s="132"/>
+      <c r="Q3" s="133" t="s">
         <v>232</v>
       </c>
-      <c r="R3" s="135"/>
-      <c r="S3" s="136"/>
+      <c r="R3" s="134"/>
+      <c r="S3" s="135"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B4" s="35">
@@ -3269,24 +3304,24 @@
       <c r="G4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="132" t="s">
+      <c r="I4" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="133"/>
-      <c r="K4" s="132" t="s">
+      <c r="J4" s="132"/>
+      <c r="K4" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="137"/>
-      <c r="M4" s="133"/>
-      <c r="O4" s="132" t="s">
+      <c r="L4" s="145"/>
+      <c r="M4" s="132"/>
+      <c r="O4" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="132" t="s">
+      <c r="P4" s="132"/>
+      <c r="Q4" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="137"/>
-      <c r="S4" s="133"/>
+      <c r="R4" s="145"/>
+      <c r="S4" s="132"/>
     </row>
     <row r="5" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="54">
@@ -3307,24 +3342,24 @@
       <c r="G5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="138" t="s">
+      <c r="I5" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="139"/>
-      <c r="K5" s="140" t="s">
+      <c r="J5" s="126"/>
+      <c r="K5" s="127" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="121"/>
-      <c r="M5" s="141"/>
-      <c r="O5" s="138" t="s">
+      <c r="L5" s="128"/>
+      <c r="M5" s="129"/>
+      <c r="O5" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="139"/>
-      <c r="Q5" s="140" t="s">
+      <c r="P5" s="126"/>
+      <c r="Q5" s="127" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="121"/>
-      <c r="S5" s="141"/>
+      <c r="R5" s="128"/>
+      <c r="S5" s="129"/>
     </row>
     <row r="6" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="55">
@@ -3390,22 +3425,22 @@
       <c r="I7" s="70">
         <v>1</v>
       </c>
-      <c r="J7" s="142" t="s">
+      <c r="J7" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
       <c r="M7" s="71" t="s">
         <v>132</v>
       </c>
       <c r="O7" s="87">
         <v>1</v>
       </c>
-      <c r="P7" s="131" t="s">
+      <c r="P7" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
+      <c r="Q7" s="146"/>
+      <c r="R7" s="146"/>
       <c r="S7" s="88" t="s">
         <v>132</v>
       </c>
@@ -3447,11 +3482,11 @@
       <c r="O8" s="80">
         <v>2</v>
       </c>
-      <c r="P8" s="121" t="s">
+      <c r="P8" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="121"/>
-      <c r="R8" s="121"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
       <c r="S8" s="82" t="s">
         <v>133</v>
       </c>
@@ -3625,15 +3660,15 @@
       <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="125" t="s">
+      <c r="I12" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="126"/>
-      <c r="K12" s="127" t="s">
+      <c r="J12" s="141"/>
+      <c r="K12" s="142" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="128"/>
-      <c r="M12" s="129"/>
+      <c r="L12" s="143"/>
+      <c r="M12" s="144"/>
       <c r="O12" s="72">
         <v>3</v>
       </c>
@@ -3650,11 +3685,11 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="146">
+    <row r="13" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B13" s="121">
         <v>10</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="147" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="50" t="s">
@@ -3774,15 +3809,15 @@
       <c r="G16" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="125" t="s">
+      <c r="O16" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="P16" s="126"/>
-      <c r="Q16" s="127" t="s">
+      <c r="P16" s="141"/>
+      <c r="Q16" s="142" t="s">
         <v>235</v>
       </c>
-      <c r="R16" s="128"/>
-      <c r="S16" s="129"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="144"/>
     </row>
     <row r="17" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="18" spans="2:19" x14ac:dyDescent="0.4">
@@ -3807,21 +3842,21 @@
       <c r="I18" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="J18" s="123"/>
+      <c r="J18" s="124"/>
       <c r="K18" s="122" t="s">
         <v>103</v>
       </c>
-      <c r="L18" s="124"/>
-      <c r="M18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="124"/>
       <c r="O18" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="P18" s="123"/>
+      <c r="P18" s="124"/>
       <c r="Q18" s="122" t="s">
         <v>159</v>
       </c>
-      <c r="R18" s="124"/>
-      <c r="S18" s="123"/>
+      <c r="R18" s="123"/>
+      <c r="S18" s="124"/>
     </row>
     <row r="19" spans="2:19" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B19" s="33">
@@ -3843,24 +3878,24 @@
       <c r="G19" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="I19" s="132" t="s">
+      <c r="I19" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="J19" s="133"/>
-      <c r="K19" s="134" t="s">
+      <c r="J19" s="132"/>
+      <c r="K19" s="133" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="135"/>
-      <c r="M19" s="136"/>
-      <c r="O19" s="132" t="s">
+      <c r="L19" s="134"/>
+      <c r="M19" s="135"/>
+      <c r="O19" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="133"/>
-      <c r="Q19" s="134" t="s">
+      <c r="P19" s="132"/>
+      <c r="Q19" s="133" t="s">
         <v>232</v>
       </c>
-      <c r="R19" s="135"/>
-      <c r="S19" s="136"/>
+      <c r="R19" s="134"/>
+      <c r="S19" s="135"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B20" s="33">
@@ -3882,24 +3917,24 @@
       <c r="G20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I20" s="132" t="s">
+      <c r="I20" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="133"/>
-      <c r="K20" s="134" t="s">
+      <c r="J20" s="132"/>
+      <c r="K20" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="L20" s="135"/>
-      <c r="M20" s="136"/>
-      <c r="O20" s="132" t="s">
+      <c r="L20" s="134"/>
+      <c r="M20" s="135"/>
+      <c r="O20" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="P20" s="133"/>
-      <c r="Q20" s="132" t="s">
+      <c r="P20" s="132"/>
+      <c r="Q20" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="R20" s="137"/>
-      <c r="S20" s="133"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="132"/>
     </row>
     <row r="21" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="33">
@@ -3921,24 +3956,24 @@
       <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I21" s="138" t="s">
+      <c r="I21" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="139"/>
-      <c r="K21" s="140" t="s">
+      <c r="J21" s="126"/>
+      <c r="K21" s="127" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="121"/>
-      <c r="M21" s="141"/>
-      <c r="O21" s="138" t="s">
+      <c r="L21" s="128"/>
+      <c r="M21" s="129"/>
+      <c r="O21" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="140" t="s">
+      <c r="P21" s="126"/>
+      <c r="Q21" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="R21" s="121"/>
-      <c r="S21" s="141"/>
+      <c r="R21" s="128"/>
+      <c r="S21" s="129"/>
     </row>
     <row r="22" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B22" s="33">
@@ -4006,22 +4041,22 @@
       <c r="I23" s="70">
         <v>1</v>
       </c>
-      <c r="J23" s="142" t="s">
+      <c r="J23" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="K23" s="142"/>
-      <c r="L23" s="142"/>
+      <c r="K23" s="139"/>
+      <c r="L23" s="139"/>
       <c r="M23" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O23" s="87">
         <v>1</v>
       </c>
-      <c r="P23" s="131" t="s">
+      <c r="P23" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="131"/>
+      <c r="Q23" s="146"/>
+      <c r="R23" s="146"/>
       <c r="S23" s="88" t="s">
         <v>132</v>
       </c>
@@ -4064,11 +4099,11 @@
       <c r="O24" s="80">
         <v>2</v>
       </c>
-      <c r="P24" s="121" t="s">
+      <c r="P24" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="121"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
       <c r="S24" s="82" t="s">
         <v>133</v>
       </c>
@@ -4450,15 +4485,15 @@
       <c r="G32" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="I32" s="125" t="s">
+      <c r="I32" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="J32" s="126"/>
-      <c r="K32" s="127" t="s">
+      <c r="J32" s="141"/>
+      <c r="K32" s="142" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="128"/>
-      <c r="M32" s="129"/>
+      <c r="L32" s="143"/>
+      <c r="M32" s="144"/>
       <c r="O32" s="83">
         <v>7</v>
       </c>
@@ -4603,15 +4638,15 @@
       <c r="G36" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="O36" s="125" t="s">
+      <c r="O36" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="P36" s="126"/>
-      <c r="Q36" s="127" t="s">
+      <c r="P36" s="141"/>
+      <c r="Q36" s="142" t="s">
         <v>236</v>
       </c>
-      <c r="R36" s="128"/>
-      <c r="S36" s="129"/>
+      <c r="R36" s="143"/>
+      <c r="S36" s="144"/>
     </row>
     <row r="37" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B37" s="33">
@@ -4657,21 +4692,21 @@
       <c r="I38" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="J38" s="123"/>
+      <c r="J38" s="124"/>
       <c r="K38" s="122" t="s">
         <v>122</v>
       </c>
-      <c r="L38" s="124"/>
-      <c r="M38" s="123"/>
+      <c r="L38" s="123"/>
+      <c r="M38" s="124"/>
       <c r="O38" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="P38" s="123"/>
+      <c r="P38" s="124"/>
       <c r="Q38" s="122" t="s">
         <v>173</v>
       </c>
-      <c r="R38" s="124"/>
-      <c r="S38" s="123"/>
+      <c r="R38" s="123"/>
+      <c r="S38" s="124"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B39" s="33">
@@ -4693,24 +4728,24 @@
       <c r="G39" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="I39" s="132" t="s">
+      <c r="I39" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="J39" s="133"/>
-      <c r="K39" s="134" t="s">
+      <c r="J39" s="132"/>
+      <c r="K39" s="133" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="135"/>
-      <c r="M39" s="136"/>
-      <c r="O39" s="132" t="s">
+      <c r="L39" s="134"/>
+      <c r="M39" s="135"/>
+      <c r="O39" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="P39" s="133"/>
-      <c r="Q39" s="134" t="s">
+      <c r="P39" s="132"/>
+      <c r="Q39" s="133" t="s">
         <v>232</v>
       </c>
-      <c r="R39" s="135"/>
-      <c r="S39" s="136"/>
+      <c r="R39" s="134"/>
+      <c r="S39" s="135"/>
     </row>
     <row r="40" spans="2:19" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B40" s="33">
@@ -4732,24 +4767,24 @@
       <c r="G40" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="I40" s="132" t="s">
+      <c r="I40" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="J40" s="133"/>
-      <c r="K40" s="134" t="s">
+      <c r="J40" s="132"/>
+      <c r="K40" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="L40" s="135"/>
-      <c r="M40" s="136"/>
-      <c r="O40" s="132" t="s">
+      <c r="L40" s="134"/>
+      <c r="M40" s="135"/>
+      <c r="O40" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="P40" s="133"/>
-      <c r="Q40" s="132" t="s">
+      <c r="P40" s="132"/>
+      <c r="Q40" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="R40" s="137"/>
-      <c r="S40" s="133"/>
+      <c r="R40" s="145"/>
+      <c r="S40" s="132"/>
     </row>
     <row r="41" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B41" s="33">
@@ -4771,24 +4806,24 @@
       <c r="G41" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="I41" s="138" t="s">
+      <c r="I41" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="139"/>
-      <c r="K41" s="140" t="s">
+      <c r="J41" s="126"/>
+      <c r="K41" s="127" t="s">
         <v>125</v>
       </c>
-      <c r="L41" s="121"/>
-      <c r="M41" s="141"/>
-      <c r="O41" s="138" t="s">
+      <c r="L41" s="128"/>
+      <c r="M41" s="129"/>
+      <c r="O41" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="P41" s="139"/>
-      <c r="Q41" s="140" t="s">
+      <c r="P41" s="126"/>
+      <c r="Q41" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="R41" s="121"/>
-      <c r="S41" s="141"/>
+      <c r="R41" s="128"/>
+      <c r="S41" s="129"/>
     </row>
     <row r="42" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B42" s="33">
@@ -4856,22 +4891,22 @@
       <c r="I43" s="70">
         <v>1</v>
       </c>
-      <c r="J43" s="142" t="s">
+      <c r="J43" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="142"/>
-      <c r="L43" s="142"/>
+      <c r="K43" s="139"/>
+      <c r="L43" s="139"/>
       <c r="M43" s="71" t="s">
         <v>133</v>
       </c>
       <c r="O43" s="87">
         <v>1</v>
       </c>
-      <c r="P43" s="131" t="s">
+      <c r="P43" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="Q43" s="131"/>
-      <c r="R43" s="131"/>
+      <c r="Q43" s="146"/>
+      <c r="R43" s="146"/>
       <c r="S43" s="88" t="s">
         <v>132</v>
       </c>
@@ -4914,11 +4949,11 @@
       <c r="O44" s="80">
         <v>2</v>
       </c>
-      <c r="P44" s="121" t="s">
+      <c r="P44" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="Q44" s="121"/>
-      <c r="R44" s="121"/>
+      <c r="Q44" s="128"/>
+      <c r="R44" s="128"/>
       <c r="S44" s="82" t="s">
         <v>133</v>
       </c>
@@ -5096,15 +5131,15 @@
       <c r="G48" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="I48" s="125" t="s">
+      <c r="I48" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="J48" s="126"/>
-      <c r="K48" s="127" t="s">
+      <c r="J48" s="141"/>
+      <c r="K48" s="142" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="128"/>
-      <c r="M48" s="129"/>
+      <c r="L48" s="143"/>
+      <c r="M48" s="144"/>
       <c r="O48" s="83">
         <v>3</v>
       </c>
@@ -5216,12 +5251,12 @@
       <c r="I51" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="J51" s="123"/>
+      <c r="J51" s="124"/>
       <c r="K51" s="122" t="s">
         <v>129</v>
       </c>
-      <c r="L51" s="124"/>
-      <c r="M51" s="123"/>
+      <c r="L51" s="123"/>
+      <c r="M51" s="124"/>
       <c r="O51" s="83">
         <v>6</v>
       </c>
@@ -5258,15 +5293,15 @@
       <c r="G52" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="I52" s="132" t="s">
+      <c r="I52" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="J52" s="133"/>
-      <c r="K52" s="134" t="s">
+      <c r="J52" s="132"/>
+      <c r="K52" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="L52" s="135"/>
-      <c r="M52" s="136"/>
+      <c r="L52" s="134"/>
+      <c r="M52" s="135"/>
       <c r="O52" s="83">
         <v>7</v>
       </c>
@@ -5303,15 +5338,15 @@
       <c r="G53" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="I53" s="132" t="s">
+      <c r="I53" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="J53" s="133"/>
-      <c r="K53" s="134" t="s">
+      <c r="J53" s="132"/>
+      <c r="K53" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="135"/>
-      <c r="M53" s="136"/>
+      <c r="L53" s="134"/>
+      <c r="M53" s="135"/>
       <c r="O53" s="83">
         <v>8</v>
       </c>
@@ -5348,15 +5383,15 @@
       <c r="G54" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I54" s="138" t="s">
+      <c r="I54" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="139"/>
-      <c r="K54" s="140" t="s">
+      <c r="J54" s="126"/>
+      <c r="K54" s="127" t="s">
         <v>131</v>
       </c>
-      <c r="L54" s="121"/>
-      <c r="M54" s="141"/>
+      <c r="L54" s="128"/>
+      <c r="M54" s="129"/>
       <c r="O54" s="83">
         <v>9</v>
       </c>
@@ -5443,23 +5478,23 @@
       <c r="I56" s="87">
         <v>1</v>
       </c>
-      <c r="J56" s="131" t="s">
+      <c r="J56" s="146" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="131"/>
-      <c r="L56" s="131"/>
+      <c r="K56" s="146"/>
+      <c r="L56" s="146"/>
       <c r="M56" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="O56" s="125" t="s">
+      <c r="O56" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="126"/>
-      <c r="Q56" s="127" t="s">
+      <c r="P56" s="141"/>
+      <c r="Q56" s="142" t="s">
         <v>237</v>
       </c>
-      <c r="R56" s="128"/>
-      <c r="S56" s="129"/>
+      <c r="R56" s="143"/>
+      <c r="S56" s="144"/>
     </row>
     <row r="57" spans="2:19" ht="35.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B57" s="33">
@@ -5484,11 +5519,11 @@
       <c r="I57" s="80">
         <v>2</v>
       </c>
-      <c r="J57" s="121" t="s">
+      <c r="J57" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="K57" s="121"/>
-      <c r="L57" s="121"/>
+      <c r="K57" s="128"/>
+      <c r="L57" s="128"/>
       <c r="M57" s="89" t="s">
         <v>134</v>
       </c>
@@ -5531,12 +5566,12 @@
       <c r="O58" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="P58" s="123"/>
+      <c r="P58" s="124"/>
       <c r="Q58" s="122" t="s">
         <v>184</v>
       </c>
-      <c r="R58" s="124"/>
-      <c r="S58" s="123"/>
+      <c r="R58" s="123"/>
+      <c r="S58" s="124"/>
     </row>
     <row r="59" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B59" s="33">
@@ -5573,15 +5608,15 @@
       <c r="M59" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="O59" s="132" t="s">
+      <c r="O59" s="131" t="s">
         <v>108</v>
       </c>
-      <c r="P59" s="133"/>
-      <c r="Q59" s="134" t="s">
+      <c r="P59" s="132"/>
+      <c r="Q59" s="133" t="s">
         <v>232</v>
       </c>
-      <c r="R59" s="135"/>
-      <c r="S59" s="136"/>
+      <c r="R59" s="134"/>
+      <c r="S59" s="135"/>
     </row>
     <row r="60" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B60" s="33">
@@ -5618,15 +5653,15 @@
       <c r="M60" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="O60" s="132" t="s">
+      <c r="O60" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="P60" s="133"/>
-      <c r="Q60" s="132" t="s">
+      <c r="P60" s="132"/>
+      <c r="Q60" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="R60" s="137"/>
-      <c r="S60" s="133"/>
+      <c r="R60" s="145"/>
+      <c r="S60" s="132"/>
     </row>
     <row r="61" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B61" s="33">
@@ -5663,15 +5698,15 @@
       <c r="M61" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="O61" s="138" t="s">
+      <c r="O61" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="P61" s="139"/>
-      <c r="Q61" s="140" t="s">
+      <c r="P61" s="126"/>
+      <c r="Q61" s="127" t="s">
         <v>185</v>
       </c>
-      <c r="R61" s="121"/>
-      <c r="S61" s="141"/>
+      <c r="R61" s="128"/>
+      <c r="S61" s="129"/>
     </row>
     <row r="62" spans="2:19" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B62" s="33">
@@ -5758,11 +5793,11 @@
       <c r="O63" s="87">
         <v>1</v>
       </c>
-      <c r="P63" s="131" t="s">
+      <c r="P63" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="Q63" s="131"/>
-      <c r="R63" s="131"/>
+      <c r="Q63" s="146"/>
+      <c r="R63" s="146"/>
       <c r="S63" s="88" t="s">
         <v>132</v>
       </c>
@@ -5805,11 +5840,11 @@
       <c r="O64" s="80">
         <v>2</v>
       </c>
-      <c r="P64" s="121" t="s">
+      <c r="P64" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="Q64" s="121"/>
-      <c r="R64" s="121"/>
+      <c r="Q64" s="128"/>
+      <c r="R64" s="128"/>
       <c r="S64" s="82" t="s">
         <v>133</v>
       </c>
@@ -6191,24 +6226,24 @@
       <c r="G72" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="I72" s="125" t="s">
+      <c r="I72" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="J72" s="126"/>
-      <c r="K72" s="127" t="s">
+      <c r="J72" s="141"/>
+      <c r="K72" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="L72" s="128"/>
-      <c r="M72" s="129"/>
-      <c r="O72" s="125" t="s">
+      <c r="L72" s="143"/>
+      <c r="M72" s="144"/>
+      <c r="O72" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="P72" s="126"/>
-      <c r="Q72" s="127" t="s">
+      <c r="P72" s="141"/>
+      <c r="Q72" s="142" t="s">
         <v>238</v>
       </c>
-      <c r="R72" s="128"/>
-      <c r="S72" s="129"/>
+      <c r="R72" s="143"/>
+      <c r="S72" s="144"/>
     </row>
     <row r="73" spans="2:19" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B73" s="33">
@@ -6321,19 +6356,19 @@
         <v>60</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D78" s="1">
-        <v>1</v>
+        <v>421</v>
+      </c>
+      <c r="D78" s="90" t="s">
+        <v>422</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>58</v>
+        <v>423</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>233</v>
+        <v>424</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>210</v>
+        <v>425</v>
       </c>
     </row>
     <row r="79" spans="2:19" x14ac:dyDescent="0.4">
@@ -6342,7 +6377,7 @@
         <v>61</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D79" s="1">
         <v>1</v>
@@ -6350,32 +6385,32 @@
       <c r="E79" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F79" s="113" t="s">
+      <c r="F79" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="2:19" x14ac:dyDescent="0.4">
+      <c r="B80" s="33">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F80" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G80" s="5" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="80" spans="2:19" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B80" s="33">
-        <f t="shared" si="1"/>
-        <v>62</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D80" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F80" s="102" t="s">
-        <v>416</v>
-      </c>
-      <c r="G80" s="98" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.4">
@@ -6384,40 +6419,40 @@
         <v>63</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>203</v>
+        <v>426</v>
       </c>
       <c r="D81" s="90" t="s">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F81" s="110" t="s">
-        <v>233</v>
+        <v>423</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>427</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.4">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B82" s="33">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="C82" s="111" t="s">
-        <v>204</v>
-      </c>
-      <c r="D82" s="112" t="s">
-        <v>20</v>
+      <c r="C82" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D82" s="90" t="s">
+        <v>21</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F82" s="110" t="s">
-        <v>233</v>
-      </c>
-      <c r="G82" s="111" t="s">
-        <v>206</v>
+        <v>234</v>
+      </c>
+      <c r="F82" s="102" t="s">
+        <v>416</v>
+      </c>
+      <c r="G82" s="98" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.4">
@@ -6426,19 +6461,19 @@
         <v>65</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D83" s="1">
-        <v>1</v>
+        <v>203</v>
+      </c>
+      <c r="D83" s="90" t="s">
+        <v>20</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>236</v>
+        <v>62</v>
+      </c>
+      <c r="F83" s="110" t="s">
+        <v>233</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.4">
@@ -6446,41 +6481,41 @@
         <f t="shared" ref="B84:B115" si="2">IF(C84="","",B83+1)</f>
         <v>66</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D84" s="1">
-        <v>1</v>
+      <c r="C84" s="111" t="s">
+        <v>204</v>
+      </c>
+      <c r="D84" s="112" t="s">
+        <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+      <c r="F84" s="110" t="s">
+        <v>233</v>
+      </c>
+      <c r="G84" s="111" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B85" s="33">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D85" s="100" t="s">
-        <v>46</v>
+        <v>336</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>227</v>
+        <v>58</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>51</v>
+        <v>208</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.4">
@@ -6489,7 +6524,7 @@
         <v>68</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D86" s="1">
         <v>1</v>
@@ -6498,31 +6533,31 @@
         <v>58</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.4">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B87" s="33">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D87" s="90" t="s">
-        <v>20</v>
+        <v>276</v>
+      </c>
+      <c r="D87" s="100" t="s">
+        <v>46</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F87" s="102" t="s">
-        <v>233</v>
+        <v>42</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>222</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.4">
@@ -6530,20 +6565,20 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C88" s="96" t="s">
-        <v>190</v>
-      </c>
-      <c r="D88" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E88" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F88" s="97" t="s">
-        <v>325</v>
-      </c>
-      <c r="G88" s="98" t="s">
-        <v>191</v>
+      <c r="C88" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D88" s="1">
+        <v>1</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.4">
@@ -6551,20 +6586,20 @@
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C89" s="118" t="s">
-        <v>412</v>
-      </c>
-      <c r="D89" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="E89" s="119" t="s">
-        <v>417</v>
-      </c>
-      <c r="F89" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="120" t="s">
-        <v>37</v>
+      <c r="C89" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D89" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="102" t="s">
+        <v>233</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.4">
@@ -6572,41 +6607,41 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C90" s="93" t="s">
-        <v>275</v>
-      </c>
-      <c r="D90" s="92">
-        <v>1</v>
-      </c>
-      <c r="E90" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F90" s="99" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="95" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="C90" s="96" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F90" s="97" t="s">
+        <v>325</v>
+      </c>
+      <c r="G90" s="98" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B91" s="33">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C91" s="96" t="s">
-        <v>411</v>
-      </c>
-      <c r="D91" s="90" t="s">
+      <c r="C91" s="118" t="s">
+        <v>412</v>
+      </c>
+      <c r="D91" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="E91" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="F91" s="97" t="s">
-        <v>418</v>
-      </c>
-      <c r="G91" s="98" t="s">
-        <v>413</v>
+      <c r="E91" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="F91" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="120" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.4">
@@ -6614,62 +6649,62 @@
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D92" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="C92" s="93" t="s">
+        <v>275</v>
+      </c>
+      <c r="D92" s="92">
+        <v>1</v>
+      </c>
+      <c r="E92" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F92" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="95" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B93" s="33">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>409</v>
+      <c r="C93" s="96" t="s">
+        <v>411</v>
       </c>
       <c r="D93" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F93" s="2" t="s">
+      <c r="E93" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="F93" s="97" t="s">
+        <v>418</v>
+      </c>
+      <c r="G93" s="98" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B94" s="33">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C94" s="103" t="s">
-        <v>254</v>
-      </c>
-      <c r="D94" s="108" t="s">
-        <v>20</v>
-      </c>
-      <c r="E94" s="104" t="s">
-        <v>237</v>
-      </c>
-      <c r="F94" s="109" t="s">
-        <v>414</v>
-      </c>
-      <c r="G94" s="106" t="s">
-        <v>257</v>
+      <c r="C94" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D94" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.4">
@@ -6678,40 +6713,40 @@
         <v>77</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>305</v>
+        <v>409</v>
       </c>
       <c r="D95" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E95" s="102" t="s">
-        <v>237</v>
-      </c>
-      <c r="F95" s="102" t="s">
-        <v>342</v>
+        <v>21</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.4">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B96" s="33">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D96" s="1">
-        <v>1</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="C96" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="D96" s="108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="102" t="s">
-        <v>330</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>360</v>
+      <c r="F96" s="109" t="s">
+        <v>414</v>
+      </c>
+      <c r="G96" s="106" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.4">
@@ -6720,19 +6755,19 @@
         <v>79</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="D97" s="1">
-        <v>2</v>
-      </c>
-      <c r="E97" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D97" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E97" s="102" t="s">
         <v>237</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>238</v>
+      <c r="F97" s="102" t="s">
+        <v>342</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>388</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.4">
@@ -6740,20 +6775,20 @@
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C98" s="103" t="s">
-        <v>249</v>
-      </c>
-      <c r="D98" s="104">
+      <c r="C98" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D98" s="1">
         <v>1</v>
       </c>
-      <c r="E98" s="104" t="s">
+      <c r="E98" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F98" s="105" t="s">
-        <v>14</v>
-      </c>
-      <c r="G98" s="106" t="s">
-        <v>251</v>
+      <c r="F98" s="102" t="s">
+        <v>330</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.4">
@@ -6762,10 +6797,10 @@
         <v>81</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>265</v>
+        <v>386</v>
       </c>
       <c r="D99" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>237</v>
@@ -6774,16 +6809,16 @@
         <v>238</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B100" s="33">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="C100" s="103" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D100" s="104">
         <v>1</v>
@@ -6791,11 +6826,11 @@
       <c r="E100" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F100" s="107" t="s">
-        <v>73</v>
+      <c r="F100" s="105" t="s">
+        <v>14</v>
       </c>
       <c r="G100" s="106" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.4">
@@ -6804,10 +6839,10 @@
         <v>83</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D101" s="90" t="s">
-        <v>21</v>
+        <v>265</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>237</v>
@@ -6816,217 +6851,217 @@
         <v>238</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.4">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B102" s="33">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C102" s="111" t="s">
-        <v>258</v>
-      </c>
-      <c r="D102" s="112" t="s">
-        <v>20</v>
-      </c>
-      <c r="E102" s="110" t="s">
+      <c r="C102" s="103" t="s">
+        <v>250</v>
+      </c>
+      <c r="D102" s="104">
+        <v>1</v>
+      </c>
+      <c r="E102" s="104" t="s">
         <v>237</v>
       </c>
-      <c r="F102" s="117" t="s">
-        <v>330</v>
-      </c>
-      <c r="G102" s="111" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="F102" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="G102" s="106" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B103" s="33">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>322</v>
+        <v>394</v>
       </c>
       <c r="D103" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E103" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F103" s="102" t="s">
-        <v>334</v>
+      <c r="F103" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B104" s="33">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D104" s="1">
-        <v>1</v>
-      </c>
-      <c r="E104" s="2" t="s">
+      <c r="C104" s="111" t="s">
+        <v>258</v>
+      </c>
+      <c r="D104" s="112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="F104" s="102" t="s">
-        <v>328</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F104" s="117" t="s">
+        <v>330</v>
+      </c>
+      <c r="G104" s="111" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B105" s="33">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="C105" s="103" t="s">
-        <v>349</v>
-      </c>
-      <c r="D105" s="108" t="s">
-        <v>20</v>
-      </c>
-      <c r="E105" s="116" t="s">
-        <v>330</v>
-      </c>
-      <c r="F105" s="105" t="s">
-        <v>17</v>
-      </c>
-      <c r="G105" s="106" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="C105" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D105" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F105" s="102" t="s">
+        <v>334</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B106" s="33">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="D106" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E106" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D106" s="1">
+        <v>1</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F106" s="1" t="s">
-        <v>330</v>
+      <c r="F106" s="102" t="s">
+        <v>328</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" ht="87" x14ac:dyDescent="0.4">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B107" s="33">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D107" s="90" t="s">
+      <c r="C107" s="103" t="s">
+        <v>349</v>
+      </c>
+      <c r="D107" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F107" s="102" t="s">
-        <v>369</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="E107" s="116" t="s">
+        <v>330</v>
+      </c>
+      <c r="F107" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="106" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B108" s="33">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D108" s="1">
-        <v>2</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F108" s="102" t="s">
-        <v>397</v>
+        <v>361</v>
+      </c>
+      <c r="D108" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" ht="87" x14ac:dyDescent="0.4">
       <c r="B109" s="33">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D109" s="1">
-        <v>1</v>
-      </c>
-      <c r="E109" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D109" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>238</v>
       </c>
       <c r="F109" s="102" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.4">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B110" s="33">
         <f>IF(C110="","",B109+1)</f>
         <v>92</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>266</v>
+        <v>387</v>
       </c>
       <c r="D110" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>80</v>
+      <c r="F110" s="102" t="s">
+        <v>397</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.4">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B111" s="33">
         <f>IF(C111="","",B110+1)</f>
         <v>93</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D111" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>62</v>
+        <v>396</v>
+      </c>
+      <c r="D111" s="1">
+        <v>1</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F111" s="102" t="s">
+        <v>340</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.4">
@@ -7035,19 +7070,19 @@
         <v>94</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D112" s="90" t="s">
-        <v>21</v>
+        <v>266</v>
+      </c>
+      <c r="D112" s="1">
+        <v>1</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F112" s="102" t="s">
+      <c r="F112" s="2" t="s">
         <v>80</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>400</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.4">
@@ -7056,52 +7091,82 @@
         <v>95</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>390</v>
+        <v>287</v>
       </c>
       <c r="D113" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F113" s="102" t="s">
+        <v>20</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="114" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B114" s="33">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="C114" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D114" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F114" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B115" s="33">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D115" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F115" s="102" t="s">
+        <v>62</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B116" s="33">
+        <f t="shared" ref="B116:B141" si="3">IF(C116="","",B115+1)</f>
+        <v>98</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D114" s="90" t="s">
+      <c r="D116" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F114" s="102" t="s">
+      <c r="F116" s="102" t="s">
         <v>391</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G116" s="5" t="s">
         <v>311</v>
-      </c>
-    </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B115" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B116" s="33" t="str">
-        <f t="shared" ref="B116:B141" si="3">IF(C116="","",B115+1)</f>
-        <v/>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.4">
@@ -7256,44 +7321,56 @@
     </row>
   </sheetData>
   <autoFilter ref="C18:G141">
-    <sortState ref="C18:G140">
-      <sortCondition ref="C17:C140"/>
+    <sortState ref="C19:G141">
+      <sortCondition ref="C18:C141"/>
     </sortState>
   </autoFilter>
   <mergeCells count="102">
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="I72:J72"/>
     <mergeCell ref="K72:M72"/>
     <mergeCell ref="J57:L57"/>
@@ -7318,51 +7395,39 @@
     <mergeCell ref="K52:M52"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:M40"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="O72:P72"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="Q59:S59"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="O61:P61"/>
-    <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="O58:P58"/>
-    <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="P62:R62"/>
-    <mergeCell ref="P63:R63"/>
-    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="J42:L42"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
